--- a/database/event/1954/event_1954_evp_summary.xlsx
+++ b/database/event/1954/event_1954_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.4208</v>
+        <v>8.4442</v>
       </c>
       <c r="C2" t="n">
-        <v>1.4578</v>
+        <v>1.6589</v>
       </c>
       <c r="D2" t="n">
-        <v>2.5765</v>
+        <v>2.9203</v>
       </c>
       <c r="E2" t="n">
-        <v>7.4208</v>
+        <v>8.4442</v>
       </c>
       <c r="F2" t="n">
-        <v>2.9249</v>
+        <v>3.9484</v>
       </c>
       <c r="G2" t="n">
         <v>4.4959</v>
       </c>
       <c r="H2" t="n">
-        <v>2.9249</v>
+        <v>3.9484</v>
       </c>
       <c r="I2" t="n">
-        <v>2.3708</v>
+        <v>3.2003</v>
       </c>
       <c r="J2" t="n">
         <v>4.4959</v>
@@ -529,7 +529,7 @@
         <v>102</v>
       </c>
       <c r="M2" t="n">
-        <v>6.8667</v>
+        <v>7.696199999999999</v>
       </c>
       <c r="N2" t="n">
         <v>142</v>
@@ -548,19 +548,19 @@
         <v>1.149</v>
       </c>
       <c r="D3" t="n">
-        <v>1.9414</v>
+        <v>1.8863</v>
       </c>
       <c r="E3" t="n">
         <v>5.8488</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5288</v>
+        <v>1.5289</v>
       </c>
       <c r="G3" t="n">
         <v>4.3199</v>
       </c>
       <c r="H3" t="n">
-        <v>1.5288</v>
+        <v>1.5289</v>
       </c>
       <c r="I3" t="n">
         <v>1.2392</v>
@@ -588,28 +588,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.7114</v>
+        <v>5.1276</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9255</v>
+        <v>1.0073</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4819</v>
+        <v>1.5989</v>
       </c>
       <c r="E4" t="n">
-        <v>4.7114</v>
+        <v>5.1276</v>
       </c>
       <c r="F4" t="n">
-        <v>3.0277</v>
+        <v>3.4439</v>
       </c>
       <c r="G4" t="n">
         <v>1.6837</v>
       </c>
       <c r="H4" t="n">
-        <v>3.0277</v>
+        <v>3.4439</v>
       </c>
       <c r="I4" t="n">
-        <v>2.454</v>
+        <v>2.7913</v>
       </c>
       <c r="J4" t="n">
         <v>1.6837</v>
@@ -621,7 +621,7 @@
         <v>91</v>
       </c>
       <c r="M4" t="n">
-        <v>4.137700000000001</v>
+        <v>4.475</v>
       </c>
       <c r="N4" t="n">
         <v>217</v>
@@ -634,28 +634,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.023</v>
+        <v>4.3283</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7903</v>
+        <v>0.8502999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2038</v>
+        <v>1.2805</v>
       </c>
       <c r="E5" t="n">
-        <v>4.023</v>
+        <v>4.3283</v>
       </c>
       <c r="F5" t="n">
-        <v>2.029</v>
+        <v>2.3343</v>
       </c>
       <c r="G5" t="n">
         <v>1.994</v>
       </c>
       <c r="H5" t="n">
-        <v>2.029</v>
+        <v>2.3343</v>
       </c>
       <c r="I5" t="n">
-        <v>1.6446</v>
+        <v>1.892</v>
       </c>
       <c r="J5" t="n">
         <v>1.994</v>
@@ -667,7 +667,7 @@
         <v>102</v>
       </c>
       <c r="M5" t="n">
-        <v>3.6386</v>
+        <v>3.886</v>
       </c>
       <c r="N5" t="n">
         <v>142</v>
@@ -676,185 +676,185 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>n0thing</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.5597</v>
+        <v>3.7402</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6993</v>
+        <v>0.7348</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0167</v>
+        <v>1.0462</v>
       </c>
       <c r="E6" t="n">
-        <v>3.5597</v>
+        <v>3.7402</v>
       </c>
       <c r="F6" t="n">
-        <v>3.6772</v>
+        <v>3.3289</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.1175</v>
+        <v>0.4113</v>
       </c>
       <c r="H6" t="n">
-        <v>3.6772</v>
+        <v>3.3289</v>
       </c>
       <c r="I6" t="n">
-        <v>2.9805</v>
+        <v>2.6982</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.1175</v>
+        <v>0.4113</v>
       </c>
       <c r="K6" t="n">
-        <v>97</v>
+        <v>126</v>
       </c>
       <c r="L6" t="n">
-        <v>52</v>
+        <v>91</v>
       </c>
       <c r="M6" t="n">
-        <v>2.863</v>
+        <v>3.1095</v>
       </c>
       <c r="N6" t="n">
-        <v>149</v>
+        <v>217</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>n0thing</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.1751</v>
+        <v>3.5597</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6237</v>
+        <v>0.6993</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8613</v>
+        <v>0.9743000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>3.1751</v>
+        <v>3.5597</v>
       </c>
       <c r="F7" t="n">
-        <v>2.7638</v>
+        <v>3.6772</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4113</v>
+        <v>-0.1175</v>
       </c>
       <c r="H7" t="n">
-        <v>2.7638</v>
+        <v>3.6772</v>
       </c>
       <c r="I7" t="n">
-        <v>2.2401</v>
+        <v>2.9805</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4113</v>
+        <v>-0.1175</v>
       </c>
       <c r="K7" t="n">
-        <v>126</v>
+        <v>97</v>
       </c>
       <c r="L7" t="n">
-        <v>91</v>
+        <v>52</v>
       </c>
       <c r="M7" t="n">
-        <v>2.6514</v>
+        <v>2.863</v>
       </c>
       <c r="N7" t="n">
-        <v>217</v>
+        <v>149</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.1652</v>
+        <v>3.5498</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6218</v>
+        <v>0.6974</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8573</v>
+        <v>0.9703000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>3.1652</v>
+        <v>3.5498</v>
       </c>
       <c r="F8" t="n">
-        <v>4.0386</v>
+        <v>2.5346</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.8734</v>
+        <v>1.0152</v>
       </c>
       <c r="H8" t="n">
-        <v>4.0386</v>
+        <v>2.5346</v>
       </c>
       <c r="I8" t="n">
-        <v>3.2734</v>
+        <v>2.0544</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.8734</v>
+        <v>1.0152</v>
       </c>
       <c r="K8" t="n">
-        <v>97</v>
+        <v>40</v>
       </c>
       <c r="L8" t="n">
-        <v>52</v>
+        <v>102</v>
       </c>
       <c r="M8" t="n">
-        <v>2.4</v>
+        <v>3.0696</v>
       </c>
       <c r="N8" t="n">
-        <v>149</v>
+        <v>142</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.1537</v>
+        <v>3.1652</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6195000000000001</v>
+        <v>0.6218</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8527</v>
+        <v>0.8171</v>
       </c>
       <c r="E9" t="n">
-        <v>3.1537</v>
+        <v>3.1652</v>
       </c>
       <c r="F9" t="n">
-        <v>2.1385</v>
+        <v>4.0386</v>
       </c>
       <c r="G9" t="n">
-        <v>1.0152</v>
+        <v>-0.8734</v>
       </c>
       <c r="H9" t="n">
-        <v>2.1385</v>
+        <v>4.0386</v>
       </c>
       <c r="I9" t="n">
-        <v>1.7333</v>
+        <v>3.2734</v>
       </c>
       <c r="J9" t="n">
-        <v>1.0152</v>
+        <v>-0.8734</v>
       </c>
       <c r="K9" t="n">
-        <v>40</v>
+        <v>97</v>
       </c>
       <c r="L9" t="n">
-        <v>102</v>
+        <v>52</v>
       </c>
       <c r="M9" t="n">
-        <v>2.7485</v>
+        <v>2.4</v>
       </c>
       <c r="N9" t="n">
-        <v>142</v>
+        <v>149</v>
       </c>
     </row>
     <row r="10">
@@ -864,28 +864,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.3274</v>
+        <v>2.6272</v>
       </c>
       <c r="C10" t="n">
-        <v>0.4572</v>
+        <v>0.5161</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5189</v>
+        <v>0.6028</v>
       </c>
       <c r="E10" t="n">
-        <v>2.3274</v>
+        <v>2.6272</v>
       </c>
       <c r="F10" t="n">
-        <v>2.0226</v>
+        <v>2.3224</v>
       </c>
       <c r="G10" t="n">
         <v>0.3048</v>
       </c>
       <c r="H10" t="n">
-        <v>2.0226</v>
+        <v>2.3224</v>
       </c>
       <c r="I10" t="n">
-        <v>1.6393</v>
+        <v>1.8824</v>
       </c>
       <c r="J10" t="n">
         <v>0.3048</v>
@@ -897,7 +897,7 @@
         <v>141</v>
       </c>
       <c r="M10" t="n">
-        <v>1.9441</v>
+        <v>2.1872</v>
       </c>
       <c r="N10" t="n">
         <v>188</v>
@@ -910,28 +910,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.3143</v>
+        <v>2.3813</v>
       </c>
       <c r="C11" t="n">
-        <v>0.4546</v>
+        <v>0.4678</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5135999999999999</v>
+        <v>0.5048</v>
       </c>
       <c r="E11" t="n">
-        <v>2.3143</v>
+        <v>2.3813</v>
       </c>
       <c r="F11" t="n">
-        <v>2.4994</v>
+        <v>2.5664</v>
       </c>
       <c r="G11" t="n">
         <v>-0.1851</v>
       </c>
       <c r="H11" t="n">
-        <v>2.4994</v>
+        <v>2.5664</v>
       </c>
       <c r="I11" t="n">
-        <v>2.0259</v>
+        <v>2.0802</v>
       </c>
       <c r="J11" t="n">
         <v>-0.1851</v>
@@ -943,7 +943,7 @@
         <v>52</v>
       </c>
       <c r="M11" t="n">
-        <v>1.8408</v>
+        <v>1.8951</v>
       </c>
       <c r="N11" t="n">
         <v>149</v>
@@ -952,35 +952,35 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>shroud</t>
+          <t>Skadoodle</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.0431</v>
+        <v>2.2137</v>
       </c>
       <c r="C12" t="n">
-        <v>0.4014</v>
+        <v>0.4349</v>
       </c>
       <c r="D12" t="n">
-        <v>0.404</v>
+        <v>0.438</v>
       </c>
       <c r="E12" t="n">
-        <v>2.0431</v>
+        <v>2.2137</v>
       </c>
       <c r="F12" t="n">
-        <v>1.887</v>
+        <v>1.801</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1561</v>
+        <v>0.4127</v>
       </c>
       <c r="H12" t="n">
-        <v>1.887</v>
+        <v>1.801</v>
       </c>
       <c r="I12" t="n">
-        <v>1.5295</v>
+        <v>1.4598</v>
       </c>
       <c r="J12" t="n">
-        <v>0.1561</v>
+        <v>0.4127</v>
       </c>
       <c r="K12" t="n">
         <v>126</v>
@@ -989,7 +989,7 @@
         <v>91</v>
       </c>
       <c r="M12" t="n">
-        <v>1.6856</v>
+        <v>1.8725</v>
       </c>
       <c r="N12" t="n">
         <v>217</v>
@@ -998,127 +998,127 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>felps</t>
+          <t>shroud</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.6887</v>
+        <v>2.0431</v>
       </c>
       <c r="C13" t="n">
-        <v>0.3317</v>
+        <v>0.4014</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2608</v>
+        <v>0.3701</v>
       </c>
       <c r="E13" t="n">
-        <v>1.6887</v>
+        <v>2.0431</v>
       </c>
       <c r="F13" t="n">
-        <v>1.4001</v>
+        <v>1.887</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2886</v>
+        <v>0.1561</v>
       </c>
       <c r="H13" t="n">
-        <v>1.4001</v>
+        <v>1.887</v>
       </c>
       <c r="I13" t="n">
-        <v>1.1348</v>
+        <v>1.5295</v>
       </c>
       <c r="J13" t="n">
-        <v>0.2886</v>
+        <v>0.1561</v>
       </c>
       <c r="K13" t="n">
-        <v>47</v>
+        <v>126</v>
       </c>
       <c r="L13" t="n">
-        <v>141</v>
+        <v>91</v>
       </c>
       <c r="M13" t="n">
-        <v>1.4234</v>
+        <v>1.6856</v>
       </c>
       <c r="N13" t="n">
-        <v>188</v>
+        <v>217</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Skadoodle</t>
+          <t>LUCAS1</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.6763</v>
+        <v>1.8753</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3293</v>
+        <v>0.3684</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2558</v>
+        <v>0.3032</v>
       </c>
       <c r="E14" t="n">
-        <v>1.6763</v>
+        <v>1.8753</v>
       </c>
       <c r="F14" t="n">
-        <v>1.2636</v>
+        <v>2.2721</v>
       </c>
       <c r="G14" t="n">
-        <v>0.4127</v>
+        <v>-0.3968</v>
       </c>
       <c r="H14" t="n">
-        <v>1.2636</v>
+        <v>2.2721</v>
       </c>
       <c r="I14" t="n">
-        <v>1.0241</v>
+        <v>1.8416</v>
       </c>
       <c r="J14" t="n">
-        <v>0.4127</v>
+        <v>-0.3968</v>
       </c>
       <c r="K14" t="n">
-        <v>126</v>
+        <v>47</v>
       </c>
       <c r="L14" t="n">
-        <v>91</v>
+        <v>141</v>
       </c>
       <c r="M14" t="n">
-        <v>1.4368</v>
+        <v>1.4448</v>
       </c>
       <c r="N14" t="n">
-        <v>217</v>
+        <v>188</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LUCAS1</t>
+          <t>felps</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.48</v>
+        <v>1.6887</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2907</v>
+        <v>0.3317</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1765</v>
+        <v>0.2289</v>
       </c>
       <c r="E15" t="n">
-        <v>1.48</v>
+        <v>1.6887</v>
       </c>
       <c r="F15" t="n">
-        <v>1.8768</v>
+        <v>1.4001</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.3968</v>
+        <v>0.2886</v>
       </c>
       <c r="H15" t="n">
-        <v>1.8768</v>
+        <v>1.4001</v>
       </c>
       <c r="I15" t="n">
-        <v>1.5212</v>
+        <v>1.1348</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.3968</v>
+        <v>0.2886</v>
       </c>
       <c r="K15" t="n">
         <v>47</v>
@@ -1127,7 +1127,7 @@
         <v>141</v>
       </c>
       <c r="M15" t="n">
-        <v>1.1244</v>
+        <v>1.4234</v>
       </c>
       <c r="N15" t="n">
         <v>188</v>
@@ -1140,28 +1140,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.2297</v>
+        <v>1.484</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2416</v>
+        <v>0.2915</v>
       </c>
       <c r="D16" t="n">
-        <v>0.07539999999999999</v>
+        <v>0.1473</v>
       </c>
       <c r="E16" t="n">
-        <v>1.2297</v>
+        <v>1.484</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2572</v>
+        <v>0.5115</v>
       </c>
       <c r="G16" t="n">
         <v>0.9725</v>
       </c>
       <c r="H16" t="n">
-        <v>0.2572</v>
+        <v>0.5115</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2084</v>
+        <v>0.4146</v>
       </c>
       <c r="J16" t="n">
         <v>0.9725</v>
@@ -1173,7 +1173,7 @@
         <v>102</v>
       </c>
       <c r="M16" t="n">
-        <v>1.1809</v>
+        <v>1.3871</v>
       </c>
       <c r="N16" t="n">
         <v>142</v>
@@ -1182,216 +1182,216 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>mitch</t>
+          <t>koosta</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.0632</v>
+        <v>1.3779</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2089</v>
+        <v>0.2707</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0081</v>
+        <v>0.105</v>
       </c>
       <c r="E17" t="n">
-        <v>1.0632</v>
+        <v>1.3779</v>
       </c>
       <c r="F17" t="n">
-        <v>1.0632</v>
+        <v>2.1445</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>-0.7665999999999999</v>
       </c>
       <c r="H17" t="n">
-        <v>1.0632</v>
+        <v>2.1445</v>
       </c>
       <c r="I17" t="n">
-        <v>1.0632</v>
+        <v>1.7382</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>-0.7665999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>157</v>
+        <v>97</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="M17" t="n">
-        <v>1.0632</v>
+        <v>0.9716</v>
       </c>
       <c r="N17" t="n">
-        <v>157</v>
+        <v>149</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>gob b</t>
+          <t>mitch</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9787</v>
+        <v>1.0632</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1923</v>
+        <v>0.2089</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.026</v>
+        <v>-0.0203</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9787</v>
+        <v>1.0632</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9787</v>
+        <v>1.0632</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9787</v>
+        <v>1.0632</v>
       </c>
       <c r="I18" t="n">
-        <v>0.9787</v>
+        <v>1.0632</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>107</v>
+        <v>157</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.9787</v>
+        <v>1.0632</v>
       </c>
       <c r="N18" t="n">
-        <v>107</v>
+        <v>157</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>koosta</t>
+          <t>SHOOWTiME</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.833</v>
+        <v>0.9838</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1636</v>
+        <v>0.1933</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0848</v>
+        <v>-0.052</v>
       </c>
       <c r="E19" t="n">
-        <v>0.833</v>
+        <v>0.9838</v>
       </c>
       <c r="F19" t="n">
-        <v>1.5996</v>
+        <v>1.1843</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.7665999999999999</v>
+        <v>-0.2005</v>
       </c>
       <c r="H19" t="n">
-        <v>1.5996</v>
+        <v>1.1843</v>
       </c>
       <c r="I19" t="n">
-        <v>1.2965</v>
+        <v>0.9599</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.7665999999999999</v>
+        <v>-0.2005</v>
       </c>
       <c r="K19" t="n">
-        <v>97</v>
+        <v>47</v>
       </c>
       <c r="L19" t="n">
-        <v>52</v>
+        <v>141</v>
       </c>
       <c r="M19" t="n">
-        <v>0.5299</v>
+        <v>0.7594</v>
       </c>
       <c r="N19" t="n">
-        <v>149</v>
+        <v>188</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>reltuC</t>
+          <t>gob b</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6505</v>
+        <v>0.9787</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1278</v>
+        <v>0.1923</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1586</v>
+        <v>-0.054</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6505</v>
+        <v>0.9787</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6505</v>
+        <v>0.9787</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.6505</v>
+        <v>0.9787</v>
       </c>
       <c r="I20" t="n">
-        <v>0.6535</v>
+        <v>0.9787</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>168</v>
+        <v>107</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.6535</v>
+        <v>0.9787</v>
       </c>
       <c r="N20" t="n">
-        <v>168</v>
+        <v>107</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>tarik</t>
+          <t>reltuC</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.5029</v>
+        <v>0.648</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0988</v>
+        <v>0.1273</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2182</v>
+        <v>-0.1857</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5029</v>
+        <v>0.648</v>
       </c>
       <c r="F21" t="n">
-        <v>0.5029</v>
+        <v>0.648</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.5029</v>
+        <v>0.648</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5052</v>
+        <v>0.6535</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.5052</v>
+        <v>0.6535</v>
       </c>
       <c r="N21" t="n">
         <v>168</v>
@@ -1412,32 +1412,32 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>jdm64</t>
+          <t>tarik</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.4654</v>
+        <v>0.501</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0914</v>
+        <v>0.0984</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2334</v>
+        <v>-0.2443</v>
       </c>
       <c r="E22" t="n">
-        <v>0.4654</v>
+        <v>0.501</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4654</v>
+        <v>0.501</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.4654</v>
+        <v>0.501</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4676</v>
+        <v>0.5052</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.4676</v>
+        <v>0.5052</v>
       </c>
       <c r="N22" t="n">
         <v>168</v>
@@ -1458,47 +1458,47 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SHOOWTiME</t>
+          <t>jdm64</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.4186</v>
+        <v>0.4637</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0822</v>
+        <v>0.0911</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2523</v>
+        <v>-0.2592</v>
       </c>
       <c r="E23" t="n">
-        <v>0.4186</v>
+        <v>0.4637</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6191</v>
+        <v>0.4637</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.2005</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.6191</v>
+        <v>0.4637</v>
       </c>
       <c r="I23" t="n">
-        <v>0.5018</v>
+        <v>0.4676</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.2005</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>47</v>
+        <v>168</v>
       </c>
       <c r="L23" t="n">
-        <v>141</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.3013</v>
+        <v>0.4676</v>
       </c>
       <c r="N23" t="n">
-        <v>188</v>
+        <v>168</v>
       </c>
     </row>
     <row r="24">
@@ -1514,7 +1514,7 @@
         <v>0.0489</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3208</v>
+        <v>-0.3447</v>
       </c>
       <c r="E24" t="n">
         <v>0.249</v>
@@ -1560,7 +1560,7 @@
         <v>0.036</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3474</v>
+        <v>-0.3709</v>
       </c>
       <c r="E25" t="n">
         <v>0.1832</v>
@@ -1606,7 +1606,7 @@
         <v>0.0041</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.413</v>
+        <v>-0.4357</v>
       </c>
       <c r="E26" t="n">
         <v>0.0207</v>
@@ -1652,7 +1652,7 @@
         <v>-0.0075</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4368</v>
+        <v>-0.4591</v>
       </c>
       <c r="E27" t="n">
         <v>-0.0382</v>
@@ -1698,7 +1698,7 @@
         <v>-0.0203</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4631</v>
+        <v>-0.4851</v>
       </c>
       <c r="E28" t="n">
         <v>-0.1033</v>
@@ -1744,7 +1744,7 @@
         <v>-0.0204</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.4634</v>
+        <v>-0.4853</v>
       </c>
       <c r="E29" t="n">
         <v>-0.104</v>
@@ -1790,7 +1790,7 @@
         <v>-0.0286</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.4802</v>
+        <v>-0.5019</v>
       </c>
       <c r="E30" t="n">
         <v>-0.1456</v>
@@ -1830,25 +1830,25 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.1476</v>
+        <v>-0.1471</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.029</v>
+        <v>-0.0289</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.481</v>
+        <v>-0.5024999999999999</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.1476</v>
+        <v>-0.1471</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.1476</v>
+        <v>-0.1471</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.1476</v>
+        <v>-0.1471</v>
       </c>
       <c r="I31" t="n">
         <v>-0.1483</v>
@@ -1882,7 +1882,7 @@
         <v>-0.0382</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.4999</v>
+        <v>-0.5213</v>
       </c>
       <c r="E32" t="n">
         <v>-0.1943</v>
@@ -1928,7 +1928,7 @@
         <v>-0.06619999999999999</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.5574</v>
+        <v>-0.5780999999999999</v>
       </c>
       <c r="E33" t="n">
         <v>-0.3368</v>
@@ -1974,7 +1974,7 @@
         <v>-0.1317</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.6922</v>
+        <v>-0.711</v>
       </c>
       <c r="E34" t="n">
         <v>-0.6705</v>
@@ -2020,7 +2020,7 @@
         <v>-0.1695</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.7699</v>
+        <v>-0.7876</v>
       </c>
       <c r="E35" t="n">
         <v>-0.8627</v>
@@ -2066,7 +2066,7 @@
         <v>-0.231</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.8965</v>
+        <v>-0.9125</v>
       </c>
       <c r="E36" t="n">
         <v>-1.1761</v>
@@ -2112,7 +2112,7 @@
         <v>-0.2995</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0372</v>
+        <v>-1.0512</v>
       </c>
       <c r="E37" t="n">
         <v>-1.5244</v>
@@ -2158,7 +2158,7 @@
         <v>-0.3049</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0483</v>
+        <v>-1.0622</v>
       </c>
       <c r="E38" t="n">
         <v>-1.5519</v>
@@ -2204,7 +2204,7 @@
         <v>-0.3139</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.0668</v>
+        <v>-1.0804</v>
       </c>
       <c r="E39" t="n">
         <v>-1.5977</v>
@@ -2244,25 +2244,25 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.9284</v>
+        <v>-1.9212</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.3788</v>
+        <v>-0.3774</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.2004</v>
+        <v>-1.2093</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.9284</v>
+        <v>-1.9212</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.9284</v>
+        <v>-1.9212</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.9284</v>
+        <v>-1.9212</v>
       </c>
       <c r="I40" t="n">
         <v>-1.9374</v>
@@ -2290,28 +2290,28 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.6895</v>
+        <v>-2.5988</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.5283</v>
+        <v>-0.5105</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.5079</v>
+        <v>-1.4793</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.6895</v>
+        <v>-2.5988</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.6895</v>
+        <v>-1.5988</v>
       </c>
       <c r="G41" t="n">
         <v>-1</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.6895</v>
+        <v>-1.5988</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.3694</v>
+        <v>-1.2959</v>
       </c>
       <c r="J41" t="n">
         <v>-1</v>
@@ -2323,7 +2323,7 @@
         <v>91</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.3694</v>
+        <v>-2.2959</v>
       </c>
       <c r="N41" t="n">
         <v>217</v>

--- a/database/event/1954/event_1954_evp_summary.xlsx
+++ b/database/event/1954/event_1954_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.4442</v>
+        <v>6.9857</v>
       </c>
       <c r="C2" t="n">
-        <v>1.6589</v>
+        <v>1.3723</v>
       </c>
       <c r="D2" t="n">
-        <v>2.9203</v>
+        <v>2.5157</v>
       </c>
       <c r="E2" t="n">
-        <v>8.4442</v>
+        <v>6.9857</v>
       </c>
       <c r="F2" t="n">
-        <v>3.9484</v>
+        <v>3.0903</v>
       </c>
       <c r="G2" t="n">
-        <v>4.4959</v>
+        <v>3.8955</v>
       </c>
       <c r="H2" t="n">
-        <v>3.9484</v>
+        <v>5.4018</v>
       </c>
       <c r="I2" t="n">
-        <v>3.2003</v>
+        <v>2.8087</v>
       </c>
       <c r="J2" t="n">
-        <v>4.4959</v>
+        <v>3.8955</v>
       </c>
       <c r="K2" t="n">
         <v>40</v>
@@ -529,7 +529,7 @@
         <v>102</v>
       </c>
       <c r="M2" t="n">
-        <v>7.696199999999999</v>
+        <v>6.7042</v>
       </c>
       <c r="N2" t="n">
         <v>142</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.8488</v>
+        <v>6.0907</v>
       </c>
       <c r="C3" t="n">
-        <v>1.149</v>
+        <v>1.1965</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8863</v>
+        <v>2.1116</v>
       </c>
       <c r="E3" t="n">
-        <v>5.8488</v>
+        <v>6.0907</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5289</v>
+        <v>2.3522</v>
       </c>
       <c r="G3" t="n">
-        <v>4.3199</v>
+        <v>3.7385</v>
       </c>
       <c r="H3" t="n">
-        <v>1.5289</v>
+        <v>2.8014</v>
       </c>
       <c r="I3" t="n">
-        <v>1.2392</v>
+        <v>1.4566</v>
       </c>
       <c r="J3" t="n">
-        <v>4.3199</v>
+        <v>3.7385</v>
       </c>
       <c r="K3" t="n">
         <v>40</v>
@@ -575,7 +575,7 @@
         <v>102</v>
       </c>
       <c r="M3" t="n">
-        <v>5.5591</v>
+        <v>5.1951</v>
       </c>
       <c r="N3" t="n">
         <v>142</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.1276</v>
+        <v>4.4954</v>
       </c>
       <c r="C4" t="n">
-        <v>1.0073</v>
+        <v>0.8831</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5989</v>
+        <v>1.3914</v>
       </c>
       <c r="E4" t="n">
-        <v>5.1276</v>
+        <v>4.4954</v>
       </c>
       <c r="F4" t="n">
-        <v>3.4439</v>
+        <v>3.0647</v>
       </c>
       <c r="G4" t="n">
-        <v>1.6837</v>
+        <v>1.4307</v>
       </c>
       <c r="H4" t="n">
-        <v>3.4439</v>
+        <v>5.3116</v>
       </c>
       <c r="I4" t="n">
-        <v>2.7913</v>
+        <v>2.7618</v>
       </c>
       <c r="J4" t="n">
-        <v>1.6837</v>
+        <v>1.4307</v>
       </c>
       <c r="K4" t="n">
         <v>126</v>
@@ -621,7 +621,7 @@
         <v>91</v>
       </c>
       <c r="M4" t="n">
-        <v>4.475</v>
+        <v>4.1925</v>
       </c>
       <c r="N4" t="n">
         <v>217</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.3283</v>
+        <v>4.4927</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8502999999999999</v>
+        <v>0.8826000000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2805</v>
+        <v>1.3902</v>
       </c>
       <c r="E5" t="n">
-        <v>4.3283</v>
+        <v>4.4927</v>
       </c>
       <c r="F5" t="n">
-        <v>2.3343</v>
+        <v>2.6334</v>
       </c>
       <c r="G5" t="n">
-        <v>1.994</v>
+        <v>1.8593</v>
       </c>
       <c r="H5" t="n">
-        <v>2.3343</v>
+        <v>3.7921</v>
       </c>
       <c r="I5" t="n">
-        <v>1.892</v>
+        <v>1.9717</v>
       </c>
       <c r="J5" t="n">
-        <v>1.994</v>
+        <v>1.8593</v>
       </c>
       <c r="K5" t="n">
         <v>40</v>
@@ -667,7 +667,7 @@
         <v>102</v>
       </c>
       <c r="M5" t="n">
-        <v>3.886</v>
+        <v>3.831</v>
       </c>
       <c r="N5" t="n">
         <v>142</v>
@@ -676,139 +676,139 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>n0thing</t>
+          <t>fer</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.7402</v>
+        <v>3.9451</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7348</v>
+        <v>0.775</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0462</v>
+        <v>1.143</v>
       </c>
       <c r="E6" t="n">
-        <v>3.7402</v>
+        <v>3.9451</v>
       </c>
       <c r="F6" t="n">
-        <v>3.3289</v>
+        <v>2.7124</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4113</v>
+        <v>1.2327</v>
       </c>
       <c r="H6" t="n">
-        <v>3.3289</v>
+        <v>4.0704</v>
       </c>
       <c r="I6" t="n">
-        <v>2.6982</v>
+        <v>2.1164</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4113</v>
+        <v>1.2327</v>
       </c>
       <c r="K6" t="n">
-        <v>126</v>
+        <v>40</v>
       </c>
       <c r="L6" t="n">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="M6" t="n">
-        <v>3.1095</v>
+        <v>3.3491</v>
       </c>
       <c r="N6" t="n">
-        <v>217</v>
+        <v>142</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>n0thing</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.5597</v>
+        <v>3.5478</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6993</v>
+        <v>0.697</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9743000000000001</v>
+        <v>0.9636</v>
       </c>
       <c r="E7" t="n">
-        <v>3.5597</v>
+        <v>3.5478</v>
       </c>
       <c r="F7" t="n">
-        <v>3.6772</v>
+        <v>3.0449</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.1175</v>
+        <v>0.5029</v>
       </c>
       <c r="H7" t="n">
-        <v>3.6772</v>
+        <v>5.2419</v>
       </c>
       <c r="I7" t="n">
-        <v>2.9805</v>
+        <v>2.7256</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.1175</v>
+        <v>0.5029</v>
       </c>
       <c r="K7" t="n">
-        <v>97</v>
+        <v>126</v>
       </c>
       <c r="L7" t="n">
-        <v>52</v>
+        <v>91</v>
       </c>
       <c r="M7" t="n">
-        <v>2.863</v>
+        <v>3.2285</v>
       </c>
       <c r="N7" t="n">
-        <v>149</v>
+        <v>217</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>fer</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.5498</v>
+        <v>3.4659</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6974</v>
+        <v>0.6808999999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9703000000000001</v>
+        <v>0.9267</v>
       </c>
       <c r="E8" t="n">
-        <v>3.5498</v>
+        <v>3.4659</v>
       </c>
       <c r="F8" t="n">
-        <v>2.5346</v>
+        <v>3.4158</v>
       </c>
       <c r="G8" t="n">
-        <v>1.0152</v>
+        <v>0.0501</v>
       </c>
       <c r="H8" t="n">
-        <v>2.5346</v>
+        <v>6.5488</v>
       </c>
       <c r="I8" t="n">
-        <v>2.0544</v>
+        <v>3.4051</v>
       </c>
       <c r="J8" t="n">
-        <v>1.0152</v>
+        <v>0.0501</v>
       </c>
       <c r="K8" t="n">
-        <v>40</v>
+        <v>97</v>
       </c>
       <c r="L8" t="n">
-        <v>102</v>
+        <v>52</v>
       </c>
       <c r="M8" t="n">
-        <v>3.0696</v>
+        <v>3.4552</v>
       </c>
       <c r="N8" t="n">
-        <v>142</v>
+        <v>149</v>
       </c>
     </row>
     <row r="9">
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.1652</v>
+        <v>3.0143</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6218</v>
+        <v>0.5921999999999999</v>
       </c>
       <c r="D9" t="n">
-        <v>0.8171</v>
+        <v>0.7228</v>
       </c>
       <c r="E9" t="n">
-        <v>3.1652</v>
+        <v>3.0143</v>
       </c>
       <c r="F9" t="n">
-        <v>4.0386</v>
+        <v>3.5857</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.8734</v>
+        <v>-0.5714</v>
       </c>
       <c r="H9" t="n">
-        <v>4.0386</v>
+        <v>7.1474</v>
       </c>
       <c r="I9" t="n">
-        <v>3.2734</v>
+        <v>3.7163</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.8734</v>
+        <v>-0.5714</v>
       </c>
       <c r="K9" t="n">
         <v>97</v>
@@ -851,7 +851,7 @@
         <v>52</v>
       </c>
       <c r="M9" t="n">
-        <v>2.4</v>
+        <v>3.1449</v>
       </c>
       <c r="N9" t="n">
         <v>149</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.6272</v>
+        <v>2.9772</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5161</v>
+        <v>0.5849</v>
       </c>
       <c r="D10" t="n">
-        <v>0.6028</v>
+        <v>0.706</v>
       </c>
       <c r="E10" t="n">
-        <v>2.6272</v>
+        <v>2.9772</v>
       </c>
       <c r="F10" t="n">
-        <v>2.3224</v>
+        <v>2.5608</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3048</v>
+        <v>0.4164</v>
       </c>
       <c r="H10" t="n">
-        <v>2.3224</v>
+        <v>3.5365</v>
       </c>
       <c r="I10" t="n">
-        <v>1.8824</v>
+        <v>1.8388</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3048</v>
+        <v>0.4164</v>
       </c>
       <c r="K10" t="n">
         <v>47</v>
@@ -897,7 +897,7 @@
         <v>141</v>
       </c>
       <c r="M10" t="n">
-        <v>2.1872</v>
+        <v>2.2552</v>
       </c>
       <c r="N10" t="n">
         <v>188</v>
@@ -906,81 +906,81 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Hiko</t>
+          <t>Skadoodle</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.3813</v>
+        <v>2.9032</v>
       </c>
       <c r="C11" t="n">
-        <v>0.4678</v>
+        <v>0.5703</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5048</v>
+        <v>0.6726</v>
       </c>
       <c r="E11" t="n">
-        <v>2.3813</v>
+        <v>2.9032</v>
       </c>
       <c r="F11" t="n">
-        <v>2.5664</v>
+        <v>2.4169</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.1851</v>
+        <v>0.4863</v>
       </c>
       <c r="H11" t="n">
-        <v>2.5664</v>
+        <v>3.0292</v>
       </c>
       <c r="I11" t="n">
-        <v>2.0802</v>
+        <v>1.5751</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.1851</v>
+        <v>0.4863</v>
       </c>
       <c r="K11" t="n">
-        <v>97</v>
+        <v>126</v>
       </c>
       <c r="L11" t="n">
-        <v>52</v>
+        <v>91</v>
       </c>
       <c r="M11" t="n">
-        <v>1.8951</v>
+        <v>2.0614</v>
       </c>
       <c r="N11" t="n">
-        <v>149</v>
+        <v>217</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Skadoodle</t>
+          <t>shroud</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.2137</v>
+        <v>2.8838</v>
       </c>
       <c r="C12" t="n">
-        <v>0.4349</v>
+        <v>0.5665</v>
       </c>
       <c r="D12" t="n">
-        <v>0.438</v>
+        <v>0.6639</v>
       </c>
       <c r="E12" t="n">
-        <v>2.2137</v>
+        <v>2.8838</v>
       </c>
       <c r="F12" t="n">
-        <v>1.801</v>
+        <v>2.5499</v>
       </c>
       <c r="G12" t="n">
-        <v>0.4127</v>
+        <v>0.3339</v>
       </c>
       <c r="H12" t="n">
-        <v>1.801</v>
+        <v>3.498</v>
       </c>
       <c r="I12" t="n">
-        <v>1.4598</v>
+        <v>1.8188</v>
       </c>
       <c r="J12" t="n">
-        <v>0.4127</v>
+        <v>0.3339</v>
       </c>
       <c r="K12" t="n">
         <v>126</v>
@@ -989,7 +989,7 @@
         <v>91</v>
       </c>
       <c r="M12" t="n">
-        <v>1.8725</v>
+        <v>2.1527</v>
       </c>
       <c r="N12" t="n">
         <v>217</v>
@@ -998,127 +998,127 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>shroud</t>
+          <t>felps</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.0431</v>
+        <v>2.7542</v>
       </c>
       <c r="C13" t="n">
-        <v>0.4014</v>
+        <v>0.5411</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3701</v>
+        <v>0.6054</v>
       </c>
       <c r="E13" t="n">
-        <v>2.0431</v>
+        <v>2.7542</v>
       </c>
       <c r="F13" t="n">
-        <v>1.887</v>
+        <v>2.2395</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1561</v>
+        <v>0.5147</v>
       </c>
       <c r="H13" t="n">
-        <v>1.887</v>
+        <v>2.4044</v>
       </c>
       <c r="I13" t="n">
-        <v>1.5295</v>
+        <v>1.2502</v>
       </c>
       <c r="J13" t="n">
-        <v>0.1561</v>
+        <v>0.5147</v>
       </c>
       <c r="K13" t="n">
-        <v>126</v>
+        <v>47</v>
       </c>
       <c r="L13" t="n">
-        <v>91</v>
+        <v>141</v>
       </c>
       <c r="M13" t="n">
-        <v>1.6856</v>
+        <v>1.7649</v>
       </c>
       <c r="N13" t="n">
-        <v>217</v>
+        <v>188</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LUCAS1</t>
+          <t>Hiko</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.8753</v>
+        <v>2.7412</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3684</v>
+        <v>0.5385</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3032</v>
+        <v>0.5995</v>
       </c>
       <c r="E14" t="n">
-        <v>1.8753</v>
+        <v>2.7412</v>
       </c>
       <c r="F14" t="n">
-        <v>2.2721</v>
+        <v>2.787</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.3968</v>
+        <v>-0.0458</v>
       </c>
       <c r="H14" t="n">
-        <v>2.2721</v>
+        <v>4.3333</v>
       </c>
       <c r="I14" t="n">
-        <v>1.8416</v>
+        <v>2.2531</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.3968</v>
+        <v>-0.0458</v>
       </c>
       <c r="K14" t="n">
-        <v>47</v>
+        <v>97</v>
       </c>
       <c r="L14" t="n">
-        <v>141</v>
+        <v>52</v>
       </c>
       <c r="M14" t="n">
-        <v>1.4448</v>
+        <v>2.2073</v>
       </c>
       <c r="N14" t="n">
-        <v>188</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>felps</t>
+          <t>LUCAS1</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.6887</v>
+        <v>2.3805</v>
       </c>
       <c r="C15" t="n">
-        <v>0.3317</v>
+        <v>0.4676</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2289</v>
+        <v>0.4367</v>
       </c>
       <c r="E15" t="n">
-        <v>1.6887</v>
+        <v>2.3805</v>
       </c>
       <c r="F15" t="n">
-        <v>1.4001</v>
+        <v>2.5448</v>
       </c>
       <c r="G15" t="n">
-        <v>0.2886</v>
+        <v>-0.1643</v>
       </c>
       <c r="H15" t="n">
-        <v>1.4001</v>
+        <v>3.4801</v>
       </c>
       <c r="I15" t="n">
-        <v>1.1348</v>
+        <v>1.8095</v>
       </c>
       <c r="J15" t="n">
-        <v>0.2886</v>
+        <v>-0.1643</v>
       </c>
       <c r="K15" t="n">
         <v>47</v>
@@ -1127,7 +1127,7 @@
         <v>141</v>
       </c>
       <c r="M15" t="n">
-        <v>1.4234</v>
+        <v>1.6452</v>
       </c>
       <c r="N15" t="n">
         <v>188</v>
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.484</v>
+        <v>2.1918</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2915</v>
+        <v>0.4306</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1473</v>
+        <v>0.3515</v>
       </c>
       <c r="E16" t="n">
-        <v>1.484</v>
+        <v>2.1918</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5115</v>
+        <v>0.9108000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9725</v>
+        <v>1.281</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5115</v>
+        <v>0.9108000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4146</v>
+        <v>0.4736</v>
       </c>
       <c r="J16" t="n">
-        <v>0.9725</v>
+        <v>1.281</v>
       </c>
       <c r="K16" t="n">
         <v>40</v>
@@ -1173,7 +1173,7 @@
         <v>102</v>
       </c>
       <c r="M16" t="n">
-        <v>1.3871</v>
+        <v>1.7546</v>
       </c>
       <c r="N16" t="n">
         <v>142</v>
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.3779</v>
+        <v>1.9872</v>
       </c>
       <c r="C17" t="n">
-        <v>0.2707</v>
+        <v>0.3904</v>
       </c>
       <c r="D17" t="n">
-        <v>0.105</v>
+        <v>0.2591</v>
       </c>
       <c r="E17" t="n">
-        <v>1.3779</v>
+        <v>1.9872</v>
       </c>
       <c r="F17" t="n">
-        <v>2.1445</v>
+        <v>2.5374</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.7665999999999999</v>
+        <v>-0.5502</v>
       </c>
       <c r="H17" t="n">
-        <v>2.1445</v>
+        <v>3.4537</v>
       </c>
       <c r="I17" t="n">
-        <v>1.7382</v>
+        <v>1.7958</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.7665999999999999</v>
+        <v>-0.5502</v>
       </c>
       <c r="K17" t="n">
         <v>97</v>
@@ -1219,7 +1219,7 @@
         <v>52</v>
       </c>
       <c r="M17" t="n">
-        <v>0.9716</v>
+        <v>1.2456</v>
       </c>
       <c r="N17" t="n">
         <v>149</v>
@@ -1228,47 +1228,47 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>mitch</t>
+          <t>jdm64</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.0632</v>
+        <v>1.7083</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2089</v>
+        <v>0.3356</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0203</v>
+        <v>0.1332</v>
       </c>
       <c r="E18" t="n">
-        <v>1.0632</v>
+        <v>1.7083</v>
       </c>
       <c r="F18" t="n">
-        <v>1.0632</v>
+        <v>1.7083</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1.0632</v>
+        <v>1.7083</v>
       </c>
       <c r="I18" t="n">
-        <v>1.0632</v>
+        <v>1.7786</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.0632</v>
+        <v>1.7786</v>
       </c>
       <c r="N18" t="n">
-        <v>157</v>
+        <v>168</v>
       </c>
     </row>
     <row r="19">
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9838</v>
+        <v>1.3168</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1933</v>
+        <v>0.2587</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.052</v>
+        <v>-0.0435</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9838</v>
+        <v>1.3168</v>
       </c>
       <c r="F19" t="n">
-        <v>1.1843</v>
+        <v>1.4855</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.2005</v>
+        <v>-0.1687</v>
       </c>
       <c r="H19" t="n">
-        <v>1.1843</v>
+        <v>1.4855</v>
       </c>
       <c r="I19" t="n">
-        <v>0.9599</v>
+        <v>0.7724</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.2005</v>
+        <v>-0.1687</v>
       </c>
       <c r="K19" t="n">
         <v>47</v>
@@ -1311,7 +1311,7 @@
         <v>141</v>
       </c>
       <c r="M19" t="n">
-        <v>0.7594</v>
+        <v>0.6037</v>
       </c>
       <c r="N19" t="n">
         <v>188</v>
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9787</v>
+        <v>1.1656</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1923</v>
+        <v>0.229</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.054</v>
+        <v>-0.1118</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9787</v>
+        <v>1.1656</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9787</v>
+        <v>1.1656</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9787</v>
+        <v>1.1656</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9787</v>
+        <v>1.1656</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.9787</v>
+        <v>1.1656</v>
       </c>
       <c r="N20" t="n">
         <v>107</v>
@@ -1366,124 +1366,124 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>reltuC</t>
+          <t>Relyks</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.648</v>
+        <v>1.1333</v>
       </c>
       <c r="C21" t="n">
-        <v>0.1273</v>
+        <v>0.2226</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1857</v>
+        <v>-0.1264</v>
       </c>
       <c r="E21" t="n">
-        <v>0.648</v>
+        <v>1.1333</v>
       </c>
       <c r="F21" t="n">
-        <v>0.648</v>
+        <v>1.1333</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.648</v>
+        <v>1.1333</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6535</v>
+        <v>1.1333</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.6535</v>
+        <v>1.1333</v>
       </c>
       <c r="N21" t="n">
-        <v>168</v>
+        <v>157</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>tarik</t>
+          <t>mitch</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.501</v>
+        <v>1.1152</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0984</v>
+        <v>0.2191</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.2443</v>
+        <v>-0.1346</v>
       </c>
       <c r="E22" t="n">
-        <v>0.501</v>
+        <v>1.1152</v>
       </c>
       <c r="F22" t="n">
-        <v>0.501</v>
+        <v>1.1152</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.501</v>
+        <v>1.1152</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5052</v>
+        <v>1.1152</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.5052</v>
+        <v>1.1152</v>
       </c>
       <c r="N22" t="n">
-        <v>168</v>
+        <v>157</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>jdm64</t>
+          <t>tarik</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.4637</v>
+        <v>0.9175</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0911</v>
+        <v>0.1802</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2592</v>
+        <v>-0.2238</v>
       </c>
       <c r="E23" t="n">
-        <v>0.4637</v>
+        <v>0.9175</v>
       </c>
       <c r="F23" t="n">
-        <v>0.4637</v>
+        <v>0.9175</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.4637</v>
+        <v>0.9175</v>
       </c>
       <c r="I23" t="n">
-        <v>0.4676</v>
+        <v>0.9552</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.4676</v>
+        <v>0.9552</v>
       </c>
       <c r="N23" t="n">
         <v>168</v>
@@ -1504,93 +1504,93 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Relyks</t>
+          <t>reltuC</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.249</v>
+        <v>0.8449</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0489</v>
+        <v>0.166</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.3447</v>
+        <v>-0.2566</v>
       </c>
       <c r="E24" t="n">
-        <v>0.249</v>
+        <v>0.8449</v>
       </c>
       <c r="F24" t="n">
-        <v>0.249</v>
+        <v>0.8449</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.249</v>
+        <v>0.8449</v>
       </c>
       <c r="I24" t="n">
-        <v>0.249</v>
+        <v>0.8796</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.249</v>
+        <v>0.8796</v>
       </c>
       <c r="N24" t="n">
-        <v>157</v>
+        <v>168</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ptr</t>
+          <t>adreN</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.1832</v>
+        <v>0.6131</v>
       </c>
       <c r="C25" t="n">
-        <v>0.036</v>
+        <v>0.1204</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3709</v>
+        <v>-0.3612</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1832</v>
+        <v>0.6131</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1832</v>
+        <v>0.8105</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>-0.1974</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1832</v>
+        <v>0.8105</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1832</v>
+        <v>0.4214</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>-0.1974</v>
       </c>
       <c r="K25" t="n">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="M25" t="n">
-        <v>0.1832</v>
+        <v>0.224</v>
       </c>
       <c r="N25" t="n">
-        <v>107</v>
+        <v>149</v>
       </c>
     </row>
     <row r="26">
@@ -1600,31 +1600,31 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.0207</v>
+        <v>0.5653</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0041</v>
+        <v>0.1111</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4357</v>
+        <v>-0.3828</v>
       </c>
       <c r="E26" t="n">
-        <v>0.0207</v>
+        <v>0.5653</v>
       </c>
       <c r="F26" t="n">
-        <v>0.1463</v>
+        <v>0.5131</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.1256</v>
+        <v>0.0522</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1463</v>
+        <v>0.5131</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1186</v>
+        <v>0.2668</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.1256</v>
+        <v>0.0522</v>
       </c>
       <c r="K26" t="n">
         <v>47</v>
@@ -1633,7 +1633,7 @@
         <v>141</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.006999999999999992</v>
+        <v>0.319</v>
       </c>
       <c r="N26" t="n">
         <v>188</v>
@@ -1642,32 +1642,32 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>just9n</t>
+          <t>ptr</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.0382</v>
+        <v>0.2896</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.0075</v>
+        <v>0.0569</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.4591</v>
+        <v>-0.5073</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.0382</v>
+        <v>0.2896</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.0382</v>
+        <v>0.2896</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.0382</v>
+        <v>0.2896</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.0382</v>
+        <v>0.2896</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.0382</v>
+        <v>0.2896</v>
       </c>
       <c r="N27" t="n">
         <v>107</v>
@@ -1688,124 +1688,124 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>jasonR</t>
+          <t>hazed</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.1033</v>
+        <v>0.1531</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0203</v>
+        <v>0.0301</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.4851</v>
+        <v>-0.5689</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.1033</v>
+        <v>0.1531</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.1033</v>
+        <v>0.1531</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.1033</v>
+        <v>0.1531</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.1033</v>
+        <v>0.1594</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>82</v>
+        <v>168</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.1033</v>
+        <v>0.1594</v>
       </c>
       <c r="N28" t="n">
-        <v>82</v>
+        <v>168</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>adreN</t>
+          <t>Nifty</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.104</v>
+        <v>0.1448</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0204</v>
+        <v>0.0284</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.4853</v>
+        <v>-0.5726</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.104</v>
+        <v>0.1448</v>
       </c>
       <c r="F29" t="n">
-        <v>0.1171</v>
+        <v>0.1448</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.2211</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1171</v>
+        <v>0.1448</v>
       </c>
       <c r="I29" t="n">
-        <v>0.0949</v>
+        <v>0.1448</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.2211</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>97</v>
+        <v>157</v>
       </c>
       <c r="L29" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.1262</v>
+        <v>0.1448</v>
       </c>
       <c r="N29" t="n">
-        <v>149</v>
+        <v>157</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>freakazoid</t>
+          <t>DAVEY</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.1456</v>
+        <v>0.113</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0286</v>
+        <v>0.0222</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.5019</v>
+        <v>-0.587</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.1456</v>
+        <v>0.113</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.1456</v>
+        <v>0.113</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.1456</v>
+        <v>0.113</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1456</v>
+        <v>0.113</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.1456</v>
+        <v>0.113</v>
       </c>
       <c r="N30" t="n">
         <v>82</v>
@@ -1826,139 +1826,139 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>hazed</t>
+          <t>jasonR</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.1471</v>
+        <v>0.0341</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0289</v>
+        <v>0.0067</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.5024999999999999</v>
+        <v>-0.6226</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.1471</v>
+        <v>0.0341</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.1471</v>
+        <v>0.0341</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.1471</v>
+        <v>0.0341</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.1483</v>
+        <v>0.0341</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>168</v>
+        <v>82</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.1483</v>
+        <v>0.0341</v>
       </c>
       <c r="N31" t="n">
-        <v>168</v>
+        <v>82</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>DAVEY</t>
+          <t>just9n</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.1943</v>
+        <v>0.0321</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0382</v>
+        <v>0.0063</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.5213</v>
+        <v>-0.6235000000000001</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.1943</v>
+        <v>0.0321</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.1943</v>
+        <v>0.0321</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.1943</v>
+        <v>0.0321</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.1943</v>
+        <v>0.0321</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>82</v>
+        <v>107</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.1943</v>
+        <v>0.0321</v>
       </c>
       <c r="N32" t="n">
-        <v>82</v>
+        <v>107</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Nifty</t>
+          <t>freakazoid</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.3368</v>
+        <v>-0.1007</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.06619999999999999</v>
+        <v>-0.0198</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.5780999999999999</v>
+        <v>-0.6835</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.3368</v>
+        <v>-0.1007</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.3368</v>
+        <v>-0.1007</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.3368</v>
+        <v>-0.1007</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.3368</v>
+        <v>-0.1007</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>157</v>
+        <v>82</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.3368</v>
+        <v>-0.1007</v>
       </c>
       <c r="N33" t="n">
-        <v>157</v>
+        <v>82</v>
       </c>
     </row>
     <row r="34">
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.6705</v>
+        <v>-0.1916</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.1317</v>
+        <v>-0.0376</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.711</v>
+        <v>-0.7245</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.6705</v>
+        <v>-0.1916</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.6705</v>
+        <v>-0.1916</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.6705</v>
+        <v>-0.1916</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.6705</v>
+        <v>-0.1916</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.6705</v>
+        <v>-0.1916</v>
       </c>
       <c r="N34" t="n">
         <v>107</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.8627</v>
+        <v>-0.4653</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.1695</v>
+        <v>-0.0914</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.7876</v>
+        <v>-0.8481</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.8627</v>
+        <v>-0.4653</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.8627</v>
+        <v>-0.4653</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.8627</v>
+        <v>-0.4653</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.8627</v>
+        <v>-0.4653</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.8627</v>
+        <v>-0.4653</v>
       </c>
       <c r="N35" t="n">
         <v>157</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.1761</v>
+        <v>-0.7634</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.231</v>
+        <v>-0.15</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9125</v>
+        <v>-0.9827</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.1761</v>
+        <v>-0.7634</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.1761</v>
+        <v>-0.7634</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.1761</v>
+        <v>-0.7634</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.1761</v>
+        <v>-0.7634</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.1761</v>
+        <v>-0.7634</v>
       </c>
       <c r="N36" t="n">
         <v>82</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.5244</v>
+        <v>-0.9998</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.2995</v>
+        <v>-0.1964</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0512</v>
+        <v>-1.0894</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.5244</v>
+        <v>-0.9998</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.5244</v>
+        <v>-0.9998</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.5244</v>
+        <v>-0.9998</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.5244</v>
+        <v>-0.9998</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.5244</v>
+        <v>-0.9998</v>
       </c>
       <c r="N37" t="n">
         <v>107</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.5519</v>
+        <v>-1.0149</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.3049</v>
+        <v>-0.1994</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0622</v>
+        <v>-1.0962</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.5519</v>
+        <v>-1.0149</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.5519</v>
+        <v>-1.0149</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.5519</v>
+        <v>-1.0149</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.5519</v>
+        <v>-1.0149</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.5519</v>
+        <v>-1.0149</v>
       </c>
       <c r="N38" t="n">
         <v>157</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.5977</v>
+        <v>-1.144</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.3139</v>
+        <v>-0.2247</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.0804</v>
+        <v>-1.1545</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.5977</v>
+        <v>-1.144</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.5977</v>
+        <v>-1.144</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.5977</v>
+        <v>-1.144</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.5977</v>
+        <v>-1.144</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.5977</v>
+        <v>-1.144</v>
       </c>
       <c r="N39" t="n">
         <v>82</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.9212</v>
+        <v>-1.3329</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.3774</v>
+        <v>-0.2618</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.2093</v>
+        <v>-1.2398</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.9212</v>
+        <v>-1.3329</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.9212</v>
+        <v>-1.3329</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.9212</v>
+        <v>-1.3329</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.9374</v>
+        <v>-1.3877</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.9374</v>
+        <v>-1.3877</v>
       </c>
       <c r="N40" t="n">
         <v>168</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.5988</v>
+        <v>-1.9545</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.5105</v>
+        <v>-0.384</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.4793</v>
+        <v>-1.5204</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.5988</v>
+        <v>-1.9545</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.5988</v>
+        <v>-1.1289</v>
       </c>
       <c r="G41" t="n">
-        <v>-1</v>
+        <v>-0.8256</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.5988</v>
+        <v>-1.1289</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.2959</v>
+        <v>-0.587</v>
       </c>
       <c r="J41" t="n">
-        <v>-1</v>
+        <v>-0.8256</v>
       </c>
       <c r="K41" t="n">
         <v>126</v>
@@ -2323,7 +2323,7 @@
         <v>91</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.2959</v>
+        <v>-1.4126</v>
       </c>
       <c r="N41" t="n">
         <v>217</v>
@@ -2429,10 +2429,10 @@
         <v>1.01</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1592</v>
+        <v>0.1321</v>
       </c>
       <c r="J2" t="n">
-        <v>3.98</v>
+        <v>3.3025</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>0.87</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1408</v>
+        <v>-0.1313</v>
       </c>
       <c r="J3" t="n">
-        <v>-3.52</v>
+        <v>-3.2825</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.67</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4866</v>
+        <v>-0.3289</v>
       </c>
       <c r="J4" t="n">
-        <v>-12.165</v>
+        <v>-8.2225</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.58</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.6152</v>
+        <v>-0.4131</v>
       </c>
       <c r="J5" t="n">
-        <v>-15.38</v>
+        <v>-10.3275</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.53</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6815</v>
+        <v>-0.4598</v>
       </c>
       <c r="J6" t="n">
-        <v>-17.0375</v>
+        <v>-11.495</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.51</v>
       </c>
       <c r="I7" t="n">
-        <v>1.1976</v>
+        <v>1.1339</v>
       </c>
       <c r="J7" t="n">
-        <v>29.94</v>
+        <v>28.3475</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.46</v>
       </c>
       <c r="I8" t="n">
-        <v>1.0954</v>
+        <v>1.0713</v>
       </c>
       <c r="J8" t="n">
-        <v>27.385</v>
+        <v>26.7825</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.3</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7286</v>
+        <v>0.7738</v>
       </c>
       <c r="J9" t="n">
-        <v>18.215</v>
+        <v>19.345</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.19</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4347</v>
+        <v>0.5185999999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>10.8675</v>
+        <v>12.965</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1535</v>
+        <v>-0.0709</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.8375</v>
+        <v>-1.7725</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.09</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2734</v>
+        <v>0.2813</v>
       </c>
       <c r="J12" t="n">
-        <v>6.835</v>
+        <v>7.0325</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>0.98</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0191</v>
+        <v>-0.0155</v>
       </c>
       <c r="J13" t="n">
-        <v>0.4775</v>
+        <v>-0.3875</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.06469999999999999</v>
+        <v>-0.0702</v>
       </c>
       <c r="J14" t="n">
-        <v>-1.6175</v>
+        <v>-1.755</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.63</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.5777</v>
+        <v>-0.382</v>
       </c>
       <c r="J15" t="n">
-        <v>-14.4425</v>
+        <v>-9.550000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.55</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.6801</v>
+        <v>-0.4564</v>
       </c>
       <c r="J16" t="n">
-        <v>-17.0025</v>
+        <v>-11.41</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.57</v>
       </c>
       <c r="I17" t="n">
-        <v>1.3216</v>
+        <v>1.2108</v>
       </c>
       <c r="J17" t="n">
-        <v>33.04</v>
+        <v>30.27</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.35</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8614000000000001</v>
+        <v>0.8858</v>
       </c>
       <c r="J18" t="n">
-        <v>21.535</v>
+        <v>22.145</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.27</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6482</v>
+        <v>0.7098</v>
       </c>
       <c r="J19" t="n">
-        <v>16.205</v>
+        <v>17.745</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.26</v>
       </c>
       <c r="I20" t="n">
-        <v>0.6207</v>
+        <v>0.6874</v>
       </c>
       <c r="J20" t="n">
-        <v>15.5175</v>
+        <v>17.185</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.95</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.3525</v>
+        <v>-0.2699</v>
       </c>
       <c r="J21" t="n">
-        <v>-8.8125</v>
+        <v>-6.7475</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.85</v>
       </c>
       <c r="I22" t="n">
-        <v>1.7576</v>
+        <v>1.2483</v>
       </c>
       <c r="J22" t="n">
-        <v>38.6672</v>
+        <v>27.4626</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.61</v>
       </c>
       <c r="I23" t="n">
-        <v>1.3538</v>
+        <v>0.9661999999999999</v>
       </c>
       <c r="J23" t="n">
-        <v>29.7836</v>
+        <v>21.2564</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.37</v>
       </c>
       <c r="I24" t="n">
-        <v>0.8299</v>
+        <v>0.6747</v>
       </c>
       <c r="J24" t="n">
-        <v>18.2578</v>
+        <v>14.8434</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>1.05</v>
       </c>
       <c r="I25" t="n">
-        <v>0.0244</v>
+        <v>0.1107</v>
       </c>
       <c r="J25" t="n">
-        <v>0.5368000000000001</v>
+        <v>2.4354</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>1.01</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.119</v>
+        <v>-0.0354</v>
       </c>
       <c r="J26" t="n">
-        <v>-2.618</v>
+        <v>-0.7788</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.039</v>
+        <v>-0.0587</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.858</v>
+        <v>-1.2914</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>0.88</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.1467</v>
+        <v>-0.1302</v>
       </c>
       <c r="J28" t="n">
-        <v>-3.2274</v>
+        <v>-2.8644</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.73</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.416</v>
+        <v>-0.2793</v>
       </c>
       <c r="J29" t="n">
-        <v>-9.151999999999999</v>
+        <v>-6.1446</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.71</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.447</v>
+        <v>-0.2982</v>
       </c>
       <c r="J30" t="n">
-        <v>-9.834</v>
+        <v>-6.5604</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.64</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.5481</v>
+        <v>-0.3643</v>
       </c>
       <c r="J31" t="n">
-        <v>-12.0582</v>
+        <v>-8.0146</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.54</v>
       </c>
       <c r="I32" t="n">
-        <v>1.2839</v>
+        <v>0.9098000000000001</v>
       </c>
       <c r="J32" t="n">
-        <v>38.517</v>
+        <v>27.294</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.26</v>
       </c>
       <c r="I33" t="n">
-        <v>0.6694</v>
+        <v>0.5457</v>
       </c>
       <c r="J33" t="n">
-        <v>20.082</v>
+        <v>16.371</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.23</v>
       </c>
       <c r="I34" t="n">
-        <v>0.5762</v>
+        <v>0.5056</v>
       </c>
       <c r="J34" t="n">
-        <v>17.286</v>
+        <v>15.168</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.11</v>
       </c>
       <c r="I35" t="n">
-        <v>0.2479</v>
+        <v>0.3206</v>
       </c>
       <c r="J35" t="n">
-        <v>7.437</v>
+        <v>9.618</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>1.04</v>
       </c>
       <c r="I36" t="n">
-        <v>0.0361</v>
+        <v>0.1104</v>
       </c>
       <c r="J36" t="n">
-        <v>1.083</v>
+        <v>3.312</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.14</v>
       </c>
       <c r="I37" t="n">
-        <v>0.3295</v>
+        <v>0.3483</v>
       </c>
       <c r="J37" t="n">
-        <v>9.885</v>
+        <v>10.449</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.08</v>
       </c>
       <c r="I38" t="n">
-        <v>0.2309</v>
+        <v>0.2335</v>
       </c>
       <c r="J38" t="n">
-        <v>6.927</v>
+        <v>7.005</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.95</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.07439999999999999</v>
+        <v>-0.0672</v>
       </c>
       <c r="J39" t="n">
-        <v>-2.232</v>
+        <v>-2.016</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.82</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.3253</v>
+        <v>-0.2071</v>
       </c>
       <c r="J40" t="n">
-        <v>-9.759</v>
+        <v>-6.213</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.52</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.7276</v>
+        <v>-0.4915</v>
       </c>
       <c r="J41" t="n">
-        <v>-21.828</v>
+        <v>-14.745</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.29</v>
       </c>
       <c r="I42" t="n">
-        <v>0.5352</v>
+        <v>0.423</v>
       </c>
       <c r="J42" t="n">
-        <v>15.5208</v>
+        <v>12.267</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>0.87</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.2499</v>
+        <v>-0.1578</v>
       </c>
       <c r="J43" t="n">
-        <v>-7.2471</v>
+        <v>-4.5762</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.86</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.267</v>
+        <v>-0.1682</v>
       </c>
       <c r="J44" t="n">
-        <v>-7.743</v>
+        <v>-4.8778</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.83</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.3159</v>
+        <v>-0.1991</v>
       </c>
       <c r="J45" t="n">
-        <v>-9.161099999999999</v>
+        <v>-5.7739</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.75</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.4351</v>
+        <v>-0.2786</v>
       </c>
       <c r="J46" t="n">
-        <v>-12.6179</v>
+        <v>-8.0794</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.47</v>
       </c>
       <c r="I47" t="n">
-        <v>0.6739000000000001</v>
+        <v>0.4879</v>
       </c>
       <c r="J47" t="n">
-        <v>19.5431</v>
+        <v>14.1491</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.35</v>
       </c>
       <c r="I48" t="n">
-        <v>0.5276999999999999</v>
+        <v>0.4083</v>
       </c>
       <c r="J48" t="n">
-        <v>15.3033</v>
+        <v>11.8407</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.15</v>
       </c>
       <c r="I49" t="n">
-        <v>0.2259</v>
+        <v>0.222</v>
       </c>
       <c r="J49" t="n">
-        <v>6.5511</v>
+        <v>6.438</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>1.09</v>
       </c>
       <c r="I50" t="n">
-        <v>0.1253</v>
+        <v>0.1404</v>
       </c>
       <c r="J50" t="n">
-        <v>3.6337</v>
+        <v>4.0716</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.83</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.3746</v>
+        <v>-0.2275</v>
       </c>
       <c r="J51" t="n">
-        <v>-10.8634</v>
+        <v>-6.5975</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.22</v>
       </c>
       <c r="I52" t="n">
-        <v>0.6646</v>
+        <v>0.5125</v>
       </c>
       <c r="J52" t="n">
-        <v>23.261</v>
+        <v>17.9375</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.18</v>
       </c>
       <c r="I53" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.4531</v>
       </c>
       <c r="J53" t="n">
-        <v>19.67</v>
+        <v>15.8585</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.09</v>
       </c>
       <c r="I54" t="n">
-        <v>0.292</v>
+        <v>0.2973</v>
       </c>
       <c r="J54" t="n">
-        <v>10.22</v>
+        <v>10.4055</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.01</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.0131</v>
+        <v>0.0349</v>
       </c>
       <c r="J55" t="n">
-        <v>-0.4585</v>
+        <v>1.2215</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.3176</v>
+        <v>-0.2531</v>
       </c>
       <c r="J56" t="n">
-        <v>-11.116</v>
+        <v>-8.858499999999999</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.23</v>
       </c>
       <c r="I57" t="n">
-        <v>0.4124</v>
+        <v>0.4204</v>
       </c>
       <c r="J57" t="n">
-        <v>14.434</v>
+        <v>14.714</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.18</v>
       </c>
       <c r="I58" t="n">
-        <v>0.3403</v>
+        <v>0.3672</v>
       </c>
       <c r="J58" t="n">
-        <v>11.9105</v>
+        <v>12.852</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.05</v>
       </c>
       <c r="I59" t="n">
-        <v>0.1147</v>
+        <v>0.1326</v>
       </c>
       <c r="J59" t="n">
-        <v>4.0145</v>
+        <v>4.641</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.92</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.2053</v>
+        <v>-0.116</v>
       </c>
       <c r="J60" t="n">
-        <v>-7.1855</v>
+        <v>-4.06</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.82</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.3636</v>
+        <v>-0.2234</v>
       </c>
       <c r="J61" t="n">
-        <v>-12.726</v>
+        <v>-7.819</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.31</v>
       </c>
       <c r="I62" t="n">
-        <v>0.8323</v>
+        <v>0.6236</v>
       </c>
       <c r="J62" t="n">
-        <v>22.4721</v>
+        <v>16.8372</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.26</v>
       </c>
       <c r="I63" t="n">
-        <v>0.7138</v>
+        <v>0.5547</v>
       </c>
       <c r="J63" t="n">
-        <v>19.2726</v>
+        <v>14.9769</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.19</v>
       </c>
       <c r="I64" t="n">
-        <v>0.5306999999999999</v>
+        <v>0.4558</v>
       </c>
       <c r="J64" t="n">
-        <v>14.3289</v>
+        <v>12.3066</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.11</v>
       </c>
       <c r="I65" t="n">
-        <v>0.2817</v>
+        <v>0.3331</v>
       </c>
       <c r="J65" t="n">
-        <v>7.6059</v>
+        <v>8.9937</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.98</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.2126</v>
+        <v>-0.1371</v>
       </c>
       <c r="J66" t="n">
-        <v>-5.7402</v>
+        <v>-3.7017</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.62</v>
       </c>
       <c r="I67" t="n">
-        <v>0.8951</v>
+        <v>0.8102</v>
       </c>
       <c r="J67" t="n">
-        <v>24.1677</v>
+        <v>21.8754</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.28</v>
       </c>
       <c r="I68" t="n">
-        <v>0.4913</v>
+        <v>0.4785</v>
       </c>
       <c r="J68" t="n">
-        <v>13.2651</v>
+        <v>12.9195</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.75</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.4553</v>
+        <v>-0.2892</v>
       </c>
       <c r="J69" t="n">
-        <v>-12.2931</v>
+        <v>-7.8084</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.73</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.4822</v>
+        <v>-0.3085</v>
       </c>
       <c r="J70" t="n">
-        <v>-13.0194</v>
+        <v>-8.329499999999999</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.66</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.5729</v>
+        <v>-0.3747</v>
       </c>
       <c r="J71" t="n">
-        <v>-15.4683</v>
+        <v>-10.1169</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.91</v>
       </c>
       <c r="I72" t="n">
-        <v>1.8136</v>
+        <v>1.5489</v>
       </c>
       <c r="J72" t="n">
-        <v>34.4584</v>
+        <v>29.4291</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.81</v>
       </c>
       <c r="I73" t="n">
-        <v>1.6396</v>
+        <v>1.438</v>
       </c>
       <c r="J73" t="n">
-        <v>31.1524</v>
+        <v>27.322</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.55</v>
       </c>
       <c r="I74" t="n">
-        <v>1.1145</v>
+        <v>1.1463</v>
       </c>
       <c r="J74" t="n">
-        <v>21.1755</v>
+        <v>21.7797</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1.48</v>
       </c>
       <c r="I75" t="n">
-        <v>0.9659</v>
+        <v>1.0642</v>
       </c>
       <c r="J75" t="n">
-        <v>18.3521</v>
+        <v>20.2198</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>1.12</v>
       </c>
       <c r="I76" t="n">
-        <v>0.1744</v>
+        <v>0.2774</v>
       </c>
       <c r="J76" t="n">
-        <v>3.3136</v>
+        <v>5.2706</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>0.98</v>
       </c>
       <c r="I77" t="n">
-        <v>0.1577</v>
+        <v>0.1608</v>
       </c>
       <c r="J77" t="n">
-        <v>2.9963</v>
+        <v>3.0552</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>0.55</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.5729</v>
+        <v>-0.4113</v>
       </c>
       <c r="J78" t="n">
-        <v>-10.8851</v>
+        <v>-7.8147</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.51</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.6423</v>
+        <v>-0.4474</v>
       </c>
       <c r="J79" t="n">
-        <v>-12.2037</v>
+        <v>-8.5006</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.48</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.6884</v>
+        <v>-0.4754</v>
       </c>
       <c r="J80" t="n">
-        <v>-13.0796</v>
+        <v>-9.0326</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.27</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.9698</v>
+        <v>-0.6787</v>
       </c>
       <c r="J81" t="n">
-        <v>-18.4262</v>
+        <v>-12.8953</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.71</v>
       </c>
       <c r="I82" t="n">
-        <v>1.6131</v>
+        <v>1.3993</v>
       </c>
       <c r="J82" t="n">
-        <v>41.9406</v>
+        <v>36.3818</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.41</v>
       </c>
       <c r="I83" t="n">
-        <v>1.0276</v>
+        <v>1.0169</v>
       </c>
       <c r="J83" t="n">
-        <v>26.7176</v>
+        <v>26.4394</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.32</v>
       </c>
       <c r="I84" t="n">
-        <v>0.8282</v>
+        <v>0.8343</v>
       </c>
       <c r="J84" t="n">
-        <v>21.5332</v>
+        <v>21.6918</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.88</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.5353</v>
+        <v>-0.4649</v>
       </c>
       <c r="J85" t="n">
-        <v>-13.9178</v>
+        <v>-12.0874</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.77</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.8038</v>
+        <v>-0.7558</v>
       </c>
       <c r="J86" t="n">
-        <v>-20.8988</v>
+        <v>-19.6508</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.04</v>
       </c>
       <c r="I87" t="n">
-        <v>0.1686</v>
+        <v>0.1521</v>
       </c>
       <c r="J87" t="n">
-        <v>4.3836</v>
+        <v>3.9546</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.96</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.0388</v>
+        <v>-0.0497</v>
       </c>
       <c r="J88" t="n">
-        <v>-1.0088</v>
+        <v>-1.2922</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.85</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.2604</v>
+        <v>-0.1731</v>
       </c>
       <c r="J89" t="n">
-        <v>-6.7704</v>
+        <v>-4.5006</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.8</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.3448</v>
+        <v>-0.2231</v>
       </c>
       <c r="J90" t="n">
-        <v>-8.9648</v>
+        <v>-5.8006</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.7</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.4915</v>
+        <v>-0.3202</v>
       </c>
       <c r="J91" t="n">
-        <v>-12.779</v>
+        <v>-8.325200000000001</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.21</v>
       </c>
       <c r="I92" t="n">
-        <v>0.6624</v>
+        <v>0.6258</v>
       </c>
       <c r="J92" t="n">
-        <v>23.184</v>
+        <v>21.903</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.17</v>
       </c>
       <c r="I93" t="n">
-        <v>0.5597</v>
+        <v>0.5228</v>
       </c>
       <c r="J93" t="n">
-        <v>19.5895</v>
+        <v>18.298</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.01</v>
       </c>
       <c r="I94" t="n">
-        <v>0.0114</v>
+        <v>0.0441</v>
       </c>
       <c r="J94" t="n">
-        <v>0.399</v>
+        <v>1.5435</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.2993</v>
+        <v>-0.2427</v>
       </c>
       <c r="J95" t="n">
-        <v>-10.4755</v>
+        <v>-8.4945</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.92</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.3622</v>
+        <v>-0.3042</v>
       </c>
       <c r="J96" t="n">
-        <v>-12.677</v>
+        <v>-10.647</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.08</v>
       </c>
       <c r="I97" t="n">
-        <v>0.1919</v>
+        <v>0.2045</v>
       </c>
       <c r="J97" t="n">
-        <v>6.7165</v>
+        <v>7.1575</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.08</v>
       </c>
       <c r="I98" t="n">
-        <v>0.1919</v>
+        <v>0.2045</v>
       </c>
       <c r="J98" t="n">
-        <v>6.7165</v>
+        <v>7.1575</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.98</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.06909999999999999</v>
+        <v>-0.0361</v>
       </c>
       <c r="J99" t="n">
-        <v>-2.4185</v>
+        <v>-1.2635</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.156</v>
+        <v>-0.0883</v>
       </c>
       <c r="J100" t="n">
-        <v>-5.46</v>
+        <v>-3.0905</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.93</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.175</v>
+        <v>-0.1002</v>
       </c>
       <c r="J101" t="n">
-        <v>-6.125</v>
+        <v>-3.507</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.25</v>
       </c>
       <c r="I102" t="n">
-        <v>0.4462</v>
+        <v>0.3992</v>
       </c>
       <c r="J102" t="n">
-        <v>12.4936</v>
+        <v>11.1776</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.1</v>
       </c>
       <c r="I103" t="n">
-        <v>0.2192</v>
+        <v>0.1846</v>
       </c>
       <c r="J103" t="n">
-        <v>6.1376</v>
+        <v>5.1688</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.1</v>
       </c>
       <c r="I104" t="n">
-        <v>0.2192</v>
+        <v>0.1846</v>
       </c>
       <c r="J104" t="n">
-        <v>6.1376</v>
+        <v>5.1688</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>1.02</v>
       </c>
       <c r="I105" t="n">
-        <v>0.0497</v>
+        <v>0.0485</v>
       </c>
       <c r="J105" t="n">
-        <v>1.3916</v>
+        <v>1.358</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.64</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.6</v>
+        <v>-0.3948</v>
       </c>
       <c r="J106" t="n">
-        <v>-16.8</v>
+        <v>-11.0544</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.53</v>
       </c>
       <c r="I107" t="n">
-        <v>0.7653</v>
+        <v>0.6807</v>
       </c>
       <c r="J107" t="n">
-        <v>21.4284</v>
+        <v>19.0596</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.3</v>
       </c>
       <c r="I108" t="n">
-        <v>0.4869</v>
+        <v>0.4156</v>
       </c>
       <c r="J108" t="n">
-        <v>13.6332</v>
+        <v>11.6368</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.01</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.012</v>
+        <v>0.0157</v>
       </c>
       <c r="J109" t="n">
-        <v>-0.336</v>
+        <v>0.4396</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.99</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.08069999999999999</v>
+        <v>-0.0301</v>
       </c>
       <c r="J110" t="n">
-        <v>-2.2596</v>
+        <v>-0.8428</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.68</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.5617</v>
+        <v>-0.3656</v>
       </c>
       <c r="J111" t="n">
-        <v>-15.7276</v>
+        <v>-10.2368</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.53</v>
       </c>
       <c r="I112" t="n">
-        <v>1.271</v>
+        <v>1.1743</v>
       </c>
       <c r="J112" t="n">
-        <v>34.317</v>
+        <v>31.7061</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.33</v>
       </c>
       <c r="I113" t="n">
-        <v>0.849</v>
+        <v>0.8558</v>
       </c>
       <c r="J113" t="n">
-        <v>22.923</v>
+        <v>23.1066</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.23</v>
       </c>
       <c r="I114" t="n">
-        <v>0.5979</v>
+        <v>0.6268</v>
       </c>
       <c r="J114" t="n">
-        <v>16.1433</v>
+        <v>16.9236</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1.2</v>
       </c>
       <c r="I115" t="n">
-        <v>0.502</v>
+        <v>0.5571</v>
       </c>
       <c r="J115" t="n">
-        <v>13.554</v>
+        <v>15.0417</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.82</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.6874</v>
+        <v>-0.6283</v>
       </c>
       <c r="J116" t="n">
-        <v>-18.5598</v>
+        <v>-16.9641</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>0.95</v>
       </c>
       <c r="I117" t="n">
-        <v>-0.039</v>
+        <v>-0.0549</v>
       </c>
       <c r="J117" t="n">
-        <v>-1.053</v>
+        <v>-1.4823</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>0.88</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.1682</v>
+        <v>-0.1375</v>
       </c>
       <c r="J118" t="n">
-        <v>-4.5414</v>
+        <v>-3.7125</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.83</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.2602</v>
+        <v>-0.1891</v>
       </c>
       <c r="J119" t="n">
-        <v>-7.0254</v>
+        <v>-5.1057</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.76</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.3887</v>
+        <v>-0.2564</v>
       </c>
       <c r="J120" t="n">
-        <v>-10.4949</v>
+        <v>-6.9228</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.7</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.4779</v>
+        <v>-0.3139</v>
       </c>
       <c r="J121" t="n">
-        <v>-12.9033</v>
+        <v>-8.475300000000001</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.27</v>
       </c>
       <c r="I122" t="n">
-        <v>0.4646</v>
+        <v>0.5483</v>
       </c>
       <c r="J122" t="n">
-        <v>16.261</v>
+        <v>19.1905</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.25</v>
       </c>
       <c r="I123" t="n">
-        <v>0.4375</v>
+        <v>0.5135</v>
       </c>
       <c r="J123" t="n">
-        <v>15.3125</v>
+        <v>17.9725</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.01</v>
       </c>
       <c r="I124" t="n">
-        <v>0.0074</v>
+        <v>0.0315</v>
       </c>
       <c r="J124" t="n">
-        <v>0.259</v>
+        <v>1.1025</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.97</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.1113</v>
+        <v>-0.0547</v>
       </c>
       <c r="J125" t="n">
-        <v>-3.8955</v>
+        <v>-1.9145</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.74</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.4762</v>
+        <v>-0.3033</v>
       </c>
       <c r="J126" t="n">
-        <v>-16.667</v>
+        <v>-10.6155</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.29</v>
       </c>
       <c r="I127" t="n">
-        <v>0.8129</v>
+        <v>0.795</v>
       </c>
       <c r="J127" t="n">
-        <v>28.4515</v>
+        <v>27.825</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.23</v>
       </c>
       <c r="I128" t="n">
-        <v>0.669</v>
+        <v>0.6505</v>
       </c>
       <c r="J128" t="n">
-        <v>23.415</v>
+        <v>22.7675</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.21</v>
       </c>
       <c r="I129" t="n">
-        <v>0.6185</v>
+        <v>0.6014</v>
       </c>
       <c r="J129" t="n">
-        <v>21.6475</v>
+        <v>21.049</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1.01</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.0312</v>
+        <v>0.0262</v>
       </c>
       <c r="J130" t="n">
-        <v>-1.092</v>
+        <v>0.917</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.87</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.5326</v>
+        <v>-0.4683</v>
       </c>
       <c r="J131" t="n">
-        <v>-18.641</v>
+        <v>-16.3905</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.55</v>
       </c>
       <c r="I132" t="n">
-        <v>0.7665999999999999</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="J132" t="n">
-        <v>20.6982</v>
+        <v>18.468</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.3</v>
       </c>
       <c r="I133" t="n">
-        <v>0.4637</v>
+        <v>0.4029</v>
       </c>
       <c r="J133" t="n">
-        <v>12.5199</v>
+        <v>10.8783</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.1</v>
       </c>
       <c r="I134" t="n">
-        <v>0.1436</v>
+        <v>0.1552</v>
       </c>
       <c r="J134" t="n">
-        <v>3.8772</v>
+        <v>4.1904</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.97</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.1446</v>
+        <v>-0.0675</v>
       </c>
       <c r="J135" t="n">
-        <v>-3.9042</v>
+        <v>-1.8225</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.95</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.1837</v>
+        <v>-0.09379999999999999</v>
       </c>
       <c r="J136" t="n">
-        <v>-4.9599</v>
+        <v>-2.5326</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.26</v>
       </c>
       <c r="I137" t="n">
-        <v>0.4845</v>
+        <v>0.4334</v>
       </c>
       <c r="J137" t="n">
-        <v>13.0815</v>
+        <v>11.7018</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.09</v>
       </c>
       <c r="I138" t="n">
-        <v>0.2299</v>
+        <v>0.1831</v>
       </c>
       <c r="J138" t="n">
-        <v>6.2073</v>
+        <v>4.9437</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.07</v>
       </c>
       <c r="I139" t="n">
-        <v>0.1944</v>
+        <v>0.1502</v>
       </c>
       <c r="J139" t="n">
-        <v>5.2488</v>
+        <v>4.0554</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.76</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.4286</v>
+        <v>-0.2726</v>
       </c>
       <c r="J140" t="n">
-        <v>-11.5722</v>
+        <v>-7.3602</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.57</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.6748</v>
+        <v>-0.4513</v>
       </c>
       <c r="J141" t="n">
-        <v>-18.2196</v>
+        <v>-12.1851</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.21</v>
       </c>
       <c r="I142" t="n">
-        <v>0.4271</v>
+        <v>0.4879</v>
       </c>
       <c r="J142" t="n">
-        <v>10.2504</v>
+        <v>11.7096</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>0.95</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.08260000000000001</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="J143" t="n">
-        <v>-1.9824</v>
+        <v>-1.656</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.89</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.2131</v>
+        <v>-0.1364</v>
       </c>
       <c r="J144" t="n">
-        <v>-5.1144</v>
+        <v>-3.2736</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.85</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.2829</v>
+        <v>-0.1784</v>
       </c>
       <c r="J145" t="n">
-        <v>-6.7896</v>
+        <v>-4.2816</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.5169</v>
+        <v>-0.336</v>
       </c>
       <c r="J146" t="n">
-        <v>-12.4056</v>
+        <v>-8.064</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.82</v>
       </c>
       <c r="I147" t="n">
-        <v>1.7693</v>
+        <v>1.5065</v>
       </c>
       <c r="J147" t="n">
-        <v>42.4632</v>
+        <v>36.156</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.57</v>
       </c>
       <c r="I148" t="n">
-        <v>1.3104</v>
+        <v>1.2058</v>
       </c>
       <c r="J148" t="n">
-        <v>31.4496</v>
+        <v>28.9392</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.26</v>
       </c>
       <c r="I149" t="n">
-        <v>0.604</v>
+        <v>0.6832</v>
       </c>
       <c r="J149" t="n">
-        <v>14.496</v>
+        <v>16.3968</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.157</v>
+        <v>-0.0737</v>
       </c>
       <c r="J150" t="n">
-        <v>-3.768</v>
+        <v>-1.7688</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.87</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.5826</v>
+        <v>-0.5125999999999999</v>
       </c>
       <c r="J151" t="n">
-        <v>-13.9824</v>
+        <v>-12.3024</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.32</v>
       </c>
       <c r="I152" t="n">
-        <v>0.5387999999999999</v>
+        <v>0.6434</v>
       </c>
       <c r="J152" t="n">
-        <v>18.858</v>
+        <v>22.519</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.07</v>
       </c>
       <c r="I153" t="n">
-        <v>0.1648</v>
+        <v>0.179</v>
       </c>
       <c r="J153" t="n">
-        <v>5.768</v>
+        <v>6.265</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.05</v>
       </c>
       <c r="I154" t="n">
-        <v>0.1249</v>
+        <v>0.1352</v>
       </c>
       <c r="J154" t="n">
-        <v>4.3715</v>
+        <v>4.732</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>1.03</v>
       </c>
       <c r="I155" t="n">
-        <v>0.0795</v>
+        <v>0.0885</v>
       </c>
       <c r="J155" t="n">
-        <v>2.7825</v>
+        <v>3.0975</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.64</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.6</v>
+        <v>-0.3948</v>
       </c>
       <c r="J156" t="n">
-        <v>-21</v>
+        <v>-13.818</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.34</v>
       </c>
       <c r="I157" t="n">
-        <v>0.9133</v>
+        <v>0.903</v>
       </c>
       <c r="J157" t="n">
-        <v>31.9655</v>
+        <v>31.605</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.34</v>
       </c>
       <c r="I158" t="n">
-        <v>0.9133</v>
+        <v>0.903</v>
       </c>
       <c r="J158" t="n">
-        <v>31.9655</v>
+        <v>31.605</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.13</v>
       </c>
       <c r="I159" t="n">
-        <v>0.359</v>
+        <v>0.3957</v>
       </c>
       <c r="J159" t="n">
-        <v>12.565</v>
+        <v>13.8495</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.96</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.276</v>
+        <v>-0.2031</v>
       </c>
       <c r="J160" t="n">
-        <v>-9.66</v>
+        <v>-7.1085</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.96</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.276</v>
+        <v>-0.2031</v>
       </c>
       <c r="J161" t="n">
-        <v>-9.66</v>
+        <v>-7.1085</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.05</v>
       </c>
       <c r="I162" t="n">
-        <v>0.2289</v>
+        <v>0.2209</v>
       </c>
       <c r="J162" t="n">
-        <v>5.9514</v>
+        <v>5.7434</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>0.85</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.1939</v>
+        <v>-0.1615</v>
       </c>
       <c r="J163" t="n">
-        <v>-5.0414</v>
+        <v>-4.199</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.7</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.4588</v>
+        <v>-0.3065</v>
       </c>
       <c r="J164" t="n">
-        <v>-11.9288</v>
+        <v>-7.969</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.66</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.5173</v>
+        <v>-0.3443</v>
       </c>
       <c r="J165" t="n">
-        <v>-13.4498</v>
+        <v>-8.9518</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.6</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.6001</v>
+        <v>-0.4006</v>
       </c>
       <c r="J166" t="n">
-        <v>-15.6026</v>
+        <v>-10.4156</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>2.03</v>
       </c>
       <c r="I167" t="n">
-        <v>2.0463</v>
+        <v>1.7657</v>
       </c>
       <c r="J167" t="n">
-        <v>53.2038</v>
+        <v>45.9082</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.15</v>
       </c>
       <c r="I168" t="n">
-        <v>0.3441</v>
+        <v>0.4231</v>
       </c>
       <c r="J168" t="n">
-        <v>8.9466</v>
+        <v>11.0006</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.13</v>
       </c>
       <c r="I169" t="n">
-        <v>0.2907</v>
+        <v>0.3702</v>
       </c>
       <c r="J169" t="n">
-        <v>7.5582</v>
+        <v>9.6252</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1.09</v>
       </c>
       <c r="I170" t="n">
-        <v>0.1797</v>
+        <v>0.2588</v>
       </c>
       <c r="J170" t="n">
-        <v>4.6722</v>
+        <v>6.7288</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.92</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.4381</v>
+        <v>-0.36</v>
       </c>
       <c r="J171" t="n">
-        <v>-11.3906</v>
+        <v>-9.359999999999999</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.57</v>
       </c>
       <c r="I172" t="n">
-        <v>1.3796</v>
+        <v>1.2418</v>
       </c>
       <c r="J172" t="n">
-        <v>35.8696</v>
+        <v>32.2868</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.26</v>
       </c>
       <c r="I173" t="n">
-        <v>0.7199</v>
+        <v>0.7114</v>
       </c>
       <c r="J173" t="n">
-        <v>18.7174</v>
+        <v>18.4964</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.18</v>
       </c>
       <c r="I174" t="n">
-        <v>0.5104</v>
+        <v>0.5181</v>
       </c>
       <c r="J174" t="n">
-        <v>13.2704</v>
+        <v>13.4706</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>1.05</v>
       </c>
       <c r="I175" t="n">
-        <v>0.1015</v>
+        <v>0.1622</v>
       </c>
       <c r="J175" t="n">
-        <v>2.639</v>
+        <v>4.2172</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.74</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.8586</v>
+        <v>-0.8173</v>
       </c>
       <c r="J176" t="n">
-        <v>-22.3236</v>
+        <v>-21.2498</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.36</v>
       </c>
       <c r="I177" t="n">
-        <v>0.594</v>
+        <v>0.717</v>
       </c>
       <c r="J177" t="n">
-        <v>15.444</v>
+        <v>18.642</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.28</v>
       </c>
       <c r="I178" t="n">
-        <v>0.4913</v>
+        <v>0.5793</v>
       </c>
       <c r="J178" t="n">
-        <v>12.7738</v>
+        <v>15.0618</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>0.9</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.2304</v>
+        <v>-0.1351</v>
       </c>
       <c r="J179" t="n">
-        <v>-5.9904</v>
+        <v>-3.5126</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.78</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.4138</v>
+        <v>-0.2598</v>
       </c>
       <c r="J180" t="n">
-        <v>-10.7588</v>
+        <v>-6.7548</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.72</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.4955</v>
+        <v>-0.3181</v>
       </c>
       <c r="J181" t="n">
-        <v>-12.883</v>
+        <v>-8.2706</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.84</v>
       </c>
       <c r="I182" t="n">
-        <v>1.7195</v>
+        <v>1.4831</v>
       </c>
       <c r="J182" t="n">
-        <v>32.6705</v>
+        <v>28.1789</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.53</v>
       </c>
       <c r="I183" t="n">
-        <v>1.1278</v>
+        <v>1.128</v>
       </c>
       <c r="J183" t="n">
-        <v>21.4282</v>
+        <v>21.432</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.5</v>
       </c>
       <c r="I184" t="n">
-        <v>1.0487</v>
+        <v>1.0938</v>
       </c>
       <c r="J184" t="n">
-        <v>19.9253</v>
+        <v>20.7822</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>1.35</v>
       </c>
       <c r="I185" t="n">
-        <v>0.7185</v>
+        <v>0.8467</v>
       </c>
       <c r="J185" t="n">
-        <v>13.6515</v>
+        <v>16.0873</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>1.31</v>
       </c>
       <c r="I186" t="n">
-        <v>0.6319</v>
+        <v>0.7576000000000001</v>
       </c>
       <c r="J186" t="n">
-        <v>12.0061</v>
+        <v>14.3944</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.14</v>
       </c>
       <c r="I187" t="n">
-        <v>0.4645</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="J187" t="n">
-        <v>8.8255</v>
+        <v>10.773</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>0.68</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.3774</v>
+        <v>-0.3008</v>
       </c>
       <c r="J188" t="n">
-        <v>-7.1706</v>
+        <v>-5.7152</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.44</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.7642</v>
+        <v>-0.5233</v>
       </c>
       <c r="J189" t="n">
-        <v>-14.5198</v>
+        <v>-9.9427</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.41</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.8037</v>
+        <v>-0.5518999999999999</v>
       </c>
       <c r="J190" t="n">
-        <v>-15.2703</v>
+        <v>-10.4861</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.37</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.8552</v>
+        <v>-0.5901</v>
       </c>
       <c r="J191" t="n">
-        <v>-16.2488</v>
+        <v>-11.2119</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.76</v>
       </c>
       <c r="I192" t="n">
-        <v>1.6607</v>
+        <v>1.4338</v>
       </c>
       <c r="J192" t="n">
-        <v>43.1782</v>
+        <v>37.2788</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.33</v>
       </c>
       <c r="I193" t="n">
-        <v>0.793</v>
+        <v>0.8362000000000001</v>
       </c>
       <c r="J193" t="n">
-        <v>20.618</v>
+        <v>21.7412</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.26</v>
       </c>
       <c r="I194" t="n">
-        <v>0.6004</v>
+        <v>0.6821</v>
       </c>
       <c r="J194" t="n">
-        <v>15.6104</v>
+        <v>17.7346</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.11</v>
       </c>
       <c r="I195" t="n">
-        <v>0.2187</v>
+        <v>0.3049</v>
       </c>
       <c r="J195" t="n">
-        <v>5.6862</v>
+        <v>7.9274</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>1.09</v>
       </c>
       <c r="I196" t="n">
-        <v>0.1632</v>
+        <v>0.2481</v>
       </c>
       <c r="J196" t="n">
-        <v>4.2432</v>
+        <v>6.4506</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.08</v>
       </c>
       <c r="I197" t="n">
-        <v>0.2997</v>
+        <v>0.3146</v>
       </c>
       <c r="J197" t="n">
-        <v>7.7922</v>
+        <v>8.179600000000001</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I198" t="n">
-        <v>-0.242</v>
+        <v>-0.197</v>
       </c>
       <c r="J198" t="n">
-        <v>-6.292</v>
+        <v>-5.122</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.76</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.3259</v>
+        <v>-0.2467</v>
       </c>
       <c r="J199" t="n">
-        <v>-8.4734</v>
+        <v>-6.4142</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.57</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.6299</v>
+        <v>-0.4231</v>
       </c>
       <c r="J200" t="n">
-        <v>-16.3774</v>
+        <v>-11.0006</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.46</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.7712</v>
+        <v>-0.5255</v>
       </c>
       <c r="J201" t="n">
-        <v>-20.0512</v>
+        <v>-13.663</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>0.96</v>
       </c>
       <c r="I202" t="n">
-        <v>0.0994</v>
+        <v>0.0755</v>
       </c>
       <c r="J202" t="n">
-        <v>1.6898</v>
+        <v>1.2835</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>0.75</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.2536</v>
+        <v>-0.2204</v>
       </c>
       <c r="J203" t="n">
-        <v>-4.3112</v>
+        <v>-3.7468</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.53</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.6249</v>
+        <v>-0.4335</v>
       </c>
       <c r="J204" t="n">
-        <v>-10.6233</v>
+        <v>-7.3695</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.34</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.8871</v>
+        <v>-0.6145</v>
       </c>
       <c r="J205" t="n">
-        <v>-15.0807</v>
+        <v>-10.4465</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.33</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.8997000000000001</v>
+        <v>-0.6242</v>
       </c>
       <c r="J206" t="n">
-        <v>-15.2949</v>
+        <v>-10.6114</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>2.03</v>
       </c>
       <c r="I207" t="n">
-        <v>1.9555</v>
+        <v>1.6649</v>
       </c>
       <c r="J207" t="n">
-        <v>33.2435</v>
+        <v>28.3033</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.83</v>
       </c>
       <c r="I208" t="n">
-        <v>1.6415</v>
+        <v>1.4484</v>
       </c>
       <c r="J208" t="n">
-        <v>27.9055</v>
+        <v>24.6228</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.71</v>
       </c>
       <c r="I209" t="n">
-        <v>1.417</v>
+        <v>1.317</v>
       </c>
       <c r="J209" t="n">
-        <v>24.089</v>
+        <v>22.389</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.43</v>
       </c>
       <c r="I210" t="n">
-        <v>0.8353</v>
+        <v>0.9821</v>
       </c>
       <c r="J210" t="n">
-        <v>14.2001</v>
+        <v>16.6957</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>1.29</v>
       </c>
       <c r="I211" t="n">
-        <v>0.5472</v>
+        <v>0.6831</v>
       </c>
       <c r="J211" t="n">
-        <v>9.3024</v>
+        <v>11.6127</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.95</v>
       </c>
       <c r="I212" t="n">
-        <v>1.9308</v>
+        <v>1.6296</v>
       </c>
       <c r="J212" t="n">
-        <v>40.5468</v>
+        <v>34.2216</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.52</v>
       </c>
       <c r="I213" t="n">
-        <v>1.1625</v>
+        <v>1.1274</v>
       </c>
       <c r="J213" t="n">
-        <v>24.4125</v>
+        <v>23.6754</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.29</v>
       </c>
       <c r="I214" t="n">
-        <v>0.6244</v>
+        <v>0.7321</v>
       </c>
       <c r="J214" t="n">
-        <v>13.1124</v>
+        <v>15.3741</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>1.22</v>
       </c>
       <c r="I215" t="n">
-        <v>0.462</v>
+        <v>0.5677</v>
       </c>
       <c r="J215" t="n">
-        <v>9.702</v>
+        <v>11.9217</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>1.05</v>
       </c>
       <c r="I216" t="n">
-        <v>0.0171</v>
+        <v>0.1046</v>
       </c>
       <c r="J216" t="n">
-        <v>0.3591</v>
+        <v>2.1966</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>0.97</v>
       </c>
       <c r="I217" t="n">
-        <v>0.0448</v>
+        <v>-0.0037</v>
       </c>
       <c r="J217" t="n">
-        <v>0.9408</v>
+        <v>-0.07770000000000001</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>0.96</v>
       </c>
       <c r="I218" t="n">
-        <v>0.0239</v>
+        <v>-0.0182</v>
       </c>
       <c r="J218" t="n">
-        <v>0.5019</v>
+        <v>-0.3822</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.73</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.3767</v>
+        <v>-0.2735</v>
       </c>
       <c r="J219" t="n">
-        <v>-7.9107</v>
+        <v>-5.7435</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.53</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.6805</v>
+        <v>-0.4592</v>
       </c>
       <c r="J220" t="n">
-        <v>-14.2905</v>
+        <v>-9.6432</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.45</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.7819</v>
+        <v>-0.5337</v>
       </c>
       <c r="J221" t="n">
-        <v>-16.4199</v>
+        <v>-11.2077</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.68</v>
       </c>
       <c r="I222" t="n">
-        <v>1.5014</v>
+        <v>1.3308</v>
       </c>
       <c r="J222" t="n">
-        <v>31.5294</v>
+        <v>27.9468</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.51</v>
       </c>
       <c r="I223" t="n">
-        <v>1.1735</v>
+        <v>1.125</v>
       </c>
       <c r="J223" t="n">
-        <v>24.6435</v>
+        <v>23.625</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.43</v>
       </c>
       <c r="I224" t="n">
-        <v>1.0057</v>
+        <v>1.0226</v>
       </c>
       <c r="J224" t="n">
-        <v>21.1197</v>
+        <v>21.4746</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1.27</v>
       </c>
       <c r="I225" t="n">
-        <v>0.6073</v>
+        <v>0.699</v>
       </c>
       <c r="J225" t="n">
-        <v>12.7533</v>
+        <v>14.679</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.82</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.7131999999999999</v>
+        <v>-0.6544</v>
       </c>
       <c r="J226" t="n">
-        <v>-14.9772</v>
+        <v>-13.7424</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>0.87</v>
       </c>
       <c r="I227" t="n">
-        <v>-0.1165</v>
+        <v>-0.1182</v>
       </c>
       <c r="J227" t="n">
-        <v>-2.4465</v>
+        <v>-2.4822</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>0.86</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.133</v>
+        <v>-0.1298</v>
       </c>
       <c r="J228" t="n">
-        <v>-2.793</v>
+        <v>-2.7258</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.67</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.4571</v>
+        <v>-0.322</v>
       </c>
       <c r="J229" t="n">
-        <v>-9.5991</v>
+        <v>-6.762</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.58</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.5977</v>
+        <v>-0.4049</v>
       </c>
       <c r="J230" t="n">
-        <v>-12.5517</v>
+        <v>-8.5029</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.43</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.7968</v>
+        <v>-0.5454</v>
       </c>
       <c r="J231" t="n">
-        <v>-16.7328</v>
+        <v>-11.4534</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/1954/event_1954_evp_summary.xlsx
+++ b/database/event/1954/event_1954_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.9857</v>
+        <v>7.0927</v>
       </c>
       <c r="C2" t="n">
-        <v>1.3723</v>
+        <v>1.3934</v>
       </c>
       <c r="D2" t="n">
-        <v>2.5157</v>
+        <v>2.6045</v>
       </c>
       <c r="E2" t="n">
-        <v>6.9857</v>
+        <v>7.0927</v>
       </c>
       <c r="F2" t="n">
-        <v>3.0903</v>
+        <v>3.0504</v>
       </c>
       <c r="G2" t="n">
-        <v>3.8955</v>
+        <v>4.0423</v>
       </c>
       <c r="H2" t="n">
-        <v>5.4018</v>
+        <v>5.1701</v>
       </c>
       <c r="I2" t="n">
-        <v>2.8087</v>
+        <v>2.7918</v>
       </c>
       <c r="J2" t="n">
-        <v>3.8955</v>
+        <v>4.0423</v>
       </c>
       <c r="K2" t="n">
         <v>40</v>
@@ -529,7 +529,7 @@
         <v>102</v>
       </c>
       <c r="M2" t="n">
-        <v>6.7042</v>
+        <v>6.834099999999999</v>
       </c>
       <c r="N2" t="n">
         <v>142</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.0907</v>
+        <v>6.1877</v>
       </c>
       <c r="C3" t="n">
-        <v>1.1965</v>
+        <v>1.2156</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1116</v>
+        <v>2.1926</v>
       </c>
       <c r="E3" t="n">
-        <v>6.0907</v>
+        <v>6.1877</v>
       </c>
       <c r="F3" t="n">
-        <v>2.3522</v>
+        <v>2.2733</v>
       </c>
       <c r="G3" t="n">
-        <v>3.7385</v>
+        <v>3.9144</v>
       </c>
       <c r="H3" t="n">
-        <v>2.8014</v>
+        <v>2.6063</v>
       </c>
       <c r="I3" t="n">
-        <v>1.4566</v>
+        <v>1.4074</v>
       </c>
       <c r="J3" t="n">
-        <v>3.7385</v>
+        <v>3.9144</v>
       </c>
       <c r="K3" t="n">
         <v>40</v>
@@ -575,7 +575,7 @@
         <v>102</v>
       </c>
       <c r="M3" t="n">
-        <v>5.1951</v>
+        <v>5.3218</v>
       </c>
       <c r="N3" t="n">
         <v>142</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.4954</v>
+        <v>4.5911</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8831</v>
+        <v>0.9019</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3914</v>
+        <v>1.4658</v>
       </c>
       <c r="E4" t="n">
-        <v>4.4954</v>
+        <v>4.5911</v>
       </c>
       <c r="F4" t="n">
-        <v>3.0647</v>
+        <v>2.9893</v>
       </c>
       <c r="G4" t="n">
-        <v>1.4307</v>
+        <v>1.6018</v>
       </c>
       <c r="H4" t="n">
-        <v>5.3116</v>
+        <v>4.9686</v>
       </c>
       <c r="I4" t="n">
-        <v>2.7618</v>
+        <v>2.683</v>
       </c>
       <c r="J4" t="n">
-        <v>1.4307</v>
+        <v>1.6018</v>
       </c>
       <c r="K4" t="n">
         <v>126</v>
@@ -621,7 +621,7 @@
         <v>91</v>
       </c>
       <c r="M4" t="n">
-        <v>4.1925</v>
+        <v>4.2848</v>
       </c>
       <c r="N4" t="n">
         <v>217</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.4927</v>
+        <v>4.5444</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8826000000000001</v>
+        <v>0.8927</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3902</v>
+        <v>1.4445</v>
       </c>
       <c r="E5" t="n">
-        <v>4.4927</v>
+        <v>4.5444</v>
       </c>
       <c r="F5" t="n">
-        <v>2.6334</v>
+        <v>2.5515</v>
       </c>
       <c r="G5" t="n">
-        <v>1.8593</v>
+        <v>1.9929</v>
       </c>
       <c r="H5" t="n">
-        <v>3.7921</v>
+        <v>3.5243</v>
       </c>
       <c r="I5" t="n">
-        <v>1.9717</v>
+        <v>1.9031</v>
       </c>
       <c r="J5" t="n">
-        <v>1.8593</v>
+        <v>1.9929</v>
       </c>
       <c r="K5" t="n">
         <v>40</v>
@@ -667,7 +667,7 @@
         <v>102</v>
       </c>
       <c r="M5" t="n">
-        <v>3.831</v>
+        <v>3.896</v>
       </c>
       <c r="N5" t="n">
         <v>142</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.9451</v>
+        <v>3.889</v>
       </c>
       <c r="C6" t="n">
-        <v>0.775</v>
+        <v>0.764</v>
       </c>
       <c r="D6" t="n">
-        <v>1.143</v>
+        <v>1.1461</v>
       </c>
       <c r="E6" t="n">
-        <v>3.9451</v>
+        <v>3.889</v>
       </c>
       <c r="F6" t="n">
-        <v>2.7124</v>
+        <v>2.6267</v>
       </c>
       <c r="G6" t="n">
-        <v>1.2327</v>
+        <v>1.2623</v>
       </c>
       <c r="H6" t="n">
-        <v>4.0704</v>
+        <v>3.7723</v>
       </c>
       <c r="I6" t="n">
-        <v>2.1164</v>
+        <v>2.037</v>
       </c>
       <c r="J6" t="n">
-        <v>1.2327</v>
+        <v>1.2623</v>
       </c>
       <c r="K6" t="n">
         <v>40</v>
@@ -713,7 +713,7 @@
         <v>102</v>
       </c>
       <c r="M6" t="n">
-        <v>3.3491</v>
+        <v>3.2993</v>
       </c>
       <c r="N6" t="n">
         <v>142</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.5478</v>
+        <v>3.5682</v>
       </c>
       <c r="C7" t="n">
-        <v>0.697</v>
+        <v>0.701</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9636</v>
+        <v>1.0001</v>
       </c>
       <c r="E7" t="n">
-        <v>3.5478</v>
+        <v>3.5682</v>
       </c>
       <c r="F7" t="n">
-        <v>3.0449</v>
+        <v>3.0066</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5029</v>
+        <v>0.5616</v>
       </c>
       <c r="H7" t="n">
-        <v>5.2419</v>
+        <v>5.0256</v>
       </c>
       <c r="I7" t="n">
-        <v>2.7256</v>
+        <v>2.7138</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5029</v>
+        <v>0.5616</v>
       </c>
       <c r="K7" t="n">
         <v>126</v>
@@ -759,7 +759,7 @@
         <v>91</v>
       </c>
       <c r="M7" t="n">
-        <v>3.2285</v>
+        <v>3.2754</v>
       </c>
       <c r="N7" t="n">
         <v>217</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.4659</v>
+        <v>3.398</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6808999999999999</v>
+        <v>0.6675</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9267</v>
+        <v>0.9226</v>
       </c>
       <c r="E8" t="n">
-        <v>3.4659</v>
+        <v>3.398</v>
       </c>
       <c r="F8" t="n">
-        <v>3.4158</v>
+        <v>3.362</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0501</v>
+        <v>0.036</v>
       </c>
       <c r="H8" t="n">
-        <v>6.5488</v>
+        <v>6.1982</v>
       </c>
       <c r="I8" t="n">
-        <v>3.4051</v>
+        <v>3.347</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0501</v>
+        <v>0.036</v>
       </c>
       <c r="K8" t="n">
         <v>97</v>
@@ -805,7 +805,7 @@
         <v>52</v>
       </c>
       <c r="M8" t="n">
-        <v>3.4552</v>
+        <v>3.383</v>
       </c>
       <c r="N8" t="n">
         <v>149</v>
@@ -814,93 +814,93 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>HEN1</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.0143</v>
+        <v>2.9432</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5921999999999999</v>
+        <v>0.5782</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7228</v>
+        <v>0.7156</v>
       </c>
       <c r="E9" t="n">
-        <v>3.0143</v>
+        <v>2.9432</v>
       </c>
       <c r="F9" t="n">
-        <v>3.5857</v>
+        <v>2.4798</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.5714</v>
+        <v>0.4634</v>
       </c>
       <c r="H9" t="n">
-        <v>7.1474</v>
+        <v>3.2876</v>
       </c>
       <c r="I9" t="n">
-        <v>3.7163</v>
+        <v>1.7753</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.5714</v>
+        <v>0.4634</v>
       </c>
       <c r="K9" t="n">
-        <v>97</v>
+        <v>47</v>
       </c>
       <c r="L9" t="n">
-        <v>52</v>
+        <v>141</v>
       </c>
       <c r="M9" t="n">
-        <v>3.1449</v>
+        <v>2.2387</v>
       </c>
       <c r="N9" t="n">
-        <v>149</v>
+        <v>188</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HEN1</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.9772</v>
+        <v>2.9114</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5849</v>
+        <v>0.5719</v>
       </c>
       <c r="D10" t="n">
-        <v>0.706</v>
+        <v>0.7010999999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>2.9772</v>
+        <v>2.9114</v>
       </c>
       <c r="F10" t="n">
-        <v>2.5608</v>
+        <v>3.5144</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4164</v>
+        <v>-0.603</v>
       </c>
       <c r="H10" t="n">
-        <v>3.5365</v>
+        <v>6.7012</v>
       </c>
       <c r="I10" t="n">
-        <v>1.8388</v>
+        <v>3.6186</v>
       </c>
       <c r="J10" t="n">
-        <v>0.4164</v>
+        <v>-0.603</v>
       </c>
       <c r="K10" t="n">
-        <v>47</v>
+        <v>97</v>
       </c>
       <c r="L10" t="n">
-        <v>141</v>
+        <v>52</v>
       </c>
       <c r="M10" t="n">
-        <v>2.2552</v>
+        <v>3.0156</v>
       </c>
       <c r="N10" t="n">
-        <v>188</v>
+        <v>149</v>
       </c>
     </row>
     <row r="11">
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.9032</v>
+        <v>2.9098</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5703</v>
+        <v>0.5716</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6726</v>
+        <v>0.7004</v>
       </c>
       <c r="E11" t="n">
-        <v>2.9032</v>
+        <v>2.9098</v>
       </c>
       <c r="F11" t="n">
-        <v>2.4169</v>
+        <v>2.3586</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4863</v>
+        <v>0.5512</v>
       </c>
       <c r="H11" t="n">
-        <v>3.0292</v>
+        <v>2.8878</v>
       </c>
       <c r="I11" t="n">
-        <v>1.5751</v>
+        <v>1.5594</v>
       </c>
       <c r="J11" t="n">
-        <v>0.4863</v>
+        <v>0.5512</v>
       </c>
       <c r="K11" t="n">
         <v>126</v>
@@ -943,7 +943,7 @@
         <v>91</v>
       </c>
       <c r="M11" t="n">
-        <v>2.0614</v>
+        <v>2.1106</v>
       </c>
       <c r="N11" t="n">
         <v>217</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.8838</v>
+        <v>2.8442</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5665</v>
+        <v>0.5587</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6639</v>
+        <v>0.6705</v>
       </c>
       <c r="E12" t="n">
-        <v>2.8838</v>
+        <v>2.8442</v>
       </c>
       <c r="F12" t="n">
-        <v>2.5499</v>
+        <v>2.46</v>
       </c>
       <c r="G12" t="n">
-        <v>0.3339</v>
+        <v>0.3842</v>
       </c>
       <c r="H12" t="n">
-        <v>3.498</v>
+        <v>3.2223</v>
       </c>
       <c r="I12" t="n">
-        <v>1.8188</v>
+        <v>1.74</v>
       </c>
       <c r="J12" t="n">
-        <v>0.3339</v>
+        <v>0.3842</v>
       </c>
       <c r="K12" t="n">
         <v>126</v>
@@ -989,7 +989,7 @@
         <v>91</v>
       </c>
       <c r="M12" t="n">
-        <v>2.1527</v>
+        <v>2.1242</v>
       </c>
       <c r="N12" t="n">
         <v>217</v>
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.7542</v>
+        <v>2.6993</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5411</v>
+        <v>0.5303</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6054</v>
+        <v>0.6046</v>
       </c>
       <c r="E13" t="n">
-        <v>2.7542</v>
+        <v>2.6993</v>
       </c>
       <c r="F13" t="n">
-        <v>2.2395</v>
+        <v>2.1638</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5147</v>
+        <v>0.5355</v>
       </c>
       <c r="H13" t="n">
-        <v>2.4044</v>
+        <v>2.245</v>
       </c>
       <c r="I13" t="n">
-        <v>1.2502</v>
+        <v>1.2123</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5147</v>
+        <v>0.5355</v>
       </c>
       <c r="K13" t="n">
         <v>47</v>
@@ -1035,7 +1035,7 @@
         <v>141</v>
       </c>
       <c r="M13" t="n">
-        <v>1.7649</v>
+        <v>1.7478</v>
       </c>
       <c r="N13" t="n">
         <v>188</v>
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.7412</v>
+        <v>2.6575</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5385</v>
+        <v>0.5221</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5995</v>
+        <v>0.5855</v>
       </c>
       <c r="E14" t="n">
-        <v>2.7412</v>
+        <v>2.6575</v>
       </c>
       <c r="F14" t="n">
-        <v>2.787</v>
+        <v>2.722</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.0458</v>
+        <v>-0.0645</v>
       </c>
       <c r="H14" t="n">
-        <v>4.3333</v>
+        <v>4.0867</v>
       </c>
       <c r="I14" t="n">
-        <v>2.2531</v>
+        <v>2.2068</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.0458</v>
+        <v>-0.0645</v>
       </c>
       <c r="K14" t="n">
         <v>97</v>
@@ -1081,7 +1081,7 @@
         <v>52</v>
       </c>
       <c r="M14" t="n">
-        <v>2.2073</v>
+        <v>2.1423</v>
       </c>
       <c r="N14" t="n">
         <v>149</v>
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.3805</v>
+        <v>2.3453</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4676</v>
+        <v>0.4607</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4367</v>
+        <v>0.4434</v>
       </c>
       <c r="E15" t="n">
-        <v>2.3805</v>
+        <v>2.3453</v>
       </c>
       <c r="F15" t="n">
-        <v>2.5448</v>
+        <v>2.4768</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.1643</v>
+        <v>-0.1315</v>
       </c>
       <c r="H15" t="n">
-        <v>3.4801</v>
+        <v>3.2776</v>
       </c>
       <c r="I15" t="n">
-        <v>1.8095</v>
+        <v>1.7699</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.1643</v>
+        <v>-0.1315</v>
       </c>
       <c r="K15" t="n">
         <v>47</v>
@@ -1127,7 +1127,7 @@
         <v>141</v>
       </c>
       <c r="M15" t="n">
-        <v>1.6452</v>
+        <v>1.6384</v>
       </c>
       <c r="N15" t="n">
         <v>188</v>
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.1918</v>
+        <v>2.2261</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4306</v>
+        <v>0.4373</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3515</v>
+        <v>0.3892</v>
       </c>
       <c r="E16" t="n">
-        <v>2.1918</v>
+        <v>2.2261</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9108000000000001</v>
+        <v>0.9239000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>1.281</v>
+        <v>1.3022</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9108000000000001</v>
+        <v>0.9239000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4736</v>
+        <v>0.4989</v>
       </c>
       <c r="J16" t="n">
-        <v>1.281</v>
+        <v>1.3022</v>
       </c>
       <c r="K16" t="n">
         <v>40</v>
@@ -1173,7 +1173,7 @@
         <v>102</v>
       </c>
       <c r="M16" t="n">
-        <v>1.7546</v>
+        <v>1.8011</v>
       </c>
       <c r="N16" t="n">
         <v>142</v>
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.9872</v>
+        <v>1.9057</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3904</v>
+        <v>0.3744</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2591</v>
+        <v>0.2433</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9872</v>
+        <v>1.9057</v>
       </c>
       <c r="F17" t="n">
-        <v>2.5374</v>
+        <v>2.4801</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.5502</v>
+        <v>-0.5744</v>
       </c>
       <c r="H17" t="n">
-        <v>3.4537</v>
+        <v>3.2886</v>
       </c>
       <c r="I17" t="n">
-        <v>1.7958</v>
+        <v>1.7758</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.5502</v>
+        <v>-0.5744</v>
       </c>
       <c r="K17" t="n">
         <v>97</v>
@@ -1219,7 +1219,7 @@
         <v>52</v>
       </c>
       <c r="M17" t="n">
-        <v>1.2456</v>
+        <v>1.2014</v>
       </c>
       <c r="N17" t="n">
         <v>149</v>
@@ -1232,28 +1232,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.7083</v>
+        <v>1.6305</v>
       </c>
       <c r="C18" t="n">
-        <v>0.3356</v>
+        <v>0.3203</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1332</v>
+        <v>0.118</v>
       </c>
       <c r="E18" t="n">
-        <v>1.7083</v>
+        <v>1.6305</v>
       </c>
       <c r="F18" t="n">
-        <v>1.7083</v>
+        <v>1.6305</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1.7083</v>
+        <v>1.6305</v>
       </c>
       <c r="I18" t="n">
-        <v>1.7786</v>
+        <v>1.6725</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.7786</v>
+        <v>1.6725</v>
       </c>
       <c r="N18" t="n">
         <v>168</v>
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.3168</v>
+        <v>1.4749</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2587</v>
+        <v>0.2897</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0435</v>
+        <v>0.0472</v>
       </c>
       <c r="E19" t="n">
-        <v>1.3168</v>
+        <v>1.4749</v>
       </c>
       <c r="F19" t="n">
-        <v>1.4855</v>
+        <v>1.6241</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.1687</v>
+        <v>-0.1492</v>
       </c>
       <c r="H19" t="n">
-        <v>1.4855</v>
+        <v>1.6241</v>
       </c>
       <c r="I19" t="n">
-        <v>0.7724</v>
+        <v>0.877</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.1687</v>
+        <v>-0.1492</v>
       </c>
       <c r="K19" t="n">
         <v>47</v>
@@ -1311,7 +1311,7 @@
         <v>141</v>
       </c>
       <c r="M19" t="n">
-        <v>0.6037</v>
+        <v>0.7278</v>
       </c>
       <c r="N19" t="n">
         <v>188</v>
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.1656</v>
+        <v>1.1336</v>
       </c>
       <c r="C20" t="n">
-        <v>0.229</v>
+        <v>0.2227</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1118</v>
+        <v>-0.1082</v>
       </c>
       <c r="E20" t="n">
-        <v>1.1656</v>
+        <v>1.1336</v>
       </c>
       <c r="F20" t="n">
-        <v>1.1656</v>
+        <v>1.1336</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.1656</v>
+        <v>1.1336</v>
       </c>
       <c r="I20" t="n">
-        <v>1.1656</v>
+        <v>1.1336</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.1656</v>
+        <v>1.1336</v>
       </c>
       <c r="N20" t="n">
         <v>107</v>
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.1333</v>
+        <v>1.0307</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2226</v>
+        <v>0.2025</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1264</v>
+        <v>-0.155</v>
       </c>
       <c r="E21" t="n">
-        <v>1.1333</v>
+        <v>1.0307</v>
       </c>
       <c r="F21" t="n">
-        <v>1.1333</v>
+        <v>1.0307</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.1333</v>
+        <v>1.0307</v>
       </c>
       <c r="I21" t="n">
-        <v>1.1333</v>
+        <v>1.0307</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.1333</v>
+        <v>1.0307</v>
       </c>
       <c r="N21" t="n">
         <v>157</v>
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.1152</v>
+        <v>1.0225</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2191</v>
+        <v>0.2009</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1346</v>
+        <v>-0.1587</v>
       </c>
       <c r="E22" t="n">
-        <v>1.1152</v>
+        <v>1.0225</v>
       </c>
       <c r="F22" t="n">
-        <v>1.1152</v>
+        <v>1.0225</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.1152</v>
+        <v>1.0225</v>
       </c>
       <c r="I22" t="n">
-        <v>1.1152</v>
+        <v>1.0225</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.1152</v>
+        <v>1.0225</v>
       </c>
       <c r="N22" t="n">
         <v>157</v>
@@ -1462,28 +1462,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9175</v>
+        <v>0.8788</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1802</v>
+        <v>0.1726</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2238</v>
+        <v>-0.2242</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9175</v>
+        <v>0.8788</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9175</v>
+        <v>0.8788</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.9175</v>
+        <v>0.8788</v>
       </c>
       <c r="I23" t="n">
-        <v>0.9552</v>
+        <v>0.9014</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.9552</v>
+        <v>0.9014</v>
       </c>
       <c r="N23" t="n">
         <v>168</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8449</v>
+        <v>0.7856</v>
       </c>
       <c r="C24" t="n">
-        <v>0.166</v>
+        <v>0.1543</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2566</v>
+        <v>-0.2666</v>
       </c>
       <c r="E24" t="n">
-        <v>0.8449</v>
+        <v>0.7856</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8449</v>
+        <v>0.7856</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.8449</v>
+        <v>0.7856</v>
       </c>
       <c r="I24" t="n">
-        <v>0.8796</v>
+        <v>0.8058</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.8796</v>
+        <v>0.8058</v>
       </c>
       <c r="N24" t="n">
         <v>168</v>
@@ -1550,93 +1550,93 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>adreN</t>
+          <t>boltz</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6131</v>
+        <v>0.6532</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1204</v>
+        <v>0.1283</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3612</v>
+        <v>-0.3269</v>
       </c>
       <c r="E25" t="n">
-        <v>0.6131</v>
+        <v>0.6532</v>
       </c>
       <c r="F25" t="n">
-        <v>0.8105</v>
+        <v>0.5785</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.1974</v>
+        <v>0.0747</v>
       </c>
       <c r="H25" t="n">
-        <v>0.8105</v>
+        <v>0.5785</v>
       </c>
       <c r="I25" t="n">
-        <v>0.4214</v>
+        <v>0.3124</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.1974</v>
+        <v>0.0747</v>
       </c>
       <c r="K25" t="n">
-        <v>97</v>
+        <v>47</v>
       </c>
       <c r="L25" t="n">
-        <v>52</v>
+        <v>141</v>
       </c>
       <c r="M25" t="n">
-        <v>0.224</v>
+        <v>0.3871</v>
       </c>
       <c r="N25" t="n">
-        <v>149</v>
+        <v>188</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>boltz</t>
+          <t>adreN</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.5653</v>
+        <v>0.6073</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1111</v>
+        <v>0.1193</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3828</v>
+        <v>-0.3477</v>
       </c>
       <c r="E26" t="n">
-        <v>0.5653</v>
+        <v>0.6073</v>
       </c>
       <c r="F26" t="n">
-        <v>0.5131</v>
+        <v>0.8361</v>
       </c>
       <c r="G26" t="n">
-        <v>0.0522</v>
+        <v>-0.2288</v>
       </c>
       <c r="H26" t="n">
-        <v>0.5131</v>
+        <v>0.8361</v>
       </c>
       <c r="I26" t="n">
-        <v>0.2668</v>
+        <v>0.4515</v>
       </c>
       <c r="J26" t="n">
-        <v>0.0522</v>
+        <v>-0.2288</v>
       </c>
       <c r="K26" t="n">
-        <v>47</v>
+        <v>97</v>
       </c>
       <c r="L26" t="n">
-        <v>141</v>
+        <v>52</v>
       </c>
       <c r="M26" t="n">
-        <v>0.319</v>
+        <v>0.2227</v>
       </c>
       <c r="N26" t="n">
-        <v>188</v>
+        <v>149</v>
       </c>
     </row>
     <row r="27">
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.2896</v>
+        <v>0.2471</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0569</v>
+        <v>0.0485</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5073</v>
+        <v>-0.5117</v>
       </c>
       <c r="E27" t="n">
-        <v>0.2896</v>
+        <v>0.2471</v>
       </c>
       <c r="F27" t="n">
-        <v>0.2896</v>
+        <v>0.2471</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2896</v>
+        <v>0.2471</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2896</v>
+        <v>0.2471</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.2896</v>
+        <v>0.2471</v>
       </c>
       <c r="N27" t="n">
         <v>107</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.1531</v>
+        <v>0.115</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0301</v>
+        <v>0.0226</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5689</v>
+        <v>-0.5719</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1531</v>
+        <v>0.115</v>
       </c>
       <c r="F28" t="n">
-        <v>0.1531</v>
+        <v>0.115</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1531</v>
+        <v>0.115</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1594</v>
+        <v>0.118</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.1594</v>
+        <v>0.118</v>
       </c>
       <c r="N28" t="n">
         <v>168</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.1448</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0284</v>
+        <v>0.0178</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5726</v>
+        <v>-0.5829</v>
       </c>
       <c r="E29" t="n">
-        <v>0.1448</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="F29" t="n">
-        <v>0.1448</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1448</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1448</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.1448</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="N29" t="n">
         <v>157</v>
@@ -1784,28 +1784,28 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.113</v>
+        <v>0.0539</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0222</v>
+        <v>0.0106</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.587</v>
+        <v>-0.5997</v>
       </c>
       <c r="E30" t="n">
-        <v>0.113</v>
+        <v>0.0539</v>
       </c>
       <c r="F30" t="n">
-        <v>0.113</v>
+        <v>0.0539</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.113</v>
+        <v>0.0539</v>
       </c>
       <c r="I30" t="n">
-        <v>0.113</v>
+        <v>0.0539</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -1817,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.113</v>
+        <v>0.0539</v>
       </c>
       <c r="N30" t="n">
         <v>82</v>
@@ -1826,93 +1826,93 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>jasonR</t>
+          <t>just9n</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.0341</v>
+        <v>0.0225</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0067</v>
+        <v>0.0044</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6226</v>
+        <v>-0.614</v>
       </c>
       <c r="E31" t="n">
-        <v>0.0341</v>
+        <v>0.0225</v>
       </c>
       <c r="F31" t="n">
-        <v>0.0341</v>
+        <v>0.0225</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.0341</v>
+        <v>0.0225</v>
       </c>
       <c r="I31" t="n">
-        <v>0.0341</v>
+        <v>0.0225</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>82</v>
+        <v>107</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0.0341</v>
+        <v>0.0225</v>
       </c>
       <c r="N31" t="n">
-        <v>82</v>
+        <v>107</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>just9n</t>
+          <t>jasonR</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.0321</v>
+        <v>0.0107</v>
       </c>
       <c r="C32" t="n">
-        <v>0.0063</v>
+        <v>0.0021</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.6235000000000001</v>
+        <v>-0.6193</v>
       </c>
       <c r="E32" t="n">
-        <v>0.0321</v>
+        <v>0.0107</v>
       </c>
       <c r="F32" t="n">
-        <v>0.0321</v>
+        <v>0.0107</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0.0321</v>
+        <v>0.0107</v>
       </c>
       <c r="I32" t="n">
-        <v>0.0321</v>
+        <v>0.0107</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>107</v>
+        <v>82</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0.0321</v>
+        <v>0.0107</v>
       </c>
       <c r="N32" t="n">
-        <v>107</v>
+        <v>82</v>
       </c>
     </row>
     <row r="33">
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.1007</v>
+        <v>-0.1354</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.0198</v>
+        <v>-0.0266</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.6835</v>
+        <v>-0.6858</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.1007</v>
+        <v>-0.1354</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.1007</v>
+        <v>-0.1354</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.1007</v>
+        <v>-0.1354</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.1007</v>
+        <v>-0.1354</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.1007</v>
+        <v>-0.1354</v>
       </c>
       <c r="N33" t="n">
         <v>82</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.1916</v>
+        <v>-0.2314</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.0376</v>
+        <v>-0.0455</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.7245</v>
+        <v>-0.7295</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.1916</v>
+        <v>-0.2314</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.1916</v>
+        <v>-0.2314</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.1916</v>
+        <v>-0.2314</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.1916</v>
+        <v>-0.2314</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.1916</v>
+        <v>-0.2314</v>
       </c>
       <c r="N34" t="n">
         <v>107</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.4653</v>
+        <v>-0.4986</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.0914</v>
+        <v>-0.0979</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8481</v>
+        <v>-0.8512</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.4653</v>
+        <v>-0.4986</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.4653</v>
+        <v>-0.4986</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.4653</v>
+        <v>-0.4986</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.4653</v>
+        <v>-0.4986</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.4653</v>
+        <v>-0.4986</v>
       </c>
       <c r="N35" t="n">
         <v>157</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.7634</v>
+        <v>-0.7798</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.15</v>
+        <v>-0.1532</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9827</v>
+        <v>-0.9792</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.7634</v>
+        <v>-0.7798</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.7634</v>
+        <v>-0.7798</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.7634</v>
+        <v>-0.7798</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.7634</v>
+        <v>-0.7798</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.7634</v>
+        <v>-0.7798</v>
       </c>
       <c r="N36" t="n">
         <v>82</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.9998</v>
+        <v>-1.0365</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.1964</v>
+        <v>-0.2036</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0894</v>
+        <v>-1.096</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.9998</v>
+        <v>-1.0365</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.9998</v>
+        <v>-1.0365</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.9998</v>
+        <v>-1.0365</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.9998</v>
+        <v>-1.0365</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.9998</v>
+        <v>-1.0365</v>
       </c>
       <c r="N37" t="n">
         <v>107</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.0149</v>
+        <v>-1.0705</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.1994</v>
+        <v>-0.2103</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0962</v>
+        <v>-1.1115</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.0149</v>
+        <v>-1.0705</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.0149</v>
+        <v>-1.0705</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.0149</v>
+        <v>-1.0705</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.0149</v>
+        <v>-1.0705</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.0149</v>
+        <v>-1.0705</v>
       </c>
       <c r="N38" t="n">
         <v>157</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.144</v>
+        <v>-1.1859</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.2247</v>
+        <v>-0.233</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1545</v>
+        <v>-1.164</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.144</v>
+        <v>-1.1859</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.144</v>
+        <v>-1.1859</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.144</v>
+        <v>-1.1859</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.144</v>
+        <v>-1.1859</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.144</v>
+        <v>-1.1859</v>
       </c>
       <c r="N39" t="n">
         <v>82</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.3329</v>
+        <v>-1.3466</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.2618</v>
+        <v>-0.2645</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.2398</v>
+        <v>-1.2372</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.3329</v>
+        <v>-1.3466</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.3329</v>
+        <v>-1.3466</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.3329</v>
+        <v>-1.3466</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.3877</v>
+        <v>-1.3813</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.3877</v>
+        <v>-1.3813</v>
       </c>
       <c r="N40" t="n">
         <v>168</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.9545</v>
+        <v>-1.9492</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.384</v>
+        <v>-0.3829</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.5204</v>
+        <v>-1.5115</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.9545</v>
+        <v>-1.9492</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.1289</v>
+        <v>-1.0915</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.8256</v>
+        <v>-0.8577</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.1289</v>
+        <v>-1.0915</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.587</v>
+        <v>-0.5894</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.8256</v>
+        <v>-0.8577</v>
       </c>
       <c r="K41" t="n">
         <v>126</v>
@@ -2323,7 +2323,7 @@
         <v>91</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.4126</v>
+        <v>-1.4471</v>
       </c>
       <c r="N41" t="n">
         <v>217</v>
@@ -2429,10 +2429,10 @@
         <v>1.01</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1321</v>
+        <v>0.1123</v>
       </c>
       <c r="J2" t="n">
-        <v>3.3025</v>
+        <v>2.8075</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>0.87</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1313</v>
+        <v>-0.1528</v>
       </c>
       <c r="J3" t="n">
-        <v>-3.2825</v>
+        <v>-3.82</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.67</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3289</v>
+        <v>-0.3472</v>
       </c>
       <c r="J4" t="n">
-        <v>-8.2225</v>
+        <v>-8.68</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.58</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4131</v>
+        <v>-0.4276</v>
       </c>
       <c r="J5" t="n">
-        <v>-10.3275</v>
+        <v>-10.69</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.53</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4598</v>
+        <v>-0.4717</v>
       </c>
       <c r="J6" t="n">
-        <v>-11.495</v>
+        <v>-11.7925</v>
       </c>
     </row>
     <row r="7">
@@ -2669,10 +2669,10 @@
         <v>1.46</v>
       </c>
       <c r="I8" t="n">
-        <v>1.0713</v>
+        <v>1.0426</v>
       </c>
       <c r="J8" t="n">
-        <v>26.7825</v>
+        <v>26.065</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.3</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7738</v>
+        <v>0.7393999999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>19.345</v>
+        <v>18.485</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.19</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5185999999999999</v>
+        <v>0.5115</v>
       </c>
       <c r="J10" t="n">
-        <v>12.965</v>
+        <v>12.7875</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.0709</v>
+        <v>-0.0492</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.7725</v>
+        <v>-1.23</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.09</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2813</v>
+        <v>0.2732</v>
       </c>
       <c r="J12" t="n">
-        <v>7.0325</v>
+        <v>6.83</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>0.98</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.0155</v>
+        <v>-0.027</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.3875</v>
+        <v>-0.675</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.0702</v>
+        <v>-0.0853</v>
       </c>
       <c r="J14" t="n">
-        <v>-1.755</v>
+        <v>-2.1325</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.63</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.382</v>
+        <v>-0.3953</v>
       </c>
       <c r="J15" t="n">
-        <v>-9.550000000000001</v>
+        <v>-9.8825</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.55</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4564</v>
+        <v>-0.4661</v>
       </c>
       <c r="J16" t="n">
-        <v>-11.41</v>
+        <v>-11.6525</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.57</v>
       </c>
       <c r="I17" t="n">
-        <v>1.2108</v>
+        <v>1.2448</v>
       </c>
       <c r="J17" t="n">
-        <v>30.27</v>
+        <v>31.12</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.35</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8858</v>
+        <v>0.8377</v>
       </c>
       <c r="J18" t="n">
-        <v>22.145</v>
+        <v>20.9425</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.27</v>
       </c>
       <c r="I19" t="n">
-        <v>0.7098</v>
+        <v>0.6821</v>
       </c>
       <c r="J19" t="n">
-        <v>17.745</v>
+        <v>17.0525</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.26</v>
       </c>
       <c r="I20" t="n">
-        <v>0.6874</v>
+        <v>0.662</v>
       </c>
       <c r="J20" t="n">
-        <v>17.185</v>
+        <v>16.55</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.95</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2699</v>
+        <v>-0.2509</v>
       </c>
       <c r="J21" t="n">
-        <v>-6.7475</v>
+        <v>-6.2725</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.85</v>
       </c>
       <c r="I22" t="n">
-        <v>1.2483</v>
+        <v>1.3685</v>
       </c>
       <c r="J22" t="n">
-        <v>27.4626</v>
+        <v>30.107</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.61</v>
       </c>
       <c r="I23" t="n">
-        <v>0.9661999999999999</v>
+        <v>1.0696</v>
       </c>
       <c r="J23" t="n">
-        <v>21.2564</v>
+        <v>23.5312</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.37</v>
       </c>
       <c r="I24" t="n">
-        <v>0.6747</v>
+        <v>0.7533</v>
       </c>
       <c r="J24" t="n">
-        <v>14.8434</v>
+        <v>16.5726</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>1.05</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1107</v>
+        <v>0.1404</v>
       </c>
       <c r="J25" t="n">
-        <v>2.4354</v>
+        <v>3.0888</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>1.01</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.0354</v>
+        <v>-0.0029</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.7788</v>
+        <v>-0.0638</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.0587</v>
+        <v>-0.07630000000000001</v>
       </c>
       <c r="J27" t="n">
-        <v>-1.2914</v>
+        <v>-1.6786</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>0.88</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.1302</v>
+        <v>-0.1494</v>
       </c>
       <c r="J28" t="n">
-        <v>-2.8644</v>
+        <v>-3.2868</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.73</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.2793</v>
+        <v>-0.2977</v>
       </c>
       <c r="J29" t="n">
-        <v>-6.1446</v>
+        <v>-6.5494</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.71</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.2982</v>
+        <v>-0.3162</v>
       </c>
       <c r="J30" t="n">
-        <v>-6.5604</v>
+        <v>-6.9564</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.64</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3643</v>
+        <v>-0.3798</v>
       </c>
       <c r="J31" t="n">
-        <v>-8.0146</v>
+        <v>-8.355600000000001</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.54</v>
       </c>
       <c r="I32" t="n">
-        <v>0.9098000000000001</v>
+        <v>1.0037</v>
       </c>
       <c r="J32" t="n">
-        <v>27.294</v>
+        <v>30.111</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.26</v>
       </c>
       <c r="I33" t="n">
-        <v>0.5457</v>
+        <v>0.6067</v>
       </c>
       <c r="J33" t="n">
-        <v>16.371</v>
+        <v>18.201</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.23</v>
       </c>
       <c r="I34" t="n">
-        <v>0.5056</v>
+        <v>0.5617</v>
       </c>
       <c r="J34" t="n">
-        <v>15.168</v>
+        <v>16.851</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.11</v>
       </c>
       <c r="I35" t="n">
-        <v>0.3206</v>
+        <v>0.3302</v>
       </c>
       <c r="J35" t="n">
-        <v>9.618</v>
+        <v>9.906000000000001</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>1.04</v>
       </c>
       <c r="I36" t="n">
-        <v>0.1104</v>
+        <v>0.1316</v>
       </c>
       <c r="J36" t="n">
-        <v>3.312</v>
+        <v>3.948</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.14</v>
       </c>
       <c r="I37" t="n">
-        <v>0.3483</v>
+        <v>0.3522</v>
       </c>
       <c r="J37" t="n">
-        <v>10.449</v>
+        <v>10.566</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.08</v>
       </c>
       <c r="I38" t="n">
-        <v>0.2335</v>
+        <v>0.2332</v>
       </c>
       <c r="J38" t="n">
-        <v>7.005</v>
+        <v>6.996</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.95</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.0672</v>
+        <v>-0.0794</v>
       </c>
       <c r="J39" t="n">
-        <v>-2.016</v>
+        <v>-2.382</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.82</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.2071</v>
+        <v>-0.2232</v>
       </c>
       <c r="J40" t="n">
-        <v>-6.213</v>
+        <v>-6.696</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.52</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.4915</v>
+        <v>-0.4981</v>
       </c>
       <c r="J41" t="n">
-        <v>-14.745</v>
+        <v>-14.943</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.29</v>
       </c>
       <c r="I42" t="n">
-        <v>0.423</v>
+        <v>0.4655</v>
       </c>
       <c r="J42" t="n">
-        <v>12.267</v>
+        <v>13.4995</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>0.87</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.1578</v>
+        <v>-0.1732</v>
       </c>
       <c r="J43" t="n">
-        <v>-4.5762</v>
+        <v>-5.0228</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.86</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.1682</v>
+        <v>-0.1838</v>
       </c>
       <c r="J44" t="n">
-        <v>-4.8778</v>
+        <v>-5.3302</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.83</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.1991</v>
+        <v>-0.2148</v>
       </c>
       <c r="J45" t="n">
-        <v>-5.7739</v>
+        <v>-6.2292</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.75</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.2786</v>
+        <v>-0.2934</v>
       </c>
       <c r="J46" t="n">
-        <v>-8.0794</v>
+        <v>-8.508599999999999</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.47</v>
       </c>
       <c r="I47" t="n">
-        <v>0.4879</v>
+        <v>0.5563</v>
       </c>
       <c r="J47" t="n">
-        <v>14.1491</v>
+        <v>16.1327</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.35</v>
       </c>
       <c r="I48" t="n">
-        <v>0.4083</v>
+        <v>0.462</v>
       </c>
       <c r="J48" t="n">
-        <v>11.8407</v>
+        <v>13.398</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.15</v>
       </c>
       <c r="I49" t="n">
-        <v>0.222</v>
+        <v>0.2395</v>
       </c>
       <c r="J49" t="n">
-        <v>6.438</v>
+        <v>6.9455</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>1.09</v>
       </c>
       <c r="I50" t="n">
-        <v>0.1404</v>
+        <v>0.1577</v>
       </c>
       <c r="J50" t="n">
-        <v>4.0716</v>
+        <v>4.5733</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.83</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.2275</v>
+        <v>-0.237</v>
       </c>
       <c r="J51" t="n">
-        <v>-6.5975</v>
+        <v>-6.873</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.22</v>
       </c>
       <c r="I52" t="n">
-        <v>0.5125</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="J52" t="n">
-        <v>17.9375</v>
+        <v>19.74</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.18</v>
       </c>
       <c r="I53" t="n">
-        <v>0.4531</v>
+        <v>0.4974</v>
       </c>
       <c r="J53" t="n">
-        <v>15.8585</v>
+        <v>17.409</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.09</v>
       </c>
       <c r="I54" t="n">
-        <v>0.2973</v>
+        <v>0.2998</v>
       </c>
       <c r="J54" t="n">
-        <v>10.4055</v>
+        <v>10.493</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.01</v>
       </c>
       <c r="I55" t="n">
-        <v>0.0349</v>
+        <v>0.0461</v>
       </c>
       <c r="J55" t="n">
-        <v>1.2215</v>
+        <v>1.6135</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.2531</v>
+        <v>-0.2471</v>
       </c>
       <c r="J56" t="n">
-        <v>-8.858499999999999</v>
+        <v>-8.6485</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.23</v>
       </c>
       <c r="I57" t="n">
-        <v>0.4204</v>
+        <v>0.4652</v>
       </c>
       <c r="J57" t="n">
-        <v>14.714</v>
+        <v>16.282</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.18</v>
       </c>
       <c r="I58" t="n">
-        <v>0.3672</v>
+        <v>0.3909</v>
       </c>
       <c r="J58" t="n">
-        <v>12.852</v>
+        <v>13.6815</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.05</v>
       </c>
       <c r="I59" t="n">
-        <v>0.1326</v>
+        <v>0.1431</v>
       </c>
       <c r="J59" t="n">
-        <v>4.641</v>
+        <v>5.0085</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.92</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.116</v>
+        <v>-0.127</v>
       </c>
       <c r="J60" t="n">
-        <v>-4.06</v>
+        <v>-4.445</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.82</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.2234</v>
+        <v>-0.236</v>
       </c>
       <c r="J61" t="n">
-        <v>-7.819</v>
+        <v>-8.26</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.31</v>
       </c>
       <c r="I62" t="n">
-        <v>0.6236</v>
+        <v>0.6906</v>
       </c>
       <c r="J62" t="n">
-        <v>16.8372</v>
+        <v>18.6462</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.26</v>
       </c>
       <c r="I63" t="n">
-        <v>0.5547</v>
+        <v>0.6145</v>
       </c>
       <c r="J63" t="n">
-        <v>14.9769</v>
+        <v>16.5915</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.19</v>
       </c>
       <c r="I64" t="n">
-        <v>0.4558</v>
+        <v>0.5036</v>
       </c>
       <c r="J64" t="n">
-        <v>12.3066</v>
+        <v>13.5972</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.11</v>
       </c>
       <c r="I65" t="n">
-        <v>0.3331</v>
+        <v>0.3407</v>
       </c>
       <c r="J65" t="n">
-        <v>8.9937</v>
+        <v>9.1989</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.98</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.1371</v>
+        <v>-0.1295</v>
       </c>
       <c r="J66" t="n">
-        <v>-3.7017</v>
+        <v>-3.4965</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.62</v>
       </c>
       <c r="I67" t="n">
-        <v>0.8102</v>
+        <v>0.9024</v>
       </c>
       <c r="J67" t="n">
-        <v>21.8754</v>
+        <v>24.3648</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.28</v>
       </c>
       <c r="I68" t="n">
-        <v>0.4785</v>
+        <v>0.5309</v>
       </c>
       <c r="J68" t="n">
-        <v>12.9195</v>
+        <v>14.3343</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.75</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.2892</v>
+        <v>-0.3017</v>
       </c>
       <c r="J69" t="n">
-        <v>-7.8084</v>
+        <v>-8.145899999999999</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.73</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.3085</v>
+        <v>-0.3205</v>
       </c>
       <c r="J70" t="n">
-        <v>-8.329499999999999</v>
+        <v>-8.653499999999999</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.66</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.3747</v>
+        <v>-0.3847</v>
       </c>
       <c r="J71" t="n">
-        <v>-10.1169</v>
+        <v>-10.3869</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.91</v>
       </c>
       <c r="I72" t="n">
-        <v>1.5489</v>
+        <v>1.5509</v>
       </c>
       <c r="J72" t="n">
-        <v>29.4291</v>
+        <v>29.4671</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.81</v>
       </c>
       <c r="I73" t="n">
-        <v>1.438</v>
+        <v>1.4339</v>
       </c>
       <c r="J73" t="n">
-        <v>27.322</v>
+        <v>27.2441</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.55</v>
       </c>
       <c r="I74" t="n">
-        <v>1.1463</v>
+        <v>1.1211</v>
       </c>
       <c r="J74" t="n">
-        <v>21.7797</v>
+        <v>21.3009</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1.48</v>
       </c>
       <c r="I75" t="n">
-        <v>1.0642</v>
+        <v>1.0294</v>
       </c>
       <c r="J75" t="n">
-        <v>20.2198</v>
+        <v>19.5586</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>1.12</v>
       </c>
       <c r="I76" t="n">
-        <v>0.2774</v>
+        <v>0.305</v>
       </c>
       <c r="J76" t="n">
-        <v>5.2706</v>
+        <v>5.795</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>0.98</v>
       </c>
       <c r="I77" t="n">
-        <v>0.1608</v>
+        <v>0.09379999999999999</v>
       </c>
       <c r="J77" t="n">
-        <v>3.0552</v>
+        <v>1.7822</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>0.55</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.4113</v>
+        <v>-0.431</v>
       </c>
       <c r="J78" t="n">
-        <v>-7.8147</v>
+        <v>-8.189</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.51</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.4474</v>
+        <v>-0.4649</v>
       </c>
       <c r="J79" t="n">
-        <v>-8.5006</v>
+        <v>-8.8331</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.48</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.4754</v>
+        <v>-0.4911</v>
       </c>
       <c r="J80" t="n">
-        <v>-9.0326</v>
+        <v>-9.3309</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.27</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.6787</v>
+        <v>-0.678</v>
       </c>
       <c r="J81" t="n">
-        <v>-12.8953</v>
+        <v>-12.882</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.71</v>
       </c>
       <c r="I82" t="n">
-        <v>1.3993</v>
+        <v>1.3793</v>
       </c>
       <c r="J82" t="n">
-        <v>36.3818</v>
+        <v>35.8618</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.41</v>
       </c>
       <c r="I83" t="n">
-        <v>1.0169</v>
+        <v>0.9628</v>
       </c>
       <c r="J83" t="n">
-        <v>26.4394</v>
+        <v>25.0328</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.32</v>
       </c>
       <c r="I84" t="n">
-        <v>0.8343</v>
+        <v>0.7897</v>
       </c>
       <c r="J84" t="n">
-        <v>21.6918</v>
+        <v>20.5322</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.88</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.4649</v>
+        <v>-0.4354</v>
       </c>
       <c r="J85" t="n">
-        <v>-12.0874</v>
+        <v>-11.3204</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.77</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.7558</v>
+        <v>-0.6961000000000001</v>
       </c>
       <c r="J86" t="n">
-        <v>-19.6508</v>
+        <v>-18.0986</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.04</v>
       </c>
       <c r="I87" t="n">
-        <v>0.1521</v>
+        <v>0.1507</v>
       </c>
       <c r="J87" t="n">
-        <v>3.9546</v>
+        <v>3.9182</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.96</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.0497</v>
+        <v>-0.0622</v>
       </c>
       <c r="J88" t="n">
-        <v>-1.2922</v>
+        <v>-1.6172</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.85</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.1731</v>
+        <v>-0.19</v>
       </c>
       <c r="J89" t="n">
-        <v>-4.5006</v>
+        <v>-4.94</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.8</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.2231</v>
+        <v>-0.2401</v>
       </c>
       <c r="J90" t="n">
-        <v>-5.8006</v>
+        <v>-6.2426</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.7</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.3202</v>
+        <v>-0.3351</v>
       </c>
       <c r="J91" t="n">
-        <v>-8.325200000000001</v>
+        <v>-8.7126</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.21</v>
       </c>
       <c r="I92" t="n">
-        <v>0.6258</v>
+        <v>0.5955</v>
       </c>
       <c r="J92" t="n">
-        <v>21.903</v>
+        <v>20.8425</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.17</v>
       </c>
       <c r="I93" t="n">
-        <v>0.5228</v>
+        <v>0.5036</v>
       </c>
       <c r="J93" t="n">
-        <v>18.298</v>
+        <v>17.626</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.01</v>
       </c>
       <c r="I94" t="n">
-        <v>0.0441</v>
+        <v>0.0525</v>
       </c>
       <c r="J94" t="n">
-        <v>1.5435</v>
+        <v>1.8375</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.2427</v>
+        <v>-0.2399</v>
       </c>
       <c r="J95" t="n">
-        <v>-8.4945</v>
+        <v>-8.3965</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.92</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.3042</v>
+        <v>-0.2974</v>
       </c>
       <c r="J96" t="n">
-        <v>-10.647</v>
+        <v>-10.409</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.08</v>
       </c>
       <c r="I97" t="n">
-        <v>0.2045</v>
+        <v>0.2121</v>
       </c>
       <c r="J97" t="n">
-        <v>7.1575</v>
+        <v>7.4235</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.08</v>
       </c>
       <c r="I98" t="n">
-        <v>0.2045</v>
+        <v>0.2121</v>
       </c>
       <c r="J98" t="n">
-        <v>7.1575</v>
+        <v>7.4235</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.98</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.0361</v>
+        <v>-0.0428</v>
       </c>
       <c r="J99" t="n">
-        <v>-1.2635</v>
+        <v>-1.498</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.0883</v>
+        <v>-0.0992</v>
       </c>
       <c r="J100" t="n">
-        <v>-3.0905</v>
+        <v>-3.472</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.93</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.1002</v>
+        <v>-0.1117</v>
       </c>
       <c r="J101" t="n">
-        <v>-3.507</v>
+        <v>-3.9095</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.25</v>
       </c>
       <c r="I102" t="n">
-        <v>0.3992</v>
+        <v>0.4007</v>
       </c>
       <c r="J102" t="n">
-        <v>11.1776</v>
+        <v>11.2196</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.1</v>
       </c>
       <c r="I103" t="n">
-        <v>0.1846</v>
+        <v>0.1948</v>
       </c>
       <c r="J103" t="n">
-        <v>5.1688</v>
+        <v>5.4544</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.1</v>
       </c>
       <c r="I104" t="n">
-        <v>0.1846</v>
+        <v>0.1948</v>
       </c>
       <c r="J104" t="n">
-        <v>5.1688</v>
+        <v>5.4544</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>1.02</v>
       </c>
       <c r="I105" t="n">
-        <v>0.0485</v>
+        <v>0.056</v>
       </c>
       <c r="J105" t="n">
-        <v>1.358</v>
+        <v>1.568</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.64</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.3948</v>
+        <v>-0.4038</v>
       </c>
       <c r="J106" t="n">
-        <v>-11.0544</v>
+        <v>-11.3064</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.53</v>
       </c>
       <c r="I107" t="n">
-        <v>0.6807</v>
+        <v>0.6743</v>
       </c>
       <c r="J107" t="n">
-        <v>19.0596</v>
+        <v>18.8804</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.3</v>
       </c>
       <c r="I108" t="n">
-        <v>0.4156</v>
+        <v>0.4256</v>
       </c>
       <c r="J108" t="n">
-        <v>11.6368</v>
+        <v>11.9168</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.01</v>
       </c>
       <c r="I109" t="n">
-        <v>0.0157</v>
+        <v>0.0239</v>
       </c>
       <c r="J109" t="n">
-        <v>0.4396</v>
+        <v>0.6692</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.99</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.0301</v>
+        <v>-0.0326</v>
       </c>
       <c r="J110" t="n">
-        <v>-0.8428</v>
+        <v>-0.9127999999999999</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.68</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.3656</v>
+        <v>-0.3742</v>
       </c>
       <c r="J111" t="n">
-        <v>-10.2368</v>
+        <v>-10.4776</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.53</v>
       </c>
       <c r="I112" t="n">
-        <v>1.1743</v>
+        <v>1.1404</v>
       </c>
       <c r="J112" t="n">
-        <v>31.7061</v>
+        <v>30.7908</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.33</v>
       </c>
       <c r="I113" t="n">
-        <v>0.8558</v>
+        <v>0.8088</v>
       </c>
       <c r="J113" t="n">
-        <v>23.1066</v>
+        <v>21.8376</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.23</v>
       </c>
       <c r="I114" t="n">
-        <v>0.6268</v>
+        <v>0.606</v>
       </c>
       <c r="J114" t="n">
-        <v>16.9236</v>
+        <v>16.362</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1.2</v>
       </c>
       <c r="I115" t="n">
-        <v>0.5571</v>
+        <v>0.5432</v>
       </c>
       <c r="J115" t="n">
-        <v>15.0417</v>
+        <v>14.6664</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.82</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.6283</v>
+        <v>-0.5826</v>
       </c>
       <c r="J116" t="n">
-        <v>-16.9641</v>
+        <v>-15.7302</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>0.95</v>
       </c>
       <c r="I117" t="n">
-        <v>-0.0549</v>
+        <v>-0.0699</v>
       </c>
       <c r="J117" t="n">
-        <v>-1.4823</v>
+        <v>-1.8873</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>0.88</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.1375</v>
+        <v>-0.1551</v>
       </c>
       <c r="J118" t="n">
-        <v>-3.7125</v>
+        <v>-4.1877</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.83</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.1891</v>
+        <v>-0.2071</v>
       </c>
       <c r="J119" t="n">
-        <v>-5.1057</v>
+        <v>-5.5917</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.76</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.2564</v>
+        <v>-0.2741</v>
       </c>
       <c r="J120" t="n">
-        <v>-6.9228</v>
+        <v>-7.4007</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.7</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.3139</v>
+        <v>-0.3302</v>
       </c>
       <c r="J121" t="n">
-        <v>-8.475300000000001</v>
+        <v>-8.9154</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.27</v>
       </c>
       <c r="I122" t="n">
-        <v>0.5483</v>
+        <v>0.5376</v>
       </c>
       <c r="J122" t="n">
-        <v>19.1905</v>
+        <v>18.816</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.25</v>
       </c>
       <c r="I123" t="n">
-        <v>0.5135</v>
+        <v>0.5056</v>
       </c>
       <c r="J123" t="n">
-        <v>17.9725</v>
+        <v>17.696</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.01</v>
       </c>
       <c r="I124" t="n">
-        <v>0.0315</v>
+        <v>0.039</v>
       </c>
       <c r="J124" t="n">
-        <v>1.1025</v>
+        <v>1.365</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.97</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.0547</v>
+        <v>-0.0618</v>
       </c>
       <c r="J125" t="n">
-        <v>-1.9145</v>
+        <v>-2.163</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.74</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.3033</v>
+        <v>-0.3146</v>
       </c>
       <c r="J126" t="n">
-        <v>-10.6155</v>
+        <v>-11.011</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.29</v>
       </c>
       <c r="I127" t="n">
-        <v>0.795</v>
+        <v>0.7497</v>
       </c>
       <c r="J127" t="n">
-        <v>27.825</v>
+        <v>26.2395</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.23</v>
       </c>
       <c r="I128" t="n">
-        <v>0.6505</v>
+        <v>0.6223</v>
       </c>
       <c r="J128" t="n">
-        <v>22.7675</v>
+        <v>21.7805</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.21</v>
       </c>
       <c r="I129" t="n">
-        <v>0.6014</v>
+        <v>0.5786</v>
       </c>
       <c r="J129" t="n">
-        <v>21.049</v>
+        <v>20.251</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1.01</v>
       </c>
       <c r="I130" t="n">
-        <v>0.0262</v>
+        <v>0.0401</v>
       </c>
       <c r="J130" t="n">
-        <v>0.917</v>
+        <v>1.4035</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.87</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.4683</v>
+        <v>-0.4436</v>
       </c>
       <c r="J131" t="n">
-        <v>-16.3905</v>
+        <v>-15.526</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.55</v>
       </c>
       <c r="I132" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.6803</v>
       </c>
       <c r="J132" t="n">
-        <v>18.468</v>
+        <v>18.3681</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.3</v>
       </c>
       <c r="I133" t="n">
-        <v>0.4029</v>
+        <v>0.416</v>
       </c>
       <c r="J133" t="n">
-        <v>10.8783</v>
+        <v>11.232</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.1</v>
       </c>
       <c r="I134" t="n">
-        <v>0.1552</v>
+        <v>0.1725</v>
       </c>
       <c r="J134" t="n">
-        <v>4.1904</v>
+        <v>4.6575</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.97</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.0675</v>
+        <v>-0.0717</v>
       </c>
       <c r="J135" t="n">
-        <v>-1.8225</v>
+        <v>-1.9359</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.95</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.09379999999999999</v>
+        <v>-0.1</v>
       </c>
       <c r="J136" t="n">
-        <v>-2.5326</v>
+        <v>-2.7</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.26</v>
       </c>
       <c r="I137" t="n">
-        <v>0.4334</v>
+        <v>0.429</v>
       </c>
       <c r="J137" t="n">
-        <v>11.7018</v>
+        <v>11.583</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.09</v>
       </c>
       <c r="I138" t="n">
-        <v>0.1831</v>
+        <v>0.1899</v>
       </c>
       <c r="J138" t="n">
-        <v>4.9437</v>
+        <v>5.1273</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.07</v>
       </c>
       <c r="I139" t="n">
-        <v>0.1502</v>
+        <v>0.1572</v>
       </c>
       <c r="J139" t="n">
-        <v>4.0554</v>
+        <v>4.2444</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.76</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.2726</v>
+        <v>-0.2867</v>
       </c>
       <c r="J140" t="n">
-        <v>-7.3602</v>
+        <v>-7.7409</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.57</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.4513</v>
+        <v>-0.4592</v>
       </c>
       <c r="J141" t="n">
-        <v>-12.1851</v>
+        <v>-12.3984</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.21</v>
       </c>
       <c r="I142" t="n">
-        <v>0.4879</v>
+        <v>0.4733</v>
       </c>
       <c r="J142" t="n">
-        <v>11.7096</v>
+        <v>11.3592</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>0.95</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-0.0809</v>
       </c>
       <c r="J143" t="n">
-        <v>-1.656</v>
+        <v>-1.9416</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.89</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.1364</v>
+        <v>-0.1514</v>
       </c>
       <c r="J144" t="n">
-        <v>-3.2736</v>
+        <v>-3.6336</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.85</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.1784</v>
+        <v>-0.1941</v>
       </c>
       <c r="J145" t="n">
-        <v>-4.2816</v>
+        <v>-4.6584</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.336</v>
+        <v>-0.3492</v>
       </c>
       <c r="J146" t="n">
-        <v>-8.064</v>
+        <v>-8.380800000000001</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.82</v>
       </c>
       <c r="I147" t="n">
-        <v>1.5065</v>
+        <v>1.4962</v>
       </c>
       <c r="J147" t="n">
-        <v>36.156</v>
+        <v>35.9088</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.57</v>
       </c>
       <c r="I148" t="n">
-        <v>1.2058</v>
+        <v>1.1776</v>
       </c>
       <c r="J148" t="n">
-        <v>28.9392</v>
+        <v>28.2624</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.26</v>
       </c>
       <c r="I149" t="n">
-        <v>0.6832</v>
+        <v>0.6592</v>
       </c>
       <c r="J149" t="n">
-        <v>16.3968</v>
+        <v>15.8208</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.0737</v>
+        <v>-0.0511</v>
       </c>
       <c r="J150" t="n">
-        <v>-1.7688</v>
+        <v>-1.2264</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.87</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.5125999999999999</v>
+        <v>-0.4747</v>
       </c>
       <c r="J151" t="n">
-        <v>-12.3024</v>
+        <v>-11.3928</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.32</v>
       </c>
       <c r="I152" t="n">
-        <v>0.6434</v>
+        <v>0.6226</v>
       </c>
       <c r="J152" t="n">
-        <v>22.519</v>
+        <v>21.791</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.07</v>
       </c>
       <c r="I153" t="n">
-        <v>0.179</v>
+        <v>0.1883</v>
       </c>
       <c r="J153" t="n">
-        <v>6.265</v>
+        <v>6.5905</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.05</v>
       </c>
       <c r="I154" t="n">
-        <v>0.1352</v>
+        <v>0.145</v>
       </c>
       <c r="J154" t="n">
-        <v>4.732</v>
+        <v>5.075</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>1.03</v>
       </c>
       <c r="I155" t="n">
-        <v>0.0885</v>
+        <v>0.09760000000000001</v>
       </c>
       <c r="J155" t="n">
-        <v>3.0975</v>
+        <v>3.416</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.64</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.3948</v>
+        <v>-0.4038</v>
       </c>
       <c r="J156" t="n">
-        <v>-13.818</v>
+        <v>-14.133</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.34</v>
       </c>
       <c r="I157" t="n">
-        <v>0.903</v>
+        <v>0.8458</v>
       </c>
       <c r="J157" t="n">
-        <v>31.605</v>
+        <v>29.603</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.34</v>
       </c>
       <c r="I158" t="n">
-        <v>0.903</v>
+        <v>0.8458</v>
       </c>
       <c r="J158" t="n">
-        <v>31.605</v>
+        <v>29.603</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.13</v>
       </c>
       <c r="I159" t="n">
-        <v>0.3957</v>
+        <v>0.3933</v>
       </c>
       <c r="J159" t="n">
-        <v>13.8495</v>
+        <v>13.7655</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.96</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.2031</v>
+        <v>-0.1956</v>
       </c>
       <c r="J160" t="n">
-        <v>-7.1085</v>
+        <v>-6.846</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.96</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.2031</v>
+        <v>-0.1956</v>
       </c>
       <c r="J161" t="n">
-        <v>-7.1085</v>
+        <v>-6.846</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.05</v>
       </c>
       <c r="I162" t="n">
-        <v>0.2209</v>
+        <v>0.2076</v>
       </c>
       <c r="J162" t="n">
-        <v>5.7434</v>
+        <v>5.3976</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>0.85</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.1615</v>
+        <v>-0.1812</v>
       </c>
       <c r="J163" t="n">
-        <v>-4.199</v>
+        <v>-4.7112</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.7</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.3065</v>
+        <v>-0.3245</v>
       </c>
       <c r="J164" t="n">
-        <v>-7.969</v>
+        <v>-8.436999999999999</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.66</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.3443</v>
+        <v>-0.3609</v>
       </c>
       <c r="J165" t="n">
-        <v>-8.9518</v>
+        <v>-9.3834</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.6</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.4006</v>
+        <v>-0.4147</v>
       </c>
       <c r="J166" t="n">
-        <v>-10.4156</v>
+        <v>-10.7822</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>2.03</v>
       </c>
       <c r="I167" t="n">
-        <v>1.7657</v>
+        <v>1.7647</v>
       </c>
       <c r="J167" t="n">
-        <v>45.9082</v>
+        <v>45.8822</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.15</v>
       </c>
       <c r="I168" t="n">
-        <v>0.4231</v>
+        <v>0.4239</v>
       </c>
       <c r="J168" t="n">
-        <v>11.0006</v>
+        <v>11.0214</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.13</v>
       </c>
       <c r="I169" t="n">
-        <v>0.3702</v>
+        <v>0.3758</v>
       </c>
       <c r="J169" t="n">
-        <v>9.6252</v>
+        <v>9.770799999999999</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1.09</v>
       </c>
       <c r="I170" t="n">
-        <v>0.2588</v>
+        <v>0.2733</v>
       </c>
       <c r="J170" t="n">
-        <v>6.7288</v>
+        <v>7.1058</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.92</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.36</v>
+        <v>-0.3365</v>
       </c>
       <c r="J171" t="n">
-        <v>-9.359999999999999</v>
+        <v>-8.749000000000001</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.57</v>
       </c>
       <c r="I172" t="n">
-        <v>1.2418</v>
+        <v>1.2094</v>
       </c>
       <c r="J172" t="n">
-        <v>32.2868</v>
+        <v>31.4444</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.26</v>
       </c>
       <c r="I173" t="n">
-        <v>0.7114</v>
+        <v>0.6784</v>
       </c>
       <c r="J173" t="n">
-        <v>18.4964</v>
+        <v>17.6384</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.18</v>
       </c>
       <c r="I174" t="n">
-        <v>0.5181</v>
+        <v>0.5058</v>
       </c>
       <c r="J174" t="n">
-        <v>13.4706</v>
+        <v>13.1508</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>1.05</v>
       </c>
       <c r="I175" t="n">
-        <v>0.1622</v>
+        <v>0.1763</v>
       </c>
       <c r="J175" t="n">
-        <v>4.2172</v>
+        <v>4.5838</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.74</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.8173</v>
+        <v>-0.7526</v>
       </c>
       <c r="J176" t="n">
-        <v>-21.2498</v>
+        <v>-19.5676</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.36</v>
       </c>
       <c r="I177" t="n">
-        <v>0.717</v>
+        <v>0.6882</v>
       </c>
       <c r="J177" t="n">
-        <v>18.642</v>
+        <v>17.8932</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.28</v>
       </c>
       <c r="I178" t="n">
-        <v>0.5793</v>
+        <v>0.5634</v>
       </c>
       <c r="J178" t="n">
-        <v>15.0618</v>
+        <v>14.6484</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>0.9</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.1351</v>
+        <v>-0.1476</v>
       </c>
       <c r="J179" t="n">
-        <v>-3.5126</v>
+        <v>-3.8376</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.78</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.2598</v>
+        <v>-0.2728</v>
       </c>
       <c r="J180" t="n">
-        <v>-6.7548</v>
+        <v>-7.0928</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.72</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.3181</v>
+        <v>-0.3299</v>
       </c>
       <c r="J181" t="n">
-        <v>-8.2706</v>
+        <v>-8.577400000000001</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.84</v>
       </c>
       <c r="I182" t="n">
-        <v>1.4831</v>
+        <v>1.4794</v>
       </c>
       <c r="J182" t="n">
-        <v>28.1789</v>
+        <v>28.1086</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.53</v>
       </c>
       <c r="I183" t="n">
-        <v>1.128</v>
+        <v>1.1</v>
       </c>
       <c r="J183" t="n">
-        <v>21.432</v>
+        <v>20.9</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.5</v>
       </c>
       <c r="I184" t="n">
-        <v>1.0938</v>
+        <v>1.0623</v>
       </c>
       <c r="J184" t="n">
-        <v>20.7822</v>
+        <v>20.1837</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>1.35</v>
       </c>
       <c r="I185" t="n">
-        <v>0.8467</v>
+        <v>0.8109</v>
       </c>
       <c r="J185" t="n">
-        <v>16.0873</v>
+        <v>15.4071</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>1.31</v>
       </c>
       <c r="I186" t="n">
-        <v>0.7576000000000001</v>
+        <v>0.7327</v>
       </c>
       <c r="J186" t="n">
-        <v>14.3944</v>
+        <v>13.9213</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.14</v>
       </c>
       <c r="I187" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.5068</v>
       </c>
       <c r="J187" t="n">
-        <v>10.773</v>
+        <v>9.629200000000001</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>0.68</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.3008</v>
+        <v>-0.3239</v>
       </c>
       <c r="J188" t="n">
-        <v>-5.7152</v>
+        <v>-6.1541</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.44</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.5233</v>
+        <v>-0.5341</v>
       </c>
       <c r="J189" t="n">
-        <v>-9.9427</v>
+        <v>-10.1479</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.41</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.5518999999999999</v>
+        <v>-0.5606</v>
       </c>
       <c r="J190" t="n">
-        <v>-10.4861</v>
+        <v>-10.6514</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.37</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.5901</v>
+        <v>-0.5959</v>
       </c>
       <c r="J191" t="n">
-        <v>-11.2119</v>
+        <v>-11.3221</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.76</v>
       </c>
       <c r="I192" t="n">
-        <v>1.4338</v>
+        <v>1.42</v>
       </c>
       <c r="J192" t="n">
-        <v>37.2788</v>
+        <v>36.92</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.33</v>
       </c>
       <c r="I193" t="n">
-        <v>0.8362000000000001</v>
+        <v>0.7953</v>
       </c>
       <c r="J193" t="n">
-        <v>21.7412</v>
+        <v>20.6778</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.26</v>
       </c>
       <c r="I194" t="n">
-        <v>0.6821</v>
+        <v>0.6585</v>
       </c>
       <c r="J194" t="n">
-        <v>17.7346</v>
+        <v>17.121</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.11</v>
       </c>
       <c r="I195" t="n">
-        <v>0.3049</v>
+        <v>0.3182</v>
       </c>
       <c r="J195" t="n">
-        <v>7.9274</v>
+        <v>8.273199999999999</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>1.09</v>
       </c>
       <c r="I196" t="n">
-        <v>0.2481</v>
+        <v>0.2658</v>
       </c>
       <c r="J196" t="n">
-        <v>6.4506</v>
+        <v>6.9108</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.08</v>
       </c>
       <c r="I197" t="n">
-        <v>0.3146</v>
+        <v>0.293</v>
       </c>
       <c r="J197" t="n">
-        <v>8.179600000000001</v>
+        <v>7.618</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I198" t="n">
-        <v>-0.197</v>
+        <v>-0.2178</v>
       </c>
       <c r="J198" t="n">
-        <v>-5.122</v>
+        <v>-5.6628</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.76</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.2467</v>
+        <v>-0.2667</v>
       </c>
       <c r="J199" t="n">
-        <v>-6.4142</v>
+        <v>-6.9342</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.57</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.4231</v>
+        <v>-0.437</v>
       </c>
       <c r="J200" t="n">
-        <v>-11.0006</v>
+        <v>-11.362</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.46</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.5255</v>
+        <v>-0.5332</v>
       </c>
       <c r="J201" t="n">
-        <v>-13.663</v>
+        <v>-13.8632</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>0.96</v>
       </c>
       <c r="I202" t="n">
-        <v>0.0755</v>
+        <v>0.0162</v>
       </c>
       <c r="J202" t="n">
-        <v>1.2835</v>
+        <v>0.2754</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>0.75</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.2204</v>
+        <v>-0.2482</v>
       </c>
       <c r="J203" t="n">
-        <v>-3.7468</v>
+        <v>-4.2194</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.53</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.4335</v>
+        <v>-0.4511</v>
       </c>
       <c r="J204" t="n">
-        <v>-7.3695</v>
+        <v>-7.6687</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.34</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.6145</v>
+        <v>-0.6188</v>
       </c>
       <c r="J205" t="n">
-        <v>-10.4465</v>
+        <v>-10.5196</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.33</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.6242</v>
+        <v>-0.6277</v>
       </c>
       <c r="J206" t="n">
-        <v>-10.6114</v>
+        <v>-10.6709</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>2.03</v>
       </c>
       <c r="I207" t="n">
-        <v>1.6649</v>
+        <v>1.6753</v>
       </c>
       <c r="J207" t="n">
-        <v>28.3033</v>
+        <v>28.4801</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.83</v>
       </c>
       <c r="I208" t="n">
-        <v>1.4484</v>
+        <v>1.447</v>
       </c>
       <c r="J208" t="n">
-        <v>24.6228</v>
+        <v>24.599</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.71</v>
       </c>
       <c r="I209" t="n">
-        <v>1.317</v>
+        <v>1.3069</v>
       </c>
       <c r="J209" t="n">
-        <v>22.389</v>
+        <v>22.2173</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.43</v>
       </c>
       <c r="I210" t="n">
-        <v>0.9821</v>
+        <v>0.9404</v>
       </c>
       <c r="J210" t="n">
-        <v>16.6957</v>
+        <v>15.9868</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>1.29</v>
       </c>
       <c r="I211" t="n">
-        <v>0.6831</v>
+        <v>0.6723</v>
       </c>
       <c r="J211" t="n">
-        <v>11.6127</v>
+        <v>11.4291</v>
       </c>
     </row>
     <row r="212">
@@ -10869,10 +10869,10 @@
         <v>1.52</v>
       </c>
       <c r="I213" t="n">
-        <v>1.1274</v>
+        <v>1.0969</v>
       </c>
       <c r="J213" t="n">
-        <v>23.6754</v>
+        <v>23.0349</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.29</v>
       </c>
       <c r="I214" t="n">
-        <v>0.7321</v>
+        <v>0.7065</v>
       </c>
       <c r="J214" t="n">
-        <v>15.3741</v>
+        <v>14.8365</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>1.22</v>
       </c>
       <c r="I215" t="n">
-        <v>0.5677</v>
+        <v>0.5605</v>
       </c>
       <c r="J215" t="n">
-        <v>11.9217</v>
+        <v>11.7705</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>1.05</v>
       </c>
       <c r="I216" t="n">
-        <v>0.1046</v>
+        <v>0.1361</v>
       </c>
       <c r="J216" t="n">
-        <v>2.1966</v>
+        <v>2.8581</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>0.97</v>
       </c>
       <c r="I217" t="n">
-        <v>-0.0037</v>
+        <v>-0.0222</v>
       </c>
       <c r="J217" t="n">
-        <v>-0.07770000000000001</v>
+        <v>-0.4662</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>0.96</v>
       </c>
       <c r="I218" t="n">
-        <v>-0.0182</v>
+        <v>-0.0376</v>
       </c>
       <c r="J218" t="n">
-        <v>-0.3822</v>
+        <v>-0.7896</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.73</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.2735</v>
+        <v>-0.2933</v>
       </c>
       <c r="J219" t="n">
-        <v>-5.7435</v>
+        <v>-6.1593</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.53</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.4592</v>
+        <v>-0.4712</v>
       </c>
       <c r="J220" t="n">
-        <v>-9.6432</v>
+        <v>-9.895200000000001</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.45</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.5337</v>
+        <v>-0.541</v>
       </c>
       <c r="J221" t="n">
-        <v>-11.2077</v>
+        <v>-11.361</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.68</v>
       </c>
       <c r="I222" t="n">
-        <v>1.3308</v>
+        <v>1.3124</v>
       </c>
       <c r="J222" t="n">
-        <v>27.9468</v>
+        <v>27.5604</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.51</v>
       </c>
       <c r="I223" t="n">
-        <v>1.125</v>
+        <v>1.0922</v>
       </c>
       <c r="J223" t="n">
-        <v>23.625</v>
+        <v>22.9362</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.43</v>
       </c>
       <c r="I224" t="n">
-        <v>1.0226</v>
+        <v>0.9747</v>
       </c>
       <c r="J224" t="n">
-        <v>21.4746</v>
+        <v>20.4687</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1.27</v>
       </c>
       <c r="I225" t="n">
-        <v>0.699</v>
+        <v>0.6747</v>
       </c>
       <c r="J225" t="n">
-        <v>14.679</v>
+        <v>14.1687</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.82</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.6544</v>
+        <v>-0.6011</v>
       </c>
       <c r="J226" t="n">
-        <v>-13.7424</v>
+        <v>-12.6231</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>0.87</v>
       </c>
       <c r="I227" t="n">
-        <v>-0.1182</v>
+        <v>-0.1425</v>
       </c>
       <c r="J227" t="n">
-        <v>-2.4822</v>
+        <v>-2.9925</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>0.86</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.1298</v>
+        <v>-0.154</v>
       </c>
       <c r="J228" t="n">
-        <v>-2.7258</v>
+        <v>-3.234</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.67</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.322</v>
+        <v>-0.3419</v>
       </c>
       <c r="J229" t="n">
-        <v>-6.762</v>
+        <v>-7.1799</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.58</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.4049</v>
+        <v>-0.4212</v>
       </c>
       <c r="J230" t="n">
-        <v>-8.5029</v>
+        <v>-8.8452</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.43</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.5454</v>
+        <v>-0.5528999999999999</v>
       </c>
       <c r="J231" t="n">
-        <v>-11.4534</v>
+        <v>-11.6109</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/1954/event_1954_evp_summary.xlsx
+++ b/database/event/1954/event_1954_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.0927</v>
+        <v>7.0767</v>
       </c>
       <c r="C2" t="n">
-        <v>1.3934</v>
+        <v>1.3902</v>
       </c>
       <c r="D2" t="n">
-        <v>2.6045</v>
+        <v>2.618</v>
       </c>
       <c r="E2" t="n">
-        <v>7.0927</v>
+        <v>7.0767</v>
       </c>
       <c r="F2" t="n">
-        <v>3.0504</v>
+        <v>3.0643</v>
       </c>
       <c r="G2" t="n">
-        <v>4.0423</v>
+        <v>4.0124</v>
       </c>
       <c r="H2" t="n">
-        <v>5.1701</v>
+        <v>5.0621</v>
       </c>
       <c r="I2" t="n">
-        <v>2.7918</v>
+        <v>2.8422</v>
       </c>
       <c r="J2" t="n">
-        <v>4.0423</v>
+        <v>4.0124</v>
       </c>
       <c r="K2" t="n">
         <v>40</v>
@@ -529,7 +529,7 @@
         <v>102</v>
       </c>
       <c r="M2" t="n">
-        <v>6.834099999999999</v>
+        <v>6.8546</v>
       </c>
       <c r="N2" t="n">
         <v>142</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.1877</v>
+        <v>6.2778</v>
       </c>
       <c r="C3" t="n">
-        <v>1.2156</v>
+        <v>1.2333</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1926</v>
+        <v>2.254</v>
       </c>
       <c r="E3" t="n">
-        <v>6.1877</v>
+        <v>6.2778</v>
       </c>
       <c r="F3" t="n">
-        <v>2.2733</v>
+        <v>2.3648</v>
       </c>
       <c r="G3" t="n">
-        <v>3.9144</v>
+        <v>3.913</v>
       </c>
       <c r="H3" t="n">
-        <v>2.6063</v>
+        <v>2.4358</v>
       </c>
       <c r="I3" t="n">
-        <v>1.4074</v>
+        <v>1.3676</v>
       </c>
       <c r="J3" t="n">
-        <v>3.9144</v>
+        <v>3.913</v>
       </c>
       <c r="K3" t="n">
         <v>40</v>
@@ -575,7 +575,7 @@
         <v>102</v>
       </c>
       <c r="M3" t="n">
-        <v>5.3218</v>
+        <v>5.2806</v>
       </c>
       <c r="N3" t="n">
         <v>142</v>
@@ -584,93 +584,93 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>fnx</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.5911</v>
+        <v>4.5724</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9019</v>
+        <v>0.8982</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4658</v>
+        <v>1.4772</v>
       </c>
       <c r="E4" t="n">
-        <v>4.5911</v>
+        <v>4.5724</v>
       </c>
       <c r="F4" t="n">
-        <v>2.9893</v>
+        <v>2.6197</v>
       </c>
       <c r="G4" t="n">
-        <v>1.6018</v>
+        <v>1.9527</v>
       </c>
       <c r="H4" t="n">
-        <v>4.9686</v>
+        <v>3.3929</v>
       </c>
       <c r="I4" t="n">
-        <v>2.683</v>
+        <v>1.905</v>
       </c>
       <c r="J4" t="n">
-        <v>1.6018</v>
+        <v>1.9527</v>
       </c>
       <c r="K4" t="n">
-        <v>126</v>
+        <v>40</v>
       </c>
       <c r="L4" t="n">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="M4" t="n">
-        <v>4.2848</v>
+        <v>3.8577</v>
       </c>
       <c r="N4" t="n">
-        <v>217</v>
+        <v>142</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>fnx</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.5444</v>
+        <v>4.4876</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8927</v>
+        <v>0.8816000000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4445</v>
+        <v>1.4385</v>
       </c>
       <c r="E5" t="n">
-        <v>4.5444</v>
+        <v>4.4876</v>
       </c>
       <c r="F5" t="n">
-        <v>2.5515</v>
+        <v>2.9876</v>
       </c>
       <c r="G5" t="n">
-        <v>1.9929</v>
+        <v>1.5</v>
       </c>
       <c r="H5" t="n">
-        <v>3.5243</v>
+        <v>4.7743</v>
       </c>
       <c r="I5" t="n">
-        <v>1.9031</v>
+        <v>2.6806</v>
       </c>
       <c r="J5" t="n">
-        <v>1.9929</v>
+        <v>1.5</v>
       </c>
       <c r="K5" t="n">
-        <v>40</v>
+        <v>126</v>
       </c>
       <c r="L5" t="n">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="M5" t="n">
-        <v>3.896</v>
+        <v>4.1806</v>
       </c>
       <c r="N5" t="n">
-        <v>142</v>
+        <v>217</v>
       </c>
     </row>
     <row r="6">
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.889</v>
+        <v>3.9243</v>
       </c>
       <c r="C6" t="n">
-        <v>0.764</v>
+        <v>0.7709</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1461</v>
+        <v>1.1819</v>
       </c>
       <c r="E6" t="n">
-        <v>3.889</v>
+        <v>3.9243</v>
       </c>
       <c r="F6" t="n">
-        <v>2.6267</v>
+        <v>2.6883</v>
       </c>
       <c r="G6" t="n">
-        <v>1.2623</v>
+        <v>1.236</v>
       </c>
       <c r="H6" t="n">
-        <v>3.7723</v>
+        <v>3.6506</v>
       </c>
       <c r="I6" t="n">
-        <v>2.037</v>
+        <v>2.0497</v>
       </c>
       <c r="J6" t="n">
-        <v>1.2623</v>
+        <v>1.236</v>
       </c>
       <c r="K6" t="n">
         <v>40</v>
@@ -713,7 +713,7 @@
         <v>102</v>
       </c>
       <c r="M6" t="n">
-        <v>3.2993</v>
+        <v>3.2857</v>
       </c>
       <c r="N6" t="n">
         <v>142</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.5682</v>
+        <v>3.5021</v>
       </c>
       <c r="C7" t="n">
-        <v>0.701</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0001</v>
+        <v>0.9896</v>
       </c>
       <c r="E7" t="n">
-        <v>3.5682</v>
+        <v>3.5021</v>
       </c>
       <c r="F7" t="n">
-        <v>3.0066</v>
+        <v>2.9855</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5616</v>
+        <v>0.5165999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>5.0256</v>
+        <v>4.7662</v>
       </c>
       <c r="I7" t="n">
-        <v>2.7138</v>
+        <v>2.6761</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5616</v>
+        <v>0.5165999999999999</v>
       </c>
       <c r="K7" t="n">
         <v>126</v>
@@ -759,7 +759,7 @@
         <v>91</v>
       </c>
       <c r="M7" t="n">
-        <v>3.2754</v>
+        <v>3.1927</v>
       </c>
       <c r="N7" t="n">
         <v>217</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.398</v>
+        <v>3.2665</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6675</v>
+        <v>0.6417</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9226</v>
+        <v>0.8823</v>
       </c>
       <c r="E8" t="n">
-        <v>3.398</v>
+        <v>3.2665</v>
       </c>
       <c r="F8" t="n">
-        <v>3.362</v>
+        <v>3.2671</v>
       </c>
       <c r="G8" t="n">
-        <v>0.036</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>6.1982</v>
+        <v>5.8235</v>
       </c>
       <c r="I8" t="n">
-        <v>3.347</v>
+        <v>3.2697</v>
       </c>
       <c r="J8" t="n">
-        <v>0.036</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="K8" t="n">
         <v>97</v>
@@ -805,7 +805,7 @@
         <v>52</v>
       </c>
       <c r="M8" t="n">
-        <v>3.383</v>
+        <v>3.2691</v>
       </c>
       <c r="N8" t="n">
         <v>149</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.9432</v>
+        <v>2.9879</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5782</v>
+        <v>0.587</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7156</v>
+        <v>0.7553</v>
       </c>
       <c r="E9" t="n">
-        <v>2.9432</v>
+        <v>2.9879</v>
       </c>
       <c r="F9" t="n">
-        <v>2.4798</v>
+        <v>2.5496</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4634</v>
+        <v>0.4383</v>
       </c>
       <c r="H9" t="n">
-        <v>3.2876</v>
+        <v>3.1298</v>
       </c>
       <c r="I9" t="n">
-        <v>1.7753</v>
+        <v>1.7573</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4634</v>
+        <v>0.4383</v>
       </c>
       <c r="K9" t="n">
         <v>47</v>
@@ -851,7 +851,7 @@
         <v>141</v>
       </c>
       <c r="M9" t="n">
-        <v>2.2387</v>
+        <v>2.1956</v>
       </c>
       <c r="N9" t="n">
         <v>188</v>
@@ -860,93 +860,93 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>Skadoodle</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.9114</v>
+        <v>2.9273</v>
       </c>
       <c r="C10" t="n">
-        <v>0.5719</v>
+        <v>0.5750999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7010999999999999</v>
+        <v>0.7277</v>
       </c>
       <c r="E10" t="n">
-        <v>2.9114</v>
+        <v>2.9273</v>
       </c>
       <c r="F10" t="n">
-        <v>3.5144</v>
+        <v>2.472</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.603</v>
+        <v>0.4553</v>
       </c>
       <c r="H10" t="n">
-        <v>6.7012</v>
+        <v>2.8384</v>
       </c>
       <c r="I10" t="n">
-        <v>3.6186</v>
+        <v>1.5937</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.603</v>
+        <v>0.4553</v>
       </c>
       <c r="K10" t="n">
-        <v>97</v>
+        <v>126</v>
       </c>
       <c r="L10" t="n">
-        <v>52</v>
+        <v>91</v>
       </c>
       <c r="M10" t="n">
-        <v>3.0156</v>
+        <v>2.049</v>
       </c>
       <c r="N10" t="n">
-        <v>149</v>
+        <v>217</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Skadoodle</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.9098</v>
+        <v>2.8316</v>
       </c>
       <c r="C11" t="n">
-        <v>0.5716</v>
+        <v>0.5563</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7004</v>
+        <v>0.6841</v>
       </c>
       <c r="E11" t="n">
-        <v>2.9098</v>
+        <v>2.8316</v>
       </c>
       <c r="F11" t="n">
-        <v>2.3586</v>
+        <v>3.4018</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5512</v>
+        <v>-0.5702</v>
       </c>
       <c r="H11" t="n">
-        <v>2.8878</v>
+        <v>6.3291</v>
       </c>
       <c r="I11" t="n">
-        <v>1.5594</v>
+        <v>3.5536</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5512</v>
+        <v>-0.5702</v>
       </c>
       <c r="K11" t="n">
-        <v>126</v>
+        <v>97</v>
       </c>
       <c r="L11" t="n">
-        <v>91</v>
+        <v>52</v>
       </c>
       <c r="M11" t="n">
-        <v>2.1106</v>
+        <v>2.9834</v>
       </c>
       <c r="N11" t="n">
-        <v>217</v>
+        <v>149</v>
       </c>
     </row>
     <row r="12">
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.8442</v>
+        <v>2.8304</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5587</v>
+        <v>0.556</v>
       </c>
       <c r="D12" t="n">
-        <v>0.6705</v>
+        <v>0.6836</v>
       </c>
       <c r="E12" t="n">
-        <v>2.8442</v>
+        <v>2.8304</v>
       </c>
       <c r="F12" t="n">
-        <v>2.46</v>
+        <v>2.5247</v>
       </c>
       <c r="G12" t="n">
-        <v>0.3842</v>
+        <v>0.3057</v>
       </c>
       <c r="H12" t="n">
-        <v>3.2223</v>
+        <v>3.0363</v>
       </c>
       <c r="I12" t="n">
-        <v>1.74</v>
+        <v>1.7048</v>
       </c>
       <c r="J12" t="n">
-        <v>0.3842</v>
+        <v>0.3057</v>
       </c>
       <c r="K12" t="n">
         <v>126</v>
@@ -989,7 +989,7 @@
         <v>91</v>
       </c>
       <c r="M12" t="n">
-        <v>2.1242</v>
+        <v>2.0105</v>
       </c>
       <c r="N12" t="n">
         <v>217</v>
@@ -998,93 +998,93 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>felps</t>
+          <t>Hiko</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.6993</v>
+        <v>2.6655</v>
       </c>
       <c r="C13" t="n">
-        <v>0.5303</v>
+        <v>0.5236</v>
       </c>
       <c r="D13" t="n">
-        <v>0.6046</v>
+        <v>0.6085</v>
       </c>
       <c r="E13" t="n">
-        <v>2.6993</v>
+        <v>2.6655</v>
       </c>
       <c r="F13" t="n">
-        <v>2.1638</v>
+        <v>2.758</v>
       </c>
       <c r="G13" t="n">
-        <v>0.5355</v>
+        <v>-0.0925</v>
       </c>
       <c r="H13" t="n">
-        <v>2.245</v>
+        <v>3.9121</v>
       </c>
       <c r="I13" t="n">
-        <v>1.2123</v>
+        <v>2.1965</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5355</v>
+        <v>-0.0925</v>
       </c>
       <c r="K13" t="n">
-        <v>47</v>
+        <v>97</v>
       </c>
       <c r="L13" t="n">
-        <v>141</v>
+        <v>52</v>
       </c>
       <c r="M13" t="n">
-        <v>1.7478</v>
+        <v>2.104</v>
       </c>
       <c r="N13" t="n">
-        <v>188</v>
+        <v>149</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Hiko</t>
+          <t>felps</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.6575</v>
+        <v>2.5321</v>
       </c>
       <c r="C14" t="n">
-        <v>0.5221</v>
+        <v>0.4974</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5855</v>
+        <v>0.5477</v>
       </c>
       <c r="E14" t="n">
-        <v>2.6575</v>
+        <v>2.5321</v>
       </c>
       <c r="F14" t="n">
-        <v>2.722</v>
+        <v>2.0584</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.0645</v>
+        <v>0.4737</v>
       </c>
       <c r="H14" t="n">
-        <v>4.0867</v>
+        <v>2.0584</v>
       </c>
       <c r="I14" t="n">
-        <v>2.2068</v>
+        <v>1.1557</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.0645</v>
+        <v>0.4737</v>
       </c>
       <c r="K14" t="n">
-        <v>97</v>
+        <v>47</v>
       </c>
       <c r="L14" t="n">
-        <v>52</v>
+        <v>141</v>
       </c>
       <c r="M14" t="n">
-        <v>2.1423</v>
+        <v>1.6294</v>
       </c>
       <c r="N14" t="n">
-        <v>149</v>
+        <v>188</v>
       </c>
     </row>
     <row r="15">
@@ -1094,31 +1094,31 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.3453</v>
+        <v>2.4264</v>
       </c>
       <c r="C15" t="n">
-        <v>0.4607</v>
+        <v>0.4767</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4434</v>
+        <v>0.4996</v>
       </c>
       <c r="E15" t="n">
-        <v>2.3453</v>
+        <v>2.4264</v>
       </c>
       <c r="F15" t="n">
-        <v>2.4768</v>
+        <v>2.5506</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.1315</v>
+        <v>-0.1242</v>
       </c>
       <c r="H15" t="n">
-        <v>3.2776</v>
+        <v>3.1334</v>
       </c>
       <c r="I15" t="n">
-        <v>1.7699</v>
+        <v>1.7593</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.1315</v>
+        <v>-0.1242</v>
       </c>
       <c r="K15" t="n">
         <v>47</v>
@@ -1127,7 +1127,7 @@
         <v>141</v>
       </c>
       <c r="M15" t="n">
-        <v>1.6384</v>
+        <v>1.6351</v>
       </c>
       <c r="N15" t="n">
         <v>188</v>
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.2261</v>
+        <v>2.1846</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4373</v>
+        <v>0.4292</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3892</v>
+        <v>0.3894</v>
       </c>
       <c r="E16" t="n">
-        <v>2.2261</v>
+        <v>2.1846</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9239000000000001</v>
+        <v>0.9758</v>
       </c>
       <c r="G16" t="n">
-        <v>1.3022</v>
+        <v>1.2088</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9239000000000001</v>
+        <v>0.9758</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4989</v>
+        <v>0.5479000000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>1.3022</v>
+        <v>1.2088</v>
       </c>
       <c r="K16" t="n">
         <v>40</v>
@@ -1173,7 +1173,7 @@
         <v>102</v>
       </c>
       <c r="M16" t="n">
-        <v>1.8011</v>
+        <v>1.7567</v>
       </c>
       <c r="N16" t="n">
         <v>142</v>
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.9057</v>
+        <v>2.0458</v>
       </c>
       <c r="C17" t="n">
-        <v>0.3744</v>
+        <v>0.4019</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2433</v>
+        <v>0.3262</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9057</v>
+        <v>2.0458</v>
       </c>
       <c r="F17" t="n">
-        <v>2.4801</v>
+        <v>2.6074</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.5744</v>
+        <v>-0.5616</v>
       </c>
       <c r="H17" t="n">
-        <v>3.2886</v>
+        <v>3.3466</v>
       </c>
       <c r="I17" t="n">
-        <v>1.7758</v>
+        <v>1.879</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.5744</v>
+        <v>-0.5616</v>
       </c>
       <c r="K17" t="n">
         <v>97</v>
@@ -1219,7 +1219,7 @@
         <v>52</v>
       </c>
       <c r="M17" t="n">
-        <v>1.2014</v>
+        <v>1.3174</v>
       </c>
       <c r="N17" t="n">
         <v>149</v>
@@ -1232,28 +1232,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.6305</v>
+        <v>1.7052</v>
       </c>
       <c r="C18" t="n">
-        <v>0.3203</v>
+        <v>0.335</v>
       </c>
       <c r="D18" t="n">
-        <v>0.118</v>
+        <v>0.171</v>
       </c>
       <c r="E18" t="n">
-        <v>1.6305</v>
+        <v>1.7052</v>
       </c>
       <c r="F18" t="n">
-        <v>1.6305</v>
+        <v>1.7052</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1.6305</v>
+        <v>1.7052</v>
       </c>
       <c r="I18" t="n">
-        <v>1.6725</v>
+        <v>1.7508</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.6725</v>
+        <v>1.7508</v>
       </c>
       <c r="N18" t="n">
         <v>168</v>
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.4749</v>
+        <v>1.6467</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2897</v>
+        <v>0.3235</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0472</v>
+        <v>0.1444</v>
       </c>
       <c r="E19" t="n">
-        <v>1.4749</v>
+        <v>1.6467</v>
       </c>
       <c r="F19" t="n">
-        <v>1.6241</v>
+        <v>1.6829</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.1492</v>
+        <v>-0.0362</v>
       </c>
       <c r="H19" t="n">
-        <v>1.6241</v>
+        <v>1.6829</v>
       </c>
       <c r="I19" t="n">
-        <v>0.877</v>
+        <v>0.9449</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.1492</v>
+        <v>-0.0362</v>
       </c>
       <c r="K19" t="n">
         <v>47</v>
@@ -1311,7 +1311,7 @@
         <v>141</v>
       </c>
       <c r="M19" t="n">
-        <v>0.7278</v>
+        <v>0.9087</v>
       </c>
       <c r="N19" t="n">
         <v>188</v>
@@ -1320,47 +1320,47 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>gob b</t>
+          <t>mitch</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.1336</v>
+        <v>1.1773</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2227</v>
+        <v>0.2313</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1082</v>
+        <v>-0.06950000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>1.1336</v>
+        <v>1.1773</v>
       </c>
       <c r="F20" t="n">
-        <v>1.1336</v>
+        <v>1.1773</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.1336</v>
+        <v>1.1773</v>
       </c>
       <c r="I20" t="n">
-        <v>1.1336</v>
+        <v>1.1773</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>107</v>
+        <v>157</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.1336</v>
+        <v>1.1773</v>
       </c>
       <c r="N20" t="n">
-        <v>107</v>
+        <v>157</v>
       </c>
     </row>
     <row r="21">
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.0307</v>
+        <v>1.0083</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2025</v>
+        <v>0.1981</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.155</v>
+        <v>-0.1465</v>
       </c>
       <c r="E21" t="n">
-        <v>1.0307</v>
+        <v>1.0083</v>
       </c>
       <c r="F21" t="n">
-        <v>1.0307</v>
+        <v>1.0083</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.0307</v>
+        <v>1.0083</v>
       </c>
       <c r="I21" t="n">
-        <v>1.0307</v>
+        <v>1.0083</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.0307</v>
+        <v>1.0083</v>
       </c>
       <c r="N21" t="n">
         <v>157</v>
@@ -1412,78 +1412,78 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>mitch</t>
+          <t>gob b</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.0225</v>
+        <v>0.9602000000000001</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2009</v>
+        <v>0.1886</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1587</v>
+        <v>-0.1684</v>
       </c>
       <c r="E22" t="n">
-        <v>1.0225</v>
+        <v>0.9602000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>1.0225</v>
+        <v>0.9602000000000001</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.0225</v>
+        <v>0.9602000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>1.0225</v>
+        <v>0.9602000000000001</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>157</v>
+        <v>107</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.0225</v>
+        <v>0.9602000000000001</v>
       </c>
       <c r="N22" t="n">
-        <v>157</v>
+        <v>107</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>tarik</t>
+          <t>reltuC</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.8788</v>
+        <v>0.745</v>
       </c>
       <c r="C23" t="n">
-        <v>0.1726</v>
+        <v>0.1464</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2242</v>
+        <v>-0.2664</v>
       </c>
       <c r="E23" t="n">
-        <v>0.8788</v>
+        <v>0.745</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8788</v>
+        <v>0.745</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0.8788</v>
+        <v>0.745</v>
       </c>
       <c r="I23" t="n">
-        <v>0.9014</v>
+        <v>0.7649</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -1495,7 +1495,7 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0.9014</v>
+        <v>0.7649</v>
       </c>
       <c r="N23" t="n">
         <v>168</v>
@@ -1504,32 +1504,32 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>reltuC</t>
+          <t>tarik</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7856</v>
+        <v>0.7189</v>
       </c>
       <c r="C24" t="n">
-        <v>0.1543</v>
+        <v>0.1412</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.2666</v>
+        <v>-0.2783</v>
       </c>
       <c r="E24" t="n">
-        <v>0.7856</v>
+        <v>0.7189</v>
       </c>
       <c r="F24" t="n">
-        <v>0.7856</v>
+        <v>0.7189</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.7856</v>
+        <v>0.7189</v>
       </c>
       <c r="I24" t="n">
-        <v>0.8058</v>
+        <v>0.7381</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.8058</v>
+        <v>0.7381</v>
       </c>
       <c r="N24" t="n">
         <v>168</v>
@@ -1550,93 +1550,93 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>boltz</t>
+          <t>adreN</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6532</v>
+        <v>0.6606</v>
       </c>
       <c r="C25" t="n">
-        <v>0.1283</v>
+        <v>0.1298</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.3269</v>
+        <v>-0.3049</v>
       </c>
       <c r="E25" t="n">
-        <v>0.6532</v>
+        <v>0.6606</v>
       </c>
       <c r="F25" t="n">
-        <v>0.5785</v>
+        <v>0.8608</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0747</v>
+        <v>-0.2002</v>
       </c>
       <c r="H25" t="n">
-        <v>0.5785</v>
+        <v>0.8608</v>
       </c>
       <c r="I25" t="n">
-        <v>0.3124</v>
+        <v>0.4833</v>
       </c>
       <c r="J25" t="n">
-        <v>0.0747</v>
+        <v>-0.2002</v>
       </c>
       <c r="K25" t="n">
-        <v>47</v>
+        <v>97</v>
       </c>
       <c r="L25" t="n">
-        <v>141</v>
+        <v>52</v>
       </c>
       <c r="M25" t="n">
-        <v>0.3871</v>
+        <v>0.2831</v>
       </c>
       <c r="N25" t="n">
-        <v>188</v>
+        <v>149</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>adreN</t>
+          <t>boltz</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6073</v>
+        <v>0.5286</v>
       </c>
       <c r="C26" t="n">
-        <v>0.1193</v>
+        <v>0.1038</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.3477</v>
+        <v>-0.365</v>
       </c>
       <c r="E26" t="n">
-        <v>0.6073</v>
+        <v>0.5286</v>
       </c>
       <c r="F26" t="n">
-        <v>0.8361</v>
+        <v>0.4595</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.2288</v>
+        <v>0.06909999999999999</v>
       </c>
       <c r="H26" t="n">
-        <v>0.8361</v>
+        <v>0.4595</v>
       </c>
       <c r="I26" t="n">
-        <v>0.4515</v>
+        <v>0.258</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.2288</v>
+        <v>0.06909999999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>97</v>
+        <v>47</v>
       </c>
       <c r="L26" t="n">
-        <v>52</v>
+        <v>141</v>
       </c>
       <c r="M26" t="n">
-        <v>0.2227</v>
+        <v>0.3271</v>
       </c>
       <c r="N26" t="n">
-        <v>149</v>
+        <v>188</v>
       </c>
     </row>
     <row r="27">
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.2471</v>
+        <v>0.2139</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0485</v>
+        <v>0.042</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5117</v>
+        <v>-0.5083</v>
       </c>
       <c r="E27" t="n">
-        <v>0.2471</v>
+        <v>0.2139</v>
       </c>
       <c r="F27" t="n">
-        <v>0.2471</v>
+        <v>0.2139</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2471</v>
+        <v>0.2139</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2471</v>
+        <v>0.2139</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.2471</v>
+        <v>0.2139</v>
       </c>
       <c r="N27" t="n">
         <v>107</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.115</v>
+        <v>0.097</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0226</v>
+        <v>0.0191</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5719</v>
+        <v>-0.5616</v>
       </c>
       <c r="E28" t="n">
-        <v>0.115</v>
+        <v>0.097</v>
       </c>
       <c r="F28" t="n">
-        <v>0.115</v>
+        <v>0.097</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.115</v>
+        <v>0.097</v>
       </c>
       <c r="I28" t="n">
-        <v>0.118</v>
+        <v>0.09950000000000001</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.118</v>
+        <v>0.09950000000000001</v>
       </c>
       <c r="N28" t="n">
         <v>168</v>
@@ -1734,139 +1734,139 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Nifty</t>
+          <t>DAVEY</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.09080000000000001</v>
+        <v>0.0204</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0178</v>
+        <v>0.004</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5829</v>
+        <v>-0.5965</v>
       </c>
       <c r="E29" t="n">
-        <v>0.09080000000000001</v>
+        <v>0.0204</v>
       </c>
       <c r="F29" t="n">
-        <v>0.09080000000000001</v>
+        <v>0.0204</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0.09080000000000001</v>
+        <v>0.0204</v>
       </c>
       <c r="I29" t="n">
-        <v>0.09080000000000001</v>
+        <v>0.0204</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>157</v>
+        <v>82</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0.09080000000000001</v>
+        <v>0.0204</v>
       </c>
       <c r="N29" t="n">
-        <v>157</v>
+        <v>82</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>DAVEY</t>
+          <t>just9n</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.0539</v>
+        <v>0.0047</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0106</v>
+        <v>0.0009</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.5997</v>
+        <v>-0.6036</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0539</v>
+        <v>0.0047</v>
       </c>
       <c r="F30" t="n">
-        <v>0.0539</v>
+        <v>0.0047</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0.0539</v>
+        <v>0.0047</v>
       </c>
       <c r="I30" t="n">
-        <v>0.0539</v>
+        <v>0.0047</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>82</v>
+        <v>107</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>0.0539</v>
+        <v>0.0047</v>
       </c>
       <c r="N30" t="n">
-        <v>82</v>
+        <v>107</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>just9n</t>
+          <t>Nifty</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.0225</v>
+        <v>-0.0058</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0044</v>
+        <v>-0.0011</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.614</v>
+        <v>-0.6084000000000001</v>
       </c>
       <c r="E31" t="n">
-        <v>0.0225</v>
+        <v>-0.0058</v>
       </c>
       <c r="F31" t="n">
-        <v>0.0225</v>
+        <v>-0.0058</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.0225</v>
+        <v>-0.0058</v>
       </c>
       <c r="I31" t="n">
-        <v>0.0225</v>
+        <v>-0.0058</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>107</v>
+        <v>157</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>0.0225</v>
+        <v>-0.0058</v>
       </c>
       <c r="N31" t="n">
-        <v>107</v>
+        <v>157</v>
       </c>
     </row>
     <row r="32">
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.0107</v>
+        <v>-0.0464</v>
       </c>
       <c r="C32" t="n">
-        <v>0.0021</v>
+        <v>-0.0091</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.6193</v>
+        <v>-0.6269</v>
       </c>
       <c r="E32" t="n">
-        <v>0.0107</v>
+        <v>-0.0464</v>
       </c>
       <c r="F32" t="n">
-        <v>0.0107</v>
+        <v>-0.0464</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0.0107</v>
+        <v>-0.0464</v>
       </c>
       <c r="I32" t="n">
-        <v>0.0107</v>
+        <v>-0.0464</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0.0107</v>
+        <v>-0.0464</v>
       </c>
       <c r="N32" t="n">
         <v>82</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.1354</v>
+        <v>-0.1419</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.0266</v>
+        <v>-0.0279</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.6858</v>
+        <v>-0.6704</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.1354</v>
+        <v>-0.1419</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.1354</v>
+        <v>-0.1419</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.1354</v>
+        <v>-0.1419</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.1354</v>
+        <v>-0.1419</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.1354</v>
+        <v>-0.1419</v>
       </c>
       <c r="N33" t="n">
         <v>82</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.2314</v>
+        <v>-0.2531</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.0455</v>
+        <v>-0.0497</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.7295</v>
+        <v>-0.7211</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.2314</v>
+        <v>-0.2531</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.2314</v>
+        <v>-0.2531</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.2314</v>
+        <v>-0.2531</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.2314</v>
+        <v>-0.2531</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.2314</v>
+        <v>-0.2531</v>
       </c>
       <c r="N34" t="n">
         <v>107</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.4986</v>
+        <v>-0.5496</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.0979</v>
+        <v>-0.108</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8512</v>
+        <v>-0.8562</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.4986</v>
+        <v>-0.5496</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.4986</v>
+        <v>-0.5496</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.4986</v>
+        <v>-0.5496</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.4986</v>
+        <v>-0.5496</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.4986</v>
+        <v>-0.5496</v>
       </c>
       <c r="N35" t="n">
         <v>157</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.7798</v>
+        <v>-0.7941</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1532</v>
+        <v>-0.156</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9792</v>
+        <v>-0.9675</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.7798</v>
+        <v>-0.7941</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.7798</v>
+        <v>-0.7941</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.7798</v>
+        <v>-0.7941</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.7798</v>
+        <v>-0.7941</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.7798</v>
+        <v>-0.7941</v>
       </c>
       <c r="N36" t="n">
         <v>82</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.0365</v>
+        <v>-0.9933</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.2036</v>
+        <v>-0.1951</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.096</v>
+        <v>-1.0583</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.0365</v>
+        <v>-0.9933</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.0365</v>
+        <v>-0.9933</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.0365</v>
+        <v>-0.9933</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.0365</v>
+        <v>-0.9933</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.0365</v>
+        <v>-0.9933</v>
       </c>
       <c r="N37" t="n">
         <v>107</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.0705</v>
+        <v>-1.0129</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.2103</v>
+        <v>-0.199</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.1115</v>
+        <v>-1.0672</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.0705</v>
+        <v>-1.0129</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.0705</v>
+        <v>-1.0129</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.0705</v>
+        <v>-1.0129</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.0705</v>
+        <v>-1.0129</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.0705</v>
+        <v>-1.0129</v>
       </c>
       <c r="N38" t="n">
         <v>157</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.1859</v>
+        <v>-1.153</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.233</v>
+        <v>-0.2265</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.164</v>
+        <v>-1.131</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.1859</v>
+        <v>-1.153</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.1859</v>
+        <v>-1.153</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.1859</v>
+        <v>-1.153</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.1859</v>
+        <v>-1.153</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.1859</v>
+        <v>-1.153</v>
       </c>
       <c r="N39" t="n">
         <v>82</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.3466</v>
+        <v>-1.2631</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.2645</v>
+        <v>-0.2481</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.2372</v>
+        <v>-1.1812</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.3466</v>
+        <v>-1.2631</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.3466</v>
+        <v>-1.2631</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.3466</v>
+        <v>-1.2631</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.3813</v>
+        <v>-1.2969</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.3813</v>
+        <v>-1.2969</v>
       </c>
       <c r="N40" t="n">
         <v>168</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.9492</v>
+        <v>-1.8104</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.3829</v>
+        <v>-0.3557</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.5115</v>
+        <v>-1.4305</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.9492</v>
+        <v>-1.8104</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.0915</v>
+        <v>-1.0038</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.8577</v>
+        <v>-0.8066</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.0915</v>
+        <v>-1.0038</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.5894</v>
+        <v>-0.5636</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.8577</v>
+        <v>-0.8066</v>
       </c>
       <c r="K41" t="n">
         <v>126</v>
@@ -2323,7 +2323,7 @@
         <v>91</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.4471</v>
+        <v>-1.3702</v>
       </c>
       <c r="N41" t="n">
         <v>217</v>
@@ -2429,10 +2429,10 @@
         <v>1.01</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1123</v>
+        <v>0.0964</v>
       </c>
       <c r="J2" t="n">
-        <v>2.8075</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>0.87</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1528</v>
+        <v>-0.1372</v>
       </c>
       <c r="J3" t="n">
-        <v>-3.82</v>
+        <v>-3.43</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.67</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3472</v>
+        <v>-0.3331</v>
       </c>
       <c r="J4" t="n">
-        <v>-8.68</v>
+        <v>-8.327500000000001</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.58</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4276</v>
+        <v>-0.4185</v>
       </c>
       <c r="J5" t="n">
-        <v>-10.69</v>
+        <v>-10.4625</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.53</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4717</v>
+        <v>-0.4669</v>
       </c>
       <c r="J6" t="n">
-        <v>-11.7925</v>
+        <v>-11.6725</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.51</v>
       </c>
       <c r="I7" t="n">
-        <v>1.1339</v>
+        <v>1.1417</v>
       </c>
       <c r="J7" t="n">
-        <v>28.3475</v>
+        <v>28.5425</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.46</v>
       </c>
       <c r="I8" t="n">
-        <v>1.0426</v>
+        <v>1.0409</v>
       </c>
       <c r="J8" t="n">
-        <v>26.065</v>
+        <v>26.0225</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.3</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7393999999999999</v>
+        <v>0.7161999999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>18.485</v>
+        <v>17.905</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.19</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5115</v>
+        <v>0.4808</v>
       </c>
       <c r="J10" t="n">
-        <v>12.7875</v>
+        <v>12.02</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.0492</v>
+        <v>-0.0445</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.23</v>
+        <v>-1.1125</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.09</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2732</v>
+        <v>0.2278</v>
       </c>
       <c r="J12" t="n">
-        <v>6.83</v>
+        <v>5.695</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>0.98</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.027</v>
+        <v>-0.0198</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.675</v>
+        <v>-0.495</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.0853</v>
+        <v>-0.0723</v>
       </c>
       <c r="J14" t="n">
-        <v>-2.1325</v>
+        <v>-1.8075</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.63</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3953</v>
+        <v>-0.3835</v>
       </c>
       <c r="J15" t="n">
-        <v>-9.8825</v>
+        <v>-9.5875</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.55</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4661</v>
+        <v>-0.4614</v>
       </c>
       <c r="J16" t="n">
-        <v>-11.6525</v>
+        <v>-11.535</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.57</v>
       </c>
       <c r="I17" t="n">
-        <v>1.2448</v>
+        <v>1.2657</v>
       </c>
       <c r="J17" t="n">
-        <v>31.12</v>
+        <v>31.6425</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.35</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8377</v>
+        <v>0.8191000000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>20.9425</v>
+        <v>20.4775</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.27</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6821</v>
+        <v>0.6556999999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>17.0525</v>
+        <v>16.3925</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.26</v>
       </c>
       <c r="I20" t="n">
-        <v>0.662</v>
+        <v>0.635</v>
       </c>
       <c r="J20" t="n">
-        <v>16.55</v>
+        <v>15.875</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.95</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2509</v>
+        <v>-0.2158</v>
       </c>
       <c r="J21" t="n">
-        <v>-6.2725</v>
+        <v>-5.395</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.85</v>
       </c>
       <c r="I22" t="n">
-        <v>1.3685</v>
+        <v>1.3758</v>
       </c>
       <c r="J22" t="n">
-        <v>30.107</v>
+        <v>30.2676</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.61</v>
       </c>
       <c r="I23" t="n">
-        <v>1.0696</v>
+        <v>1.0605</v>
       </c>
       <c r="J23" t="n">
-        <v>23.5312</v>
+        <v>23.331</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.37</v>
       </c>
       <c r="I24" t="n">
-        <v>0.7533</v>
+        <v>0.7437</v>
       </c>
       <c r="J24" t="n">
-        <v>16.5726</v>
+        <v>16.3614</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>1.05</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1404</v>
+        <v>0.1132</v>
       </c>
       <c r="J25" t="n">
-        <v>3.0888</v>
+        <v>2.4904</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>1.01</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.0029</v>
+        <v>-0.0151</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.0638</v>
+        <v>-0.3322</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.07630000000000001</v>
+        <v>-0.0634</v>
       </c>
       <c r="J27" t="n">
-        <v>-1.6786</v>
+        <v>-1.3948</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>0.88</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.1494</v>
+        <v>-0.1338</v>
       </c>
       <c r="J28" t="n">
-        <v>-3.2868</v>
+        <v>-2.9436</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.73</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.2977</v>
+        <v>-0.2811</v>
       </c>
       <c r="J29" t="n">
-        <v>-6.5494</v>
+        <v>-6.1842</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.71</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.3162</v>
+        <v>-0.3</v>
       </c>
       <c r="J30" t="n">
-        <v>-6.9564</v>
+        <v>-6.6</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.64</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3798</v>
+        <v>-0.3668</v>
       </c>
       <c r="J31" t="n">
-        <v>-8.355600000000001</v>
+        <v>-8.069599999999999</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.54</v>
       </c>
       <c r="I32" t="n">
-        <v>1.0037</v>
+        <v>0.9912</v>
       </c>
       <c r="J32" t="n">
-        <v>30.111</v>
+        <v>29.736</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.26</v>
       </c>
       <c r="I33" t="n">
-        <v>0.6067</v>
+        <v>0.5978</v>
       </c>
       <c r="J33" t="n">
-        <v>18.201</v>
+        <v>17.934</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.23</v>
       </c>
       <c r="I34" t="n">
-        <v>0.5617</v>
+        <v>0.5553</v>
       </c>
       <c r="J34" t="n">
-        <v>16.851</v>
+        <v>16.659</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.11</v>
       </c>
       <c r="I35" t="n">
-        <v>0.3302</v>
+        <v>0.2977</v>
       </c>
       <c r="J35" t="n">
-        <v>9.906000000000001</v>
+        <v>8.930999999999999</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>1.04</v>
       </c>
       <c r="I36" t="n">
-        <v>0.1316</v>
+        <v>0.1081</v>
       </c>
       <c r="J36" t="n">
-        <v>3.948</v>
+        <v>3.243</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.14</v>
       </c>
       <c r="I37" t="n">
-        <v>0.3522</v>
+        <v>0.2994</v>
       </c>
       <c r="J37" t="n">
-        <v>10.566</v>
+        <v>8.981999999999999</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.08</v>
       </c>
       <c r="I38" t="n">
-        <v>0.2332</v>
+        <v>0.1886</v>
       </c>
       <c r="J38" t="n">
-        <v>6.996</v>
+        <v>5.658</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.95</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.0794</v>
+        <v>-0.0664</v>
       </c>
       <c r="J39" t="n">
-        <v>-2.382</v>
+        <v>-1.992</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.82</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.2232</v>
+        <v>-0.2034</v>
       </c>
       <c r="J40" t="n">
-        <v>-6.696</v>
+        <v>-6.102</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.52</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.4981</v>
+        <v>-0.4982</v>
       </c>
       <c r="J41" t="n">
-        <v>-14.943</v>
+        <v>-14.946</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.29</v>
       </c>
       <c r="I42" t="n">
-        <v>0.4655</v>
+        <v>0.4839</v>
       </c>
       <c r="J42" t="n">
-        <v>13.4995</v>
+        <v>14.0331</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>0.87</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.1732</v>
+        <v>-0.1537</v>
       </c>
       <c r="J43" t="n">
-        <v>-5.0228</v>
+        <v>-4.4573</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.86</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.1838</v>
+        <v>-0.164</v>
       </c>
       <c r="J44" t="n">
-        <v>-5.3302</v>
+        <v>-4.756</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.83</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.2148</v>
+        <v>-0.1947</v>
       </c>
       <c r="J45" t="n">
-        <v>-6.2292</v>
+        <v>-5.6463</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.75</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.2934</v>
+        <v>-0.275</v>
       </c>
       <c r="J46" t="n">
-        <v>-8.508599999999999</v>
+        <v>-7.975</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.47</v>
       </c>
       <c r="I47" t="n">
-        <v>0.5563</v>
+        <v>0.5207000000000001</v>
       </c>
       <c r="J47" t="n">
-        <v>16.1327</v>
+        <v>15.1003</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.35</v>
       </c>
       <c r="I48" t="n">
-        <v>0.462</v>
+        <v>0.4039</v>
       </c>
       <c r="J48" t="n">
-        <v>13.398</v>
+        <v>11.7131</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.15</v>
       </c>
       <c r="I49" t="n">
-        <v>0.2395</v>
+        <v>0.1935</v>
       </c>
       <c r="J49" t="n">
-        <v>6.9455</v>
+        <v>5.6115</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>1.09</v>
       </c>
       <c r="I50" t="n">
-        <v>0.1577</v>
+        <v>0.123</v>
       </c>
       <c r="J50" t="n">
-        <v>4.5733</v>
+        <v>3.567</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.83</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.237</v>
+        <v>-0.2178</v>
       </c>
       <c r="J51" t="n">
-        <v>-6.873</v>
+        <v>-6.3162</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.22</v>
       </c>
       <c r="I52" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.5528999999999999</v>
       </c>
       <c r="J52" t="n">
-        <v>19.74</v>
+        <v>19.3515</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.18</v>
       </c>
       <c r="I53" t="n">
-        <v>0.4974</v>
+        <v>0.4778</v>
       </c>
       <c r="J53" t="n">
-        <v>17.409</v>
+        <v>16.723</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.09</v>
       </c>
       <c r="I54" t="n">
-        <v>0.2998</v>
+        <v>0.2631</v>
       </c>
       <c r="J54" t="n">
-        <v>10.493</v>
+        <v>9.208500000000001</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.01</v>
       </c>
       <c r="I55" t="n">
-        <v>0.0461</v>
+        <v>0.0346</v>
       </c>
       <c r="J55" t="n">
-        <v>1.6135</v>
+        <v>1.211</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.2471</v>
+        <v>-0.2084</v>
       </c>
       <c r="J56" t="n">
-        <v>-8.6485</v>
+        <v>-7.294</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.23</v>
       </c>
       <c r="I57" t="n">
-        <v>0.4652</v>
+        <v>0.4161</v>
       </c>
       <c r="J57" t="n">
-        <v>16.282</v>
+        <v>14.5635</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.18</v>
       </c>
       <c r="I58" t="n">
-        <v>0.3909</v>
+        <v>0.3353</v>
       </c>
       <c r="J58" t="n">
-        <v>13.6815</v>
+        <v>11.7355</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.05</v>
       </c>
       <c r="I59" t="n">
-        <v>0.1431</v>
+        <v>0.111</v>
       </c>
       <c r="J59" t="n">
-        <v>5.0085</v>
+        <v>3.885</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.92</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.127</v>
+        <v>-0.108</v>
       </c>
       <c r="J60" t="n">
-        <v>-4.445</v>
+        <v>-3.78</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.82</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.236</v>
+        <v>-0.2157</v>
       </c>
       <c r="J61" t="n">
-        <v>-8.26</v>
+        <v>-7.5495</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.31</v>
       </c>
       <c r="I62" t="n">
-        <v>0.6906</v>
+        <v>0.6763</v>
       </c>
       <c r="J62" t="n">
-        <v>18.6462</v>
+        <v>18.2601</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.26</v>
       </c>
       <c r="I63" t="n">
-        <v>0.6145</v>
+        <v>0.6029</v>
       </c>
       <c r="J63" t="n">
-        <v>16.5915</v>
+        <v>16.2783</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.19</v>
       </c>
       <c r="I64" t="n">
-        <v>0.5036</v>
+        <v>0.4895</v>
       </c>
       <c r="J64" t="n">
-        <v>13.5972</v>
+        <v>13.2165</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>1.11</v>
       </c>
       <c r="I65" t="n">
-        <v>0.3407</v>
+        <v>0.3062</v>
       </c>
       <c r="J65" t="n">
-        <v>9.1989</v>
+        <v>8.2674</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.98</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.1295</v>
+        <v>-0.1022</v>
       </c>
       <c r="J66" t="n">
-        <v>-3.4965</v>
+        <v>-2.7594</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.62</v>
       </c>
       <c r="I67" t="n">
-        <v>0.9024</v>
+        <v>0.8683</v>
       </c>
       <c r="J67" t="n">
-        <v>24.3648</v>
+        <v>23.4441</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.28</v>
       </c>
       <c r="I68" t="n">
-        <v>0.5309</v>
+        <v>0.5016</v>
       </c>
       <c r="J68" t="n">
-        <v>14.3343</v>
+        <v>13.5432</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.75</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.3017</v>
+        <v>-0.2839</v>
       </c>
       <c r="J69" t="n">
-        <v>-8.145899999999999</v>
+        <v>-7.6653</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.73</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.3205</v>
+        <v>-0.3039</v>
       </c>
       <c r="J70" t="n">
-        <v>-8.653499999999999</v>
+        <v>-8.205299999999999</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.66</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.3847</v>
+        <v>-0.3731</v>
       </c>
       <c r="J71" t="n">
-        <v>-10.3869</v>
+        <v>-10.0737</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.91</v>
       </c>
       <c r="I72" t="n">
-        <v>1.5509</v>
+        <v>1.5868</v>
       </c>
       <c r="J72" t="n">
-        <v>29.4671</v>
+        <v>30.1492</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.81</v>
       </c>
       <c r="I73" t="n">
-        <v>1.4339</v>
+        <v>1.4628</v>
       </c>
       <c r="J73" t="n">
-        <v>27.2441</v>
+        <v>27.7932</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.55</v>
       </c>
       <c r="I74" t="n">
-        <v>1.1211</v>
+        <v>1.1415</v>
       </c>
       <c r="J74" t="n">
-        <v>21.3009</v>
+        <v>21.6885</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1.48</v>
       </c>
       <c r="I75" t="n">
-        <v>1.0294</v>
+        <v>1.0439</v>
       </c>
       <c r="J75" t="n">
-        <v>19.5586</v>
+        <v>19.8341</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>1.12</v>
       </c>
       <c r="I76" t="n">
-        <v>0.305</v>
+        <v>0.2697</v>
       </c>
       <c r="J76" t="n">
-        <v>5.795</v>
+        <v>5.1243</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>0.98</v>
       </c>
       <c r="I77" t="n">
-        <v>0.09379999999999999</v>
+        <v>0.1405</v>
       </c>
       <c r="J77" t="n">
-        <v>1.7822</v>
+        <v>2.6695</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>0.55</v>
       </c>
       <c r="I78" t="n">
-        <v>-0.431</v>
+        <v>-0.4259</v>
       </c>
       <c r="J78" t="n">
-        <v>-8.189</v>
+        <v>-8.0921</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>0.51</v>
       </c>
       <c r="I79" t="n">
-        <v>-0.4649</v>
+        <v>-0.4612</v>
       </c>
       <c r="J79" t="n">
-        <v>-8.8331</v>
+        <v>-8.7628</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.48</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.4911</v>
+        <v>-0.4891</v>
       </c>
       <c r="J80" t="n">
-        <v>-9.3309</v>
+        <v>-9.292899999999999</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.27</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.678</v>
+        <v>-0.7028</v>
       </c>
       <c r="J81" t="n">
-        <v>-12.882</v>
+        <v>-13.3532</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.71</v>
       </c>
       <c r="I82" t="n">
-        <v>1.3793</v>
+        <v>1.4047</v>
       </c>
       <c r="J82" t="n">
-        <v>35.8618</v>
+        <v>36.5222</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.41</v>
       </c>
       <c r="I83" t="n">
-        <v>0.9628</v>
+        <v>0.9539</v>
       </c>
       <c r="J83" t="n">
-        <v>25.0328</v>
+        <v>24.8014</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>1.32</v>
       </c>
       <c r="I84" t="n">
-        <v>0.7897</v>
+        <v>0.7653</v>
       </c>
       <c r="J84" t="n">
-        <v>20.5322</v>
+        <v>19.8978</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.88</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.4354</v>
+        <v>-0.3951</v>
       </c>
       <c r="J85" t="n">
-        <v>-11.3204</v>
+        <v>-10.2726</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.77</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.6961000000000001</v>
+        <v>-0.6675</v>
       </c>
       <c r="J86" t="n">
-        <v>-18.0986</v>
+        <v>-17.355</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.04</v>
       </c>
       <c r="I87" t="n">
-        <v>0.1507</v>
+        <v>0.1165</v>
       </c>
       <c r="J87" t="n">
-        <v>3.9182</v>
+        <v>3.029</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>0.96</v>
       </c>
       <c r="I88" t="n">
-        <v>-0.0622</v>
+        <v>-0.0511</v>
       </c>
       <c r="J88" t="n">
-        <v>-1.6172</v>
+        <v>-1.3286</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>0.85</v>
       </c>
       <c r="I89" t="n">
-        <v>-0.19</v>
+        <v>-0.1713</v>
       </c>
       <c r="J89" t="n">
-        <v>-4.94</v>
+        <v>-4.4538</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>0.8</v>
       </c>
       <c r="I90" t="n">
-        <v>-0.2401</v>
+        <v>-0.2208</v>
       </c>
       <c r="J90" t="n">
-        <v>-6.2426</v>
+        <v>-5.7408</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.7</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.3351</v>
+        <v>-0.3189</v>
       </c>
       <c r="J91" t="n">
-        <v>-8.7126</v>
+        <v>-8.291399999999999</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.21</v>
       </c>
       <c r="I92" t="n">
-        <v>0.5955</v>
+        <v>0.5567</v>
       </c>
       <c r="J92" t="n">
-        <v>20.8425</v>
+        <v>19.4845</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.17</v>
       </c>
       <c r="I93" t="n">
-        <v>0.5036</v>
+        <v>0.4623</v>
       </c>
       <c r="J93" t="n">
-        <v>17.626</v>
+        <v>16.1805</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.01</v>
       </c>
       <c r="I94" t="n">
-        <v>0.0525</v>
+        <v>0.0394</v>
       </c>
       <c r="J94" t="n">
-        <v>1.8375</v>
+        <v>1.379</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.2399</v>
+        <v>-0.2016</v>
       </c>
       <c r="J95" t="n">
-        <v>-8.3965</v>
+        <v>-7.056</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.92</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.2974</v>
+        <v>-0.2564</v>
       </c>
       <c r="J96" t="n">
-        <v>-10.409</v>
+        <v>-8.974</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.08</v>
       </c>
       <c r="I97" t="n">
-        <v>0.2121</v>
+        <v>0.1698</v>
       </c>
       <c r="J97" t="n">
-        <v>7.4235</v>
+        <v>5.943</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.08</v>
       </c>
       <c r="I98" t="n">
-        <v>0.2121</v>
+        <v>0.1698</v>
       </c>
       <c r="J98" t="n">
-        <v>7.4235</v>
+        <v>5.943</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>0.98</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.0428</v>
+        <v>-0.0325</v>
       </c>
       <c r="J99" t="n">
-        <v>-1.498</v>
+        <v>-1.1375</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.0992</v>
+        <v>-0.0823</v>
       </c>
       <c r="J100" t="n">
-        <v>-3.472</v>
+        <v>-2.8805</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.93</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.1117</v>
+        <v>-0.0939</v>
       </c>
       <c r="J101" t="n">
-        <v>-3.9095</v>
+        <v>-3.2865</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.25</v>
       </c>
       <c r="I102" t="n">
-        <v>0.4007</v>
+        <v>0.3976</v>
       </c>
       <c r="J102" t="n">
-        <v>11.2196</v>
+        <v>11.1328</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.1</v>
       </c>
       <c r="I103" t="n">
-        <v>0.1948</v>
+        <v>0.1785</v>
       </c>
       <c r="J103" t="n">
-        <v>5.4544</v>
+        <v>4.998</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.1</v>
       </c>
       <c r="I104" t="n">
-        <v>0.1948</v>
+        <v>0.1785</v>
       </c>
       <c r="J104" t="n">
-        <v>5.4544</v>
+        <v>4.998</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>1.02</v>
       </c>
       <c r="I105" t="n">
-        <v>0.056</v>
+        <v>0.0454</v>
       </c>
       <c r="J105" t="n">
-        <v>1.568</v>
+        <v>1.2712</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.64</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.4038</v>
+        <v>-0.3942</v>
       </c>
       <c r="J106" t="n">
-        <v>-11.3064</v>
+        <v>-11.0376</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.53</v>
       </c>
       <c r="I107" t="n">
-        <v>0.6743</v>
+        <v>0.6037</v>
       </c>
       <c r="J107" t="n">
-        <v>18.8804</v>
+        <v>16.9036</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.3</v>
       </c>
       <c r="I108" t="n">
-        <v>0.4256</v>
+        <v>0.3607</v>
       </c>
       <c r="J108" t="n">
-        <v>11.9168</v>
+        <v>10.0996</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>1.01</v>
       </c>
       <c r="I109" t="n">
-        <v>0.0239</v>
+        <v>0.0157</v>
       </c>
       <c r="J109" t="n">
-        <v>0.6692</v>
+        <v>0.4396</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.99</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.0326</v>
+        <v>-0.0236</v>
       </c>
       <c r="J110" t="n">
-        <v>-0.9127999999999999</v>
+        <v>-0.6608000000000001</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.68</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.3742</v>
+        <v>-0.3627</v>
       </c>
       <c r="J111" t="n">
-        <v>-10.4776</v>
+        <v>-10.1556</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.53</v>
       </c>
       <c r="I112" t="n">
-        <v>1.1404</v>
+        <v>1.1532</v>
       </c>
       <c r="J112" t="n">
-        <v>30.7908</v>
+        <v>31.1364</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.33</v>
       </c>
       <c r="I113" t="n">
-        <v>0.8088</v>
+        <v>0.7858000000000001</v>
       </c>
       <c r="J113" t="n">
-        <v>21.8376</v>
+        <v>21.2166</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>1.23</v>
       </c>
       <c r="I114" t="n">
-        <v>0.606</v>
+        <v>0.5743</v>
       </c>
       <c r="J114" t="n">
-        <v>16.362</v>
+        <v>15.5061</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>1.2</v>
       </c>
       <c r="I115" t="n">
-        <v>0.5432</v>
+        <v>0.5102</v>
       </c>
       <c r="J115" t="n">
-        <v>14.6664</v>
+        <v>13.7754</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.82</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.5826</v>
+        <v>-0.5471</v>
       </c>
       <c r="J116" t="n">
-        <v>-15.7302</v>
+        <v>-14.7717</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>0.95</v>
       </c>
       <c r="I117" t="n">
-        <v>-0.0699</v>
+        <v>-0.0581</v>
       </c>
       <c r="J117" t="n">
-        <v>-1.8873</v>
+        <v>-1.5687</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>0.88</v>
       </c>
       <c r="I118" t="n">
-        <v>-0.1551</v>
+        <v>-0.1388</v>
       </c>
       <c r="J118" t="n">
-        <v>-4.1877</v>
+        <v>-3.7476</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>0.83</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.2071</v>
+        <v>-0.1893</v>
       </c>
       <c r="J119" t="n">
-        <v>-5.5917</v>
+        <v>-5.1111</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>0.76</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.2741</v>
+        <v>-0.2561</v>
       </c>
       <c r="J120" t="n">
-        <v>-7.4007</v>
+        <v>-6.9147</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.7</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.3302</v>
+        <v>-0.314</v>
       </c>
       <c r="J121" t="n">
-        <v>-8.9154</v>
+        <v>-8.478</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.27</v>
       </c>
       <c r="I122" t="n">
-        <v>0.5376</v>
+        <v>0.4779</v>
       </c>
       <c r="J122" t="n">
-        <v>18.816</v>
+        <v>16.7265</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.25</v>
       </c>
       <c r="I123" t="n">
-        <v>0.5056</v>
+        <v>0.4463</v>
       </c>
       <c r="J123" t="n">
-        <v>17.696</v>
+        <v>15.6205</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.01</v>
       </c>
       <c r="I124" t="n">
-        <v>0.039</v>
+        <v>0.0272</v>
       </c>
       <c r="J124" t="n">
-        <v>1.365</v>
+        <v>0.952</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.97</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.0618</v>
+        <v>-0.0483</v>
       </c>
       <c r="J125" t="n">
-        <v>-2.163</v>
+        <v>-1.6905</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.74</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.3146</v>
+        <v>-0.2979</v>
       </c>
       <c r="J126" t="n">
-        <v>-11.011</v>
+        <v>-10.4265</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.29</v>
       </c>
       <c r="I127" t="n">
-        <v>0.7497</v>
+        <v>0.7199</v>
       </c>
       <c r="J127" t="n">
-        <v>26.2395</v>
+        <v>25.1965</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.23</v>
       </c>
       <c r="I128" t="n">
-        <v>0.6223</v>
+        <v>0.5862000000000001</v>
       </c>
       <c r="J128" t="n">
-        <v>21.7805</v>
+        <v>20.517</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.21</v>
       </c>
       <c r="I129" t="n">
-        <v>0.5786</v>
+        <v>0.5412</v>
       </c>
       <c r="J129" t="n">
-        <v>20.251</v>
+        <v>18.942</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1.01</v>
       </c>
       <c r="I130" t="n">
-        <v>0.0401</v>
+        <v>0.0295</v>
       </c>
       <c r="J130" t="n">
-        <v>1.4035</v>
+        <v>1.0325</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.87</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.4436</v>
+        <v>-0.4013</v>
       </c>
       <c r="J131" t="n">
-        <v>-15.526</v>
+        <v>-14.0455</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.55</v>
       </c>
       <c r="I132" t="n">
-        <v>0.6803</v>
+        <v>0.6086</v>
       </c>
       <c r="J132" t="n">
-        <v>18.3681</v>
+        <v>16.4322</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.3</v>
       </c>
       <c r="I133" t="n">
-        <v>0.416</v>
+        <v>0.3525</v>
       </c>
       <c r="J133" t="n">
-        <v>11.232</v>
+        <v>9.5175</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.1</v>
       </c>
       <c r="I134" t="n">
-        <v>0.1725</v>
+        <v>0.1355</v>
       </c>
       <c r="J134" t="n">
-        <v>4.6575</v>
+        <v>3.6585</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.97</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.0717</v>
+        <v>-0.0574</v>
       </c>
       <c r="J135" t="n">
-        <v>-1.9359</v>
+        <v>-1.5498</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.95</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.1</v>
+        <v>-0.08309999999999999</v>
       </c>
       <c r="J136" t="n">
-        <v>-2.7</v>
+        <v>-2.2437</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.26</v>
       </c>
       <c r="I137" t="n">
-        <v>0.429</v>
+        <v>0.4306</v>
       </c>
       <c r="J137" t="n">
-        <v>11.583</v>
+        <v>11.6262</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.09</v>
       </c>
       <c r="I138" t="n">
-        <v>0.1899</v>
+        <v>0.1728</v>
       </c>
       <c r="J138" t="n">
-        <v>5.1273</v>
+        <v>4.6656</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.07</v>
       </c>
       <c r="I139" t="n">
-        <v>0.1572</v>
+        <v>0.1399</v>
       </c>
       <c r="J139" t="n">
-        <v>4.2444</v>
+        <v>3.7773</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.76</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.2867</v>
+        <v>-0.268</v>
       </c>
       <c r="J140" t="n">
-        <v>-7.7409</v>
+        <v>-7.236</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.57</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.4592</v>
+        <v>-0.4549</v>
       </c>
       <c r="J141" t="n">
-        <v>-12.3984</v>
+        <v>-12.2823</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>1.21</v>
       </c>
       <c r="I142" t="n">
-        <v>0.4733</v>
+        <v>0.4167</v>
       </c>
       <c r="J142" t="n">
-        <v>11.3592</v>
+        <v>10.0008</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>0.95</v>
       </c>
       <c r="I143" t="n">
-        <v>-0.0809</v>
+        <v>-0.0674</v>
       </c>
       <c r="J143" t="n">
-        <v>-1.9416</v>
+        <v>-1.6176</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>0.89</v>
       </c>
       <c r="I144" t="n">
-        <v>-0.1514</v>
+        <v>-0.1328</v>
       </c>
       <c r="J144" t="n">
-        <v>-3.6336</v>
+        <v>-3.1872</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>0.85</v>
       </c>
       <c r="I145" t="n">
-        <v>-0.1941</v>
+        <v>-0.1742</v>
       </c>
       <c r="J145" t="n">
-        <v>-4.6584</v>
+        <v>-4.1808</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.3492</v>
+        <v>-0.334</v>
       </c>
       <c r="J146" t="n">
-        <v>-8.380800000000001</v>
+        <v>-8.016</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>1.82</v>
       </c>
       <c r="I147" t="n">
-        <v>1.4962</v>
+        <v>1.5287</v>
       </c>
       <c r="J147" t="n">
-        <v>35.9088</v>
+        <v>36.6888</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>1.57</v>
       </c>
       <c r="I148" t="n">
-        <v>1.1776</v>
+        <v>1.1919</v>
       </c>
       <c r="J148" t="n">
-        <v>28.2624</v>
+        <v>28.6056</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>1.26</v>
       </c>
       <c r="I149" t="n">
-        <v>0.6592</v>
+        <v>0.6333</v>
       </c>
       <c r="J149" t="n">
-        <v>15.8208</v>
+        <v>15.1992</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>1</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.0511</v>
+        <v>-0.0467</v>
       </c>
       <c r="J150" t="n">
-        <v>-1.2264</v>
+        <v>-1.1208</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.87</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.4747</v>
+        <v>-0.4375</v>
       </c>
       <c r="J151" t="n">
-        <v>-11.3928</v>
+        <v>-10.5</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.32</v>
       </c>
       <c r="I152" t="n">
-        <v>0.6226</v>
+        <v>0.5636</v>
       </c>
       <c r="J152" t="n">
-        <v>21.791</v>
+        <v>19.726</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.07</v>
       </c>
       <c r="I153" t="n">
-        <v>0.1883</v>
+        <v>0.1493</v>
       </c>
       <c r="J153" t="n">
-        <v>6.5905</v>
+        <v>5.2255</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>1.05</v>
       </c>
       <c r="I154" t="n">
-        <v>0.145</v>
+        <v>0.112</v>
       </c>
       <c r="J154" t="n">
-        <v>5.075</v>
+        <v>3.92</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>1.03</v>
       </c>
       <c r="I155" t="n">
-        <v>0.09760000000000001</v>
+        <v>0.0726</v>
       </c>
       <c r="J155" t="n">
-        <v>3.416</v>
+        <v>2.541</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.64</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.4038</v>
+        <v>-0.3942</v>
       </c>
       <c r="J156" t="n">
-        <v>-14.133</v>
+        <v>-13.797</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.34</v>
       </c>
       <c r="I157" t="n">
-        <v>0.8458</v>
+        <v>0.8233</v>
       </c>
       <c r="J157" t="n">
-        <v>29.603</v>
+        <v>28.8155</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.34</v>
       </c>
       <c r="I158" t="n">
-        <v>0.8458</v>
+        <v>0.8233</v>
       </c>
       <c r="J158" t="n">
-        <v>29.603</v>
+        <v>28.8155</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.13</v>
       </c>
       <c r="I159" t="n">
-        <v>0.3933</v>
+        <v>0.3566</v>
       </c>
       <c r="J159" t="n">
-        <v>13.7655</v>
+        <v>12.481</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.96</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.1956</v>
+        <v>-0.1609</v>
       </c>
       <c r="J160" t="n">
-        <v>-6.846</v>
+        <v>-5.6315</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.96</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.1956</v>
+        <v>-0.1609</v>
       </c>
       <c r="J161" t="n">
-        <v>-6.846</v>
+        <v>-5.6315</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.05</v>
       </c>
       <c r="I162" t="n">
-        <v>0.2076</v>
+        <v>0.1729</v>
       </c>
       <c r="J162" t="n">
-        <v>5.3976</v>
+        <v>4.4954</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>0.85</v>
       </c>
       <c r="I163" t="n">
-        <v>-0.1812</v>
+        <v>-0.1652</v>
       </c>
       <c r="J163" t="n">
-        <v>-4.7112</v>
+        <v>-4.2952</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>0.7</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.3245</v>
+        <v>-0.3087</v>
       </c>
       <c r="J164" t="n">
-        <v>-8.436999999999999</v>
+        <v>-8.026199999999999</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>0.66</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.3609</v>
+        <v>-0.3468</v>
       </c>
       <c r="J165" t="n">
-        <v>-9.3834</v>
+        <v>-9.0168</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.6</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.4147</v>
+        <v>-0.4044</v>
       </c>
       <c r="J166" t="n">
-        <v>-10.7822</v>
+        <v>-10.5144</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>2.03</v>
       </c>
       <c r="I167" t="n">
-        <v>1.7647</v>
+        <v>1.8267</v>
       </c>
       <c r="J167" t="n">
-        <v>45.8822</v>
+        <v>47.4942</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.15</v>
       </c>
       <c r="I168" t="n">
-        <v>0.4239</v>
+        <v>0.3914</v>
       </c>
       <c r="J168" t="n">
-        <v>11.0214</v>
+        <v>10.1764</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>1.13</v>
       </c>
       <c r="I169" t="n">
-        <v>0.3758</v>
+        <v>0.3432</v>
       </c>
       <c r="J169" t="n">
-        <v>9.770799999999999</v>
+        <v>8.9232</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>1.09</v>
       </c>
       <c r="I170" t="n">
-        <v>0.2733</v>
+        <v>0.2422</v>
       </c>
       <c r="J170" t="n">
-        <v>7.1058</v>
+        <v>6.2972</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.92</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.3365</v>
+        <v>-0.2976</v>
       </c>
       <c r="J171" t="n">
-        <v>-8.749000000000001</v>
+        <v>-7.7376</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.57</v>
       </c>
       <c r="I172" t="n">
-        <v>1.2094</v>
+        <v>1.2257</v>
       </c>
       <c r="J172" t="n">
-        <v>31.4444</v>
+        <v>31.8682</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.26</v>
       </c>
       <c r="I173" t="n">
-        <v>0.6784</v>
+        <v>0.646</v>
       </c>
       <c r="J173" t="n">
-        <v>17.6384</v>
+        <v>16.796</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>1.18</v>
       </c>
       <c r="I174" t="n">
-        <v>0.5058</v>
+        <v>0.4691</v>
       </c>
       <c r="J174" t="n">
-        <v>13.1508</v>
+        <v>12.1966</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>1.05</v>
       </c>
       <c r="I175" t="n">
-        <v>0.1763</v>
+        <v>0.1495</v>
       </c>
       <c r="J175" t="n">
-        <v>4.5838</v>
+        <v>3.887</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.74</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.7526</v>
+        <v>-0.7269</v>
       </c>
       <c r="J176" t="n">
-        <v>-19.5676</v>
+        <v>-18.8994</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.36</v>
       </c>
       <c r="I177" t="n">
-        <v>0.6882</v>
+        <v>0.6312</v>
       </c>
       <c r="J177" t="n">
-        <v>17.8932</v>
+        <v>16.4112</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.28</v>
       </c>
       <c r="I178" t="n">
-        <v>0.5634</v>
+        <v>0.5041</v>
       </c>
       <c r="J178" t="n">
-        <v>14.6484</v>
+        <v>13.1066</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>0.9</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.1476</v>
+        <v>-0.1279</v>
       </c>
       <c r="J179" t="n">
-        <v>-3.8376</v>
+        <v>-3.3254</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.78</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.2728</v>
+        <v>-0.2537</v>
       </c>
       <c r="J180" t="n">
-        <v>-7.0928</v>
+        <v>-6.5962</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.72</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.3299</v>
+        <v>-0.3139</v>
       </c>
       <c r="J181" t="n">
-        <v>-8.577400000000001</v>
+        <v>-8.1614</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.84</v>
       </c>
       <c r="I182" t="n">
-        <v>1.4794</v>
+        <v>1.5099</v>
       </c>
       <c r="J182" t="n">
-        <v>28.1086</v>
+        <v>28.6881</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>1.53</v>
       </c>
       <c r="I183" t="n">
-        <v>1.1</v>
+        <v>1.1179</v>
       </c>
       <c r="J183" t="n">
-        <v>20.9</v>
+        <v>21.2401</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>1.5</v>
       </c>
       <c r="I184" t="n">
-        <v>1.0623</v>
+        <v>1.0778</v>
       </c>
       <c r="J184" t="n">
-        <v>20.1837</v>
+        <v>20.4782</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>1.35</v>
       </c>
       <c r="I185" t="n">
-        <v>0.8109</v>
+        <v>0.8004</v>
       </c>
       <c r="J185" t="n">
-        <v>15.4071</v>
+        <v>15.2076</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>1.31</v>
       </c>
       <c r="I186" t="n">
-        <v>0.7327</v>
+        <v>0.7166</v>
       </c>
       <c r="J186" t="n">
-        <v>13.9213</v>
+        <v>13.6154</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.14</v>
       </c>
       <c r="I187" t="n">
-        <v>0.5068</v>
+        <v>0.5007</v>
       </c>
       <c r="J187" t="n">
-        <v>9.629200000000001</v>
+        <v>9.513299999999999</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>0.68</v>
       </c>
       <c r="I188" t="n">
-        <v>-0.3239</v>
+        <v>-0.3135</v>
       </c>
       <c r="J188" t="n">
-        <v>-6.1541</v>
+        <v>-5.9565</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>0.44</v>
       </c>
       <c r="I189" t="n">
-        <v>-0.5341</v>
+        <v>-0.5362</v>
       </c>
       <c r="J189" t="n">
-        <v>-10.1479</v>
+        <v>-10.1878</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>0.41</v>
       </c>
       <c r="I190" t="n">
-        <v>-0.5606</v>
+        <v>-0.5661</v>
       </c>
       <c r="J190" t="n">
-        <v>-10.6514</v>
+        <v>-10.7559</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.37</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.5959</v>
+        <v>-0.6066</v>
       </c>
       <c r="J191" t="n">
-        <v>-11.3221</v>
+        <v>-11.5254</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>1.76</v>
       </c>
       <c r="I192" t="n">
-        <v>1.42</v>
+        <v>1.4465</v>
       </c>
       <c r="J192" t="n">
-        <v>36.92</v>
+        <v>37.609</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>1.33</v>
       </c>
       <c r="I193" t="n">
-        <v>0.7953</v>
+        <v>0.7758</v>
       </c>
       <c r="J193" t="n">
-        <v>20.6778</v>
+        <v>20.1708</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>1.26</v>
       </c>
       <c r="I194" t="n">
-        <v>0.6585</v>
+        <v>0.6328</v>
       </c>
       <c r="J194" t="n">
-        <v>17.121</v>
+        <v>16.4528</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>1.11</v>
       </c>
       <c r="I195" t="n">
-        <v>0.3182</v>
+        <v>0.2864</v>
       </c>
       <c r="J195" t="n">
-        <v>8.273199999999999</v>
+        <v>7.4464</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>1.09</v>
       </c>
       <c r="I196" t="n">
-        <v>0.2658</v>
+        <v>0.2348</v>
       </c>
       <c r="J196" t="n">
-        <v>6.9108</v>
+        <v>6.1048</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>1.08</v>
       </c>
       <c r="I197" t="n">
-        <v>0.293</v>
+        <v>0.2561</v>
       </c>
       <c r="J197" t="n">
-        <v>7.618</v>
+        <v>6.6586</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I198" t="n">
-        <v>-0.2178</v>
+        <v>-0.2023</v>
       </c>
       <c r="J198" t="n">
-        <v>-5.6628</v>
+        <v>-5.2598</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>0.76</v>
       </c>
       <c r="I199" t="n">
-        <v>-0.2667</v>
+        <v>-0.2514</v>
       </c>
       <c r="J199" t="n">
-        <v>-6.9342</v>
+        <v>-6.5364</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>0.57</v>
       </c>
       <c r="I200" t="n">
-        <v>-0.437</v>
+        <v>-0.4287</v>
       </c>
       <c r="J200" t="n">
-        <v>-11.362</v>
+        <v>-11.1462</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>0.46</v>
       </c>
       <c r="I201" t="n">
-        <v>-0.5332</v>
+        <v>-0.5361</v>
       </c>
       <c r="J201" t="n">
-        <v>-13.8632</v>
+        <v>-13.9386</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>0.96</v>
       </c>
       <c r="I202" t="n">
-        <v>0.0162</v>
+        <v>0.0604</v>
       </c>
       <c r="J202" t="n">
-        <v>0.2754</v>
+        <v>1.0268</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>0.75</v>
       </c>
       <c r="I203" t="n">
-        <v>-0.2482</v>
+        <v>-0.2337</v>
       </c>
       <c r="J203" t="n">
-        <v>-4.2194</v>
+        <v>-3.9729</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>0.53</v>
       </c>
       <c r="I204" t="n">
-        <v>-0.4511</v>
+        <v>-0.4459</v>
       </c>
       <c r="J204" t="n">
-        <v>-7.6687</v>
+        <v>-7.5803</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>0.34</v>
       </c>
       <c r="I205" t="n">
-        <v>-0.6188</v>
+        <v>-0.633</v>
       </c>
       <c r="J205" t="n">
-        <v>-10.5196</v>
+        <v>-10.761</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>0.33</v>
       </c>
       <c r="I206" t="n">
-        <v>-0.6277</v>
+        <v>-0.6434</v>
       </c>
       <c r="J206" t="n">
-        <v>-10.6709</v>
+        <v>-10.9378</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>2.03</v>
       </c>
       <c r="I207" t="n">
-        <v>1.6753</v>
+        <v>1.7212</v>
       </c>
       <c r="J207" t="n">
-        <v>28.4801</v>
+        <v>29.2604</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>1.83</v>
       </c>
       <c r="I208" t="n">
-        <v>1.447</v>
+        <v>1.4785</v>
       </c>
       <c r="J208" t="n">
-        <v>24.599</v>
+        <v>25.1345</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>1.71</v>
       </c>
       <c r="I209" t="n">
-        <v>1.3069</v>
+        <v>1.3332</v>
       </c>
       <c r="J209" t="n">
-        <v>22.2173</v>
+        <v>22.6644</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>1.43</v>
       </c>
       <c r="I210" t="n">
-        <v>0.9404</v>
+        <v>0.9449</v>
       </c>
       <c r="J210" t="n">
-        <v>15.9868</v>
+        <v>16.0633</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>1.29</v>
       </c>
       <c r="I211" t="n">
-        <v>0.6723</v>
+        <v>0.6529</v>
       </c>
       <c r="J211" t="n">
-        <v>11.4291</v>
+        <v>11.0993</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.95</v>
       </c>
       <c r="I212" t="n">
-        <v>1.6296</v>
+        <v>1.6718</v>
       </c>
       <c r="J212" t="n">
-        <v>34.2216</v>
+        <v>35.1078</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.52</v>
       </c>
       <c r="I213" t="n">
-        <v>1.0969</v>
+        <v>1.1113</v>
       </c>
       <c r="J213" t="n">
-        <v>23.0349</v>
+        <v>23.3373</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.29</v>
       </c>
       <c r="I214" t="n">
-        <v>0.7065</v>
+        <v>0.6866</v>
       </c>
       <c r="J214" t="n">
-        <v>14.8365</v>
+        <v>14.4186</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>1.22</v>
       </c>
       <c r="I215" t="n">
-        <v>0.5605</v>
+        <v>0.5336</v>
       </c>
       <c r="J215" t="n">
-        <v>11.7705</v>
+        <v>11.2056</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>1.05</v>
       </c>
       <c r="I216" t="n">
-        <v>0.1361</v>
+        <v>0.1085</v>
       </c>
       <c r="J216" t="n">
-        <v>2.8581</v>
+        <v>2.2785</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>0.97</v>
       </c>
       <c r="I217" t="n">
-        <v>-0.0222</v>
+        <v>-0.0108</v>
       </c>
       <c r="J217" t="n">
-        <v>-0.4662</v>
+        <v>-0.2268</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>0.96</v>
       </c>
       <c r="I218" t="n">
-        <v>-0.0376</v>
+        <v>-0.025</v>
       </c>
       <c r="J218" t="n">
-        <v>-0.7896</v>
+        <v>-0.525</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>0.73</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.2933</v>
+        <v>-0.2783</v>
       </c>
       <c r="J219" t="n">
-        <v>-6.1593</v>
+        <v>-5.8443</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.53</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.4712</v>
+        <v>-0.4663</v>
       </c>
       <c r="J220" t="n">
-        <v>-9.895200000000001</v>
+        <v>-9.792299999999999</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.45</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.541</v>
+        <v>-0.5449000000000001</v>
       </c>
       <c r="J221" t="n">
-        <v>-11.361</v>
+        <v>-11.4429</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.68</v>
       </c>
       <c r="I222" t="n">
-        <v>1.3124</v>
+        <v>1.3323</v>
       </c>
       <c r="J222" t="n">
-        <v>27.5604</v>
+        <v>27.9783</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.51</v>
       </c>
       <c r="I223" t="n">
-        <v>1.0922</v>
+        <v>1.1046</v>
       </c>
       <c r="J223" t="n">
-        <v>22.9362</v>
+        <v>23.1966</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.43</v>
       </c>
       <c r="I224" t="n">
-        <v>0.9747</v>
+        <v>0.9719</v>
       </c>
       <c r="J224" t="n">
-        <v>20.4687</v>
+        <v>20.4099</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1.27</v>
       </c>
       <c r="I225" t="n">
-        <v>0.6747</v>
+        <v>0.651</v>
       </c>
       <c r="J225" t="n">
-        <v>14.1687</v>
+        <v>13.671</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>0.82</v>
       </c>
       <c r="I226" t="n">
-        <v>-0.6011</v>
+        <v>-0.57</v>
       </c>
       <c r="J226" t="n">
-        <v>-12.6231</v>
+        <v>-11.97</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>0.87</v>
       </c>
       <c r="I227" t="n">
-        <v>-0.1425</v>
+        <v>-0.126</v>
       </c>
       <c r="J227" t="n">
-        <v>-2.9925</v>
+        <v>-2.646</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>0.86</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.154</v>
+        <v>-0.1377</v>
       </c>
       <c r="J228" t="n">
-        <v>-3.234</v>
+        <v>-2.8917</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.67</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.3419</v>
+        <v>-0.3293</v>
       </c>
       <c r="J229" t="n">
-        <v>-7.1799</v>
+        <v>-6.9153</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.58</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.4212</v>
+        <v>-0.412</v>
       </c>
       <c r="J230" t="n">
-        <v>-8.8452</v>
+        <v>-8.651999999999999</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.43</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.5528999999999999</v>
+        <v>-0.5580000000000001</v>
       </c>
       <c r="J231" t="n">
-        <v>-11.6109</v>
+        <v>-11.718</v>
       </c>
     </row>
   </sheetData>
